--- a/analysis/TEST/ABATCH.v2.0.0.xlsx
+++ b/analysis/TEST/ABATCH.v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DBB61A-CDCF-7B41-8156-E722635F0DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675D6DB3-9CA7-DE42-A7CB-92013E88CA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="6" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="214">
   <si>
     <t>Assay</t>
   </si>
@@ -600,9 +600,6 @@
     <t>D6</t>
   </si>
   <si>
-    <t>E1</t>
-  </si>
-  <si>
     <t>E42</t>
   </si>
   <si>
@@ -616,9 +613,6 @@
   </si>
   <si>
     <t>E6</t>
-  </si>
-  <si>
-    <t>F42</t>
   </si>
   <si>
     <t>F2</t>
@@ -1499,6 +1493,12 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1527,12 +1527,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1760,7 +1754,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="64" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B1" s="65" t="s">
         <v>0</v>
@@ -1792,7 +1786,7 @@
     </row>
     <row r="2" spans="1:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B2" s="70" t="s">
         <v>106</v>
@@ -1920,10 +1914,10 @@
     </row>
     <row r="6" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="75" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B6" s="75" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C6" s="73"/>
       <c r="D6" s="67"/>
@@ -1952,13 +1946,13 @@
     </row>
     <row r="7" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="71" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B7" s="71">
         <v>5</v>
       </c>
       <c r="C7" s="94" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D7" s="67"/>
       <c r="E7" s="67"/>
@@ -1986,7 +1980,7 @@
     </row>
     <row r="8" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="73" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B8" s="73">
         <v>20</v>
@@ -2114,7 +2108,7 @@
     </row>
     <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="73" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B12" s="73" t="s">
         <v>134</v>
@@ -2209,10 +2203,10 @@
       <c r="Z14" s="67"/>
     </row>
     <row r="15" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="112" t="s">
-        <v>211</v>
+      <c r="A15" s="98" t="s">
+        <v>209</v>
       </c>
-      <c r="B15" s="113" t="s">
+      <c r="B15" s="99" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="97"/>
@@ -2242,7 +2236,7 @@
     </row>
     <row r="16" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="96" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B16" s="96" t="s">
         <v>61</v>
@@ -2378,9 +2372,11 @@
     </row>
     <row r="21" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="79" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
-      <c r="B21" s="79"/>
+      <c r="B21" s="79">
+        <v>0</v>
+      </c>
       <c r="C21" s="76"/>
       <c r="D21" s="67"/>
       <c r="E21" s="67"/>
@@ -2457,10 +2453,10 @@
     </row>
     <row r="25" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="85" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B25" s="84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" s="78"/>
       <c r="E25" s="67"/>
@@ -2488,7 +2484,7 @@
     </row>
     <row r="26" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="85" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B26" s="85">
         <v>0</v>
@@ -2615,10 +2611,10 @@
     </row>
     <row r="30" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="89" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B30" s="89" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C30" s="76"/>
       <c r="D30" s="67"/>
@@ -2647,7 +2643,7 @@
     </row>
     <row r="31" spans="1:26" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="89" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B31" s="89">
         <v>100</v>
@@ -2679,7 +2675,7 @@
     </row>
     <row r="32" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="96" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B32" s="91" t="s">
         <v>66</v>
@@ -2838,9 +2834,11 @@
     </row>
     <row r="37" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="79" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
-      <c r="B37" s="79"/>
+      <c r="B37" s="79">
+        <v>0</v>
+      </c>
       <c r="C37" s="67"/>
       <c r="D37" s="67"/>
       <c r="E37" s="67"/>
@@ -2961,10 +2959,10 @@
     </row>
     <row r="41" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="85" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B41" s="84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D41" s="67"/>
       <c r="E41" s="67"/>
@@ -2992,7 +2990,7 @@
     </row>
     <row r="42" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="85" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B42" s="85">
         <v>0</v>
@@ -3120,10 +3118,10 @@
     </row>
     <row r="46" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="89" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B46" s="89" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C46" s="67"/>
       <c r="D46" s="67"/>
@@ -3152,7 +3150,7 @@
     </row>
     <row r="47" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="89" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B47" s="89">
         <v>600</v>
@@ -3184,7 +3182,7 @@
     </row>
     <row r="48" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="96" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B48" s="91" t="s">
         <v>63</v>
@@ -3343,7 +3341,7 @@
     </row>
     <row r="53" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="79" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B53" s="79">
         <v>0</v>
@@ -3468,10 +3466,10 @@
     </row>
     <row r="57" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="85" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B57" s="84" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D57" s="67"/>
       <c r="E57" s="67"/>
@@ -3499,7 +3497,7 @@
     </row>
     <row r="58" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="85" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B58" s="85">
         <v>0</v>
@@ -3651,7 +3649,7 @@
     </row>
     <row r="63" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="92" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B63" s="92"/>
       <c r="C63" s="77"/>
@@ -27987,23 +27985,21 @@
       <c r="A6" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="D6" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="E6" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="F6" s="42" t="s">
         <v>189</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="G6" s="43" t="s">
         <v>190</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>191</v>
       </c>
       <c r="H6" s="42"/>
       <c r="I6" s="43"/>
@@ -28016,23 +28012,21 @@
       <c r="A7" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="43"/>
+      <c r="C7" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="43" t="s">
         <v>192</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="E7" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="F7" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="G7" s="42" t="s">
         <v>195</v>
-      </c>
-      <c r="F7" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>197</v>
       </c>
       <c r="H7" s="43"/>
       <c r="I7" s="42"/>
@@ -31197,7 +31191,7 @@
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="43" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="43"/>
@@ -37440,25 +37434,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="107"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="109"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="3"/>
@@ -37476,17 +37470,17 @@
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="108" t="s">
+      <c r="C2" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="107"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="109"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -37605,11 +37599,11 @@
       <c r="B6" s="16">
         <v>16.5</v>
       </c>
-      <c r="C6" s="101" t="s">
+      <c r="C6" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
@@ -37639,9 +37633,9 @@
       <c r="B7" s="16">
         <v>5.5</v>
       </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
       <c r="F7" s="14"/>
       <c r="G7" s="14"/>
       <c r="H7" s="14"/>
@@ -37672,9 +37666,9 @@
         <f>SUM(B6:B7)</f>
         <v>22</v>
       </c>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
+      <c r="C8" s="104"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
@@ -37704,9 +37698,9 @@
       <c r="B9" s="16">
         <v>20</v>
       </c>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
@@ -37758,12 +37752,12 @@
       <c r="Z10" s="3"/>
     </row>
     <row r="11" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="109" t="s">
+      <c r="A11" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="107"/>
+      <c r="B11" s="108"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="109"/>
       <c r="E11" s="18"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
@@ -37841,7 +37835,7 @@
       <c r="C15" s="23">
         <v>0.5</v>
       </c>
-      <c r="D15" s="110">
+      <c r="D15" s="112">
         <v>40</v>
       </c>
     </row>
@@ -37855,7 +37849,7 @@
       <c r="C16" s="23">
         <v>1</v>
       </c>
-      <c r="D16" s="111"/>
+      <c r="D16" s="113"/>
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
@@ -37878,12 +37872,12 @@
       <c r="D18" s="18"/>
     </row>
     <row r="19" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="98" t="s">
+      <c r="A19" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="99"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="100"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="102"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
@@ -37922,20 +37916,20 @@
       </c>
       <c r="B24" s="28">
         <f>COUNTIF(Samples!B2:M9,"&lt;&gt;"&amp;"")</f>
-        <v>38</v>
+        <v>36</v>
       </c>
-      <c r="C24" s="101" t="s">
+      <c r="C24" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="102"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="102"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="102"/>
+      <c r="D24" s="104"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -38014,10 +38008,10 @@
       <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="103" t="s">
+      <c r="A27" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="104"/>
+      <c r="B27" s="106"/>
       <c r="C27" s="31"/>
       <c r="D27" s="31"/>
       <c r="E27" s="18"/>
@@ -38043,7 +38037,7 @@
       </c>
       <c r="B28" s="34">
         <f>ROUNDUP(B33-B29-B30-B31-($B$5*B32),0)</f>
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C28" s="35"/>
       <c r="D28" s="35"/>
@@ -38070,7 +38064,7 @@
       </c>
       <c r="B29" s="34">
         <f>ROUNDUP(5.5*($B$24*B25),0)</f>
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>41</v>
@@ -38099,7 +38093,7 @@
       </c>
       <c r="B30" s="34">
         <f>ROUNDUP(2.2*($B$24*B25),1)</f>
-        <v>92</v>
+        <v>87.199999999999989</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>41</v>
@@ -38128,7 +38122,7 @@
       </c>
       <c r="B31" s="34">
         <f>ROUNDUP(1.1*$B$24*B25,1)</f>
-        <v>46</v>
+        <v>43.6</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>41</v>
@@ -38157,7 +38151,7 @@
       </c>
       <c r="B32" s="34">
         <f>ROUNDUP(1.1*$B$24*B25,1)</f>
-        <v>46</v>
+        <v>43.6</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>41</v>
@@ -38186,7 +38180,7 @@
       </c>
       <c r="B33" s="38">
         <f>ROUNDUP(B25*$B$24*16.5,0)</f>
-        <v>690</v>
+        <v>654</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>46</v>

--- a/analysis/TEST/ABATCH.v2.0.0.xlsx
+++ b/analysis/TEST/ABATCH.v2.0.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA135599-6095-AE4D-83FC-4FE756CF0857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40913497-018A-6844-BCCA-BD640B1F1250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="220">
   <si>
     <t>Assay</t>
   </si>
@@ -282,12 +282,6 @@
     <t>SARS-CoV-2 ddPCR Triplex (dEXD28563542)</t>
   </si>
   <si>
-    <t>ZPM Lab QX200</t>
-  </si>
-  <si>
-    <t>ZPM Lab QX600</t>
-  </si>
-  <si>
     <t>SARS-CoV-2</t>
   </si>
   <si>
@@ -325,9 +319,6 @@
   </si>
   <si>
     <t>DNA</t>
-  </si>
-  <si>
-    <t>Monkeypox Virus (MPXV)</t>
   </si>
   <si>
     <t>Respiratory Syncitial Virus (RSV)</t>
@@ -388,9 +379,6 @@
   </si>
   <si>
     <t>RT-PCR</t>
-  </si>
-  <si>
-    <t>Control 2 Well ID</t>
   </si>
   <si>
     <t>PCR Positive</t>
@@ -695,16 +683,41 @@
   <si>
     <t>QX Manager Version</t>
   </si>
+  <si>
+    <t>Mpox Virus (MPXV)</t>
+  </si>
+  <si>
+    <t>Zoo QX200</t>
+  </si>
+  <si>
+    <t>Zoo QX600</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>ROX</t>
+  </si>
+  <si>
+    <t>ATTO 590</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1264,271 +1277,266 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="24" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="25" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1744,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D39BBE7-67FA-5442-B147-F43387474561}">
-  <dimension ref="A1:Z988"/>
+  <dimension ref="A1:Z924"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5703125" style="57" customWidth="1"/>
@@ -1756,7 +1764,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="53" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B1" s="54" t="s">
         <v>0</v>
@@ -1788,10 +1796,10 @@
     </row>
     <row r="2" spans="1:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="58" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C2" s="55"/>
       <c r="D2" s="56"/>
@@ -1855,7 +1863,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="56"/>
@@ -1887,7 +1895,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="C5" s="56"/>
       <c r="D5" s="56"/>
@@ -1915,11 +1923,11 @@
       <c r="Z5" s="56"/>
     </row>
     <row r="6" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="99" t="s">
-        <v>217</v>
-      </c>
-      <c r="B6" s="99" t="s">
-        <v>215</v>
+      <c r="A6" s="56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>211</v>
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="56"/>
@@ -1947,11 +1955,11 @@
       <c r="Z6" s="56"/>
     </row>
     <row r="7" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="102" t="s">
-        <v>208</v>
-      </c>
-      <c r="B7" s="102" t="s">
-        <v>211</v>
+      <c r="A7" s="86" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>207</v>
       </c>
       <c r="C7" s="56"/>
       <c r="D7" s="56"/>
@@ -1979,14 +1987,14 @@
       <c r="Z7" s="56"/>
     </row>
     <row r="8" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="99" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8" s="99">
+      <c r="A8" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="56">
         <v>5</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="56"/>
@@ -2014,7 +2022,7 @@
     </row>
     <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="60" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B9" s="60">
         <v>20</v>
@@ -2045,10 +2053,10 @@
       <c r="Z9" s="56"/>
     </row>
     <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="99" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="99" t="s">
+      <c r="A10" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>70</v>
       </c>
       <c r="C10" s="63"/>
@@ -2078,7 +2086,7 @@
     </row>
     <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="60" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B11" s="60">
         <v>456645</v>
@@ -2109,11 +2117,11 @@
       <c r="Z11" s="56"/>
     </row>
     <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="99" t="s">
-        <v>154</v>
-      </c>
-      <c r="B12" s="99" t="s">
-        <v>114</v>
+      <c r="A12" s="56" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>111</v>
       </c>
       <c r="C12" s="63"/>
       <c r="D12" s="56"/>
@@ -2142,10 +2150,10 @@
     </row>
     <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="60" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="56"/>
@@ -2173,10 +2181,10 @@
       <c r="Z13" s="56"/>
     </row>
     <row r="14" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="99" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="99" t="s">
+      <c r="A14" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="56" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="63"/>
@@ -2205,10 +2213,10 @@
       <c r="Z14" s="56"/>
     </row>
     <row r="15" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="103" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" s="103">
+      <c r="A15" s="87" t="s">
+        <v>152</v>
+      </c>
+      <c r="B15" s="87">
         <v>4242</v>
       </c>
       <c r="C15" s="81"/>
@@ -2237,10 +2245,10 @@
       <c r="Z15" s="56"/>
     </row>
     <row r="16" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="100" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="101" t="s">
+      <c r="A16" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="B16" s="85" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="83"/>
@@ -2270,7 +2278,7 @@
     </row>
     <row r="17" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="82" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B17" s="82" t="s">
         <v>61</v>
@@ -2301,10 +2309,10 @@
     </row>
     <row r="18" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="66" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C18" s="63"/>
       <c r="D18" s="56"/>
@@ -2333,19 +2341,19 @@
     </row>
     <row r="19" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="67" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B19" s="68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C19" s="65"/>
     </row>
     <row r="20" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="66" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B20" s="66" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C20" s="63"/>
       <c r="D20" s="56"/>
@@ -2374,10 +2382,10 @@
     </row>
     <row r="21" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="66" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="56"/>
@@ -2406,7 +2414,7 @@
     </row>
     <row r="22" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="66" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B22" s="66">
         <v>0</v>
@@ -2438,19 +2446,19 @@
     </row>
     <row r="23" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="69" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C23" s="65"/>
     </row>
     <row r="24" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="69" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>59</v>
+        <v>217</v>
       </c>
       <c r="C24" s="65"/>
       <c r="E24" s="56"/>
@@ -2478,19 +2486,19 @@
     </row>
     <row r="25" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="69" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B25" s="70" t="s">
-        <v>59</v>
+        <v>217</v>
       </c>
       <c r="C25" s="65"/>
     </row>
     <row r="26" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="72" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C26" s="65"/>
       <c r="E26" s="56"/>
@@ -2518,7 +2526,7 @@
     </row>
     <row r="27" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="72" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B27" s="72">
         <v>0</v>
@@ -2549,10 +2557,10 @@
     </row>
     <row r="28" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="73" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B28" s="74" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C28" s="75"/>
       <c r="D28" s="56"/>
@@ -2581,10 +2589,10 @@
     </row>
     <row r="29" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="76" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="76" t="s">
         <v>120</v>
-      </c>
-      <c r="B29" s="76" t="s">
-        <v>124</v>
       </c>
       <c r="C29" s="63"/>
       <c r="D29" s="56"/>
@@ -2613,10 +2621,10 @@
     </row>
     <row r="30" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="73" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B30" s="77" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C30" s="75"/>
       <c r="D30" s="56"/>
@@ -2645,10 +2653,10 @@
     </row>
     <row r="31" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="76" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B31" s="76" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C31" s="63"/>
       <c r="D31" s="56"/>
@@ -2676,8 +2684,8 @@
       <c r="Z31" s="56"/>
     </row>
     <row r="32" spans="1:26" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="76" t="s">
-        <v>198</v>
+      <c r="A32" s="79" t="s">
+        <v>194</v>
       </c>
       <c r="B32" s="76">
         <v>100</v>
@@ -2709,7 +2717,7 @@
     </row>
     <row r="33" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="82" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B33" s="78" t="s">
         <v>66</v>
@@ -2741,10 +2749,10 @@
     </row>
     <row r="34" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="66" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B34" s="66" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C34" s="56"/>
       <c r="D34" s="56"/>
@@ -2773,10 +2781,10 @@
     </row>
     <row r="35" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="67" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B35" s="68" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D35" s="56"/>
       <c r="E35" s="56"/>
@@ -2804,10 +2812,10 @@
     </row>
     <row r="36" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="66" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B36" s="66" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
@@ -2836,10 +2844,10 @@
     </row>
     <row r="37" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="66" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B37" s="66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
@@ -2868,7 +2876,7 @@
     </row>
     <row r="38" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="66" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B38" s="66">
         <v>0</v>
@@ -2900,10 +2908,10 @@
     </row>
     <row r="39" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="69" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B39" s="70" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D39" s="56"/>
       <c r="E39" s="56"/>
@@ -2931,10 +2939,10 @@
     </row>
     <row r="40" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="69" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B40" s="71" t="s">
-        <v>59</v>
+        <v>217</v>
       </c>
       <c r="D40" s="56"/>
       <c r="E40" s="56"/>
@@ -2962,10 +2970,10 @@
     </row>
     <row r="41" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="69" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B41" s="70" t="s">
-        <v>59</v>
+        <v>217</v>
       </c>
       <c r="D41" s="56"/>
       <c r="E41" s="56"/>
@@ -2993,10 +3001,10 @@
     </row>
     <row r="42" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="72" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B42" s="71" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D42" s="56"/>
       <c r="E42" s="56"/>
@@ -3024,7 +3032,7 @@
     </row>
     <row r="43" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="72" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B43" s="72">
         <v>0</v>
@@ -3056,10 +3064,10 @@
     </row>
     <row r="44" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="73" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B44" s="74" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C44" s="56"/>
       <c r="D44" s="56"/>
@@ -3088,10 +3096,10 @@
     </row>
     <row r="45" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="76" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="76" t="s">
         <v>120</v>
-      </c>
-      <c r="B45" s="76" t="s">
-        <v>124</v>
       </c>
       <c r="C45" s="56"/>
       <c r="D45" s="56"/>
@@ -3120,10 +3128,10 @@
     </row>
     <row r="46" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="73" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B46" s="77" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C46" s="56"/>
       <c r="D46" s="56"/>
@@ -3152,10 +3160,10 @@
     </row>
     <row r="47" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="76" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B47" s="76" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
@@ -3183,10 +3191,10 @@
       <c r="Z47" s="56"/>
     </row>
     <row r="48" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="76" t="s">
-        <v>198</v>
-      </c>
-      <c r="B48" s="76">
+      <c r="A48" s="79" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" s="79">
         <v>600</v>
       </c>
       <c r="C48" s="64"/>
@@ -3216,11 +3224,12 @@
     </row>
     <row r="49" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="82" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B49" s="78" t="s">
         <v>63</v>
       </c>
+      <c r="C49" s="65"/>
       <c r="D49" s="56"/>
       <c r="E49" s="56"/>
       <c r="F49" s="56"/>
@@ -3247,10 +3256,10 @@
     </row>
     <row r="50" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="66" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B50" s="66" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C50" s="56"/>
       <c r="D50" s="56"/>
@@ -3279,12 +3288,11 @@
     </row>
     <row r="51" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="67" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B51" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="C51" s="56"/>
+        <v>149</v>
+      </c>
       <c r="D51" s="56"/>
       <c r="E51" s="56"/>
       <c r="F51" s="56"/>
@@ -3311,10 +3319,10 @@
     </row>
     <row r="52" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="66" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B52" s="66" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C52" s="56"/>
       <c r="D52" s="56"/>
@@ -3343,10 +3351,10 @@
     </row>
     <row r="53" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="66" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B53" s="66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C53" s="56"/>
       <c r="D53" s="56"/>
@@ -3375,7 +3383,7 @@
     </row>
     <row r="54" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="66" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B54" s="66">
         <v>0</v>
@@ -3407,10 +3415,10 @@
     </row>
     <row r="55" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="69" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B55" s="70" t="s">
-        <v>118</v>
+        <v>217</v>
       </c>
       <c r="D55" s="56"/>
       <c r="E55" s="56"/>
@@ -3438,10 +3446,10 @@
     </row>
     <row r="56" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="69" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B56" s="71" t="s">
-        <v>59</v>
+        <v>217</v>
       </c>
       <c r="D56" s="56"/>
       <c r="E56" s="56"/>
@@ -3469,10 +3477,10 @@
     </row>
     <row r="57" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="69" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B57" s="70" t="s">
-        <v>59</v>
+        <v>217</v>
       </c>
       <c r="D57" s="56"/>
       <c r="E57" s="56"/>
@@ -3500,11 +3508,9 @@
     </row>
     <row r="58" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="72" t="s">
-        <v>202</v>
-      </c>
-      <c r="B58" s="71" t="s">
-        <v>201</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B58" s="71"/>
       <c r="D58" s="56"/>
       <c r="E58" s="56"/>
       <c r="F58" s="56"/>
@@ -3531,11 +3537,9 @@
     </row>
     <row r="59" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="72" t="s">
-        <v>197</v>
-      </c>
-      <c r="B59" s="72">
-        <v>0</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="B59" s="72"/>
       <c r="C59" s="56"/>
       <c r="D59" s="56"/>
       <c r="E59" s="56"/>
@@ -3563,9 +3567,11 @@
     </row>
     <row r="60" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="73" t="s">
-        <v>108</v>
-      </c>
-      <c r="B60" s="74"/>
+        <v>105</v>
+      </c>
+      <c r="B60" s="74" t="s">
+        <v>217</v>
+      </c>
       <c r="C60" s="56"/>
       <c r="D60" s="56"/>
       <c r="E60" s="56"/>
@@ -3593,9 +3599,11 @@
     </row>
     <row r="61" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="76" t="s">
-        <v>120</v>
-      </c>
-      <c r="B61" s="76"/>
+        <v>116</v>
+      </c>
+      <c r="B61" s="76" t="s">
+        <v>217</v>
+      </c>
       <c r="C61" s="56"/>
       <c r="D61" s="56"/>
       <c r="E61" s="56"/>
@@ -3623,9 +3631,11 @@
     </row>
     <row r="62" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="73" t="s">
-        <v>103</v>
-      </c>
-      <c r="B62" s="77"/>
+        <v>100</v>
+      </c>
+      <c r="B62" s="77" t="s">
+        <v>217</v>
+      </c>
       <c r="C62" s="56"/>
       <c r="D62" s="56"/>
       <c r="E62" s="56"/>
@@ -3653,7 +3663,7 @@
     </row>
     <row r="63" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="76" t="s">
-        <v>116</v>
+        <v>199</v>
       </c>
       <c r="B63" s="76"/>
       <c r="C63" s="56"/>
@@ -3683,7 +3693,7 @@
     </row>
     <row r="64" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="79" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B64" s="79"/>
       <c r="C64" s="64"/>
@@ -3711,74 +3721,1802 @@
       <c r="Y64" s="56"/>
       <c r="Z64" s="56"/>
     </row>
-    <row r="65" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" spans="1:26" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" spans="1:26" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" spans="1:26" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" spans="1:26" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="1:26" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="1:26" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:26" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="1:26" s="80" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="56"/>
+      <c r="B69" s="56"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="56"/>
+      <c r="F69" s="56"/>
+      <c r="G69" s="56"/>
+      <c r="H69" s="56"/>
+      <c r="I69" s="56"/>
+      <c r="J69" s="56"/>
+      <c r="K69" s="56"/>
+      <c r="L69" s="56"/>
+      <c r="M69" s="56"/>
+      <c r="N69" s="56"/>
+      <c r="O69" s="56"/>
+      <c r="P69" s="56"/>
+      <c r="Q69" s="56"/>
+      <c r="R69" s="56"/>
+      <c r="S69" s="56"/>
+      <c r="T69" s="56"/>
+      <c r="U69" s="56"/>
+      <c r="V69" s="56"/>
+      <c r="W69" s="56"/>
+      <c r="X69" s="56"/>
+      <c r="Y69" s="56"/>
+      <c r="Z69" s="56"/>
+    </row>
+    <row r="70" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="56"/>
+      <c r="B70" s="56"/>
+      <c r="C70" s="56"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="56"/>
+      <c r="F70" s="56"/>
+      <c r="G70" s="56"/>
+      <c r="H70" s="56"/>
+      <c r="I70" s="56"/>
+      <c r="J70" s="56"/>
+      <c r="K70" s="56"/>
+      <c r="L70" s="56"/>
+      <c r="M70" s="56"/>
+      <c r="N70" s="56"/>
+      <c r="O70" s="56"/>
+      <c r="P70" s="56"/>
+      <c r="Q70" s="56"/>
+      <c r="R70" s="56"/>
+      <c r="S70" s="56"/>
+      <c r="T70" s="56"/>
+      <c r="U70" s="56"/>
+      <c r="V70" s="56"/>
+      <c r="W70" s="56"/>
+      <c r="X70" s="56"/>
+      <c r="Y70" s="56"/>
+      <c r="Z70" s="56"/>
+    </row>
+    <row r="71" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="56"/>
+      <c r="B71" s="56"/>
+      <c r="C71" s="56"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="56"/>
+      <c r="F71" s="56"/>
+      <c r="G71" s="56"/>
+      <c r="H71" s="56"/>
+      <c r="I71" s="56"/>
+      <c r="J71" s="56"/>
+      <c r="K71" s="56"/>
+      <c r="L71" s="56"/>
+      <c r="M71" s="56"/>
+      <c r="N71" s="56"/>
+      <c r="O71" s="56"/>
+      <c r="P71" s="56"/>
+      <c r="Q71" s="56"/>
+      <c r="R71" s="56"/>
+      <c r="S71" s="56"/>
+      <c r="T71" s="56"/>
+      <c r="U71" s="56"/>
+      <c r="V71" s="56"/>
+      <c r="W71" s="56"/>
+      <c r="X71" s="56"/>
+      <c r="Y71" s="56"/>
+      <c r="Z71" s="56"/>
+    </row>
+    <row r="72" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="56"/>
+      <c r="B72" s="56"/>
+      <c r="C72" s="56"/>
+      <c r="D72" s="56"/>
+      <c r="E72" s="56"/>
+      <c r="F72" s="56"/>
+      <c r="G72" s="56"/>
+      <c r="H72" s="56"/>
+      <c r="I72" s="56"/>
+      <c r="J72" s="56"/>
+      <c r="K72" s="56"/>
+      <c r="L72" s="56"/>
+      <c r="M72" s="56"/>
+      <c r="N72" s="56"/>
+      <c r="O72" s="56"/>
+      <c r="P72" s="56"/>
+      <c r="Q72" s="56"/>
+      <c r="R72" s="56"/>
+      <c r="S72" s="56"/>
+      <c r="T72" s="56"/>
+      <c r="U72" s="56"/>
+      <c r="V72" s="56"/>
+      <c r="W72" s="56"/>
+      <c r="X72" s="56"/>
+      <c r="Y72" s="56"/>
+      <c r="Z72" s="56"/>
+    </row>
+    <row r="73" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="56"/>
+      <c r="B73" s="56"/>
+      <c r="C73" s="56"/>
+      <c r="D73" s="56"/>
+      <c r="E73" s="56"/>
+      <c r="F73" s="56"/>
+      <c r="G73" s="56"/>
+      <c r="H73" s="56"/>
+      <c r="I73" s="56"/>
+      <c r="J73" s="56"/>
+      <c r="K73" s="56"/>
+      <c r="L73" s="56"/>
+      <c r="M73" s="56"/>
+      <c r="N73" s="56"/>
+      <c r="O73" s="56"/>
+      <c r="P73" s="56"/>
+      <c r="Q73" s="56"/>
+      <c r="R73" s="56"/>
+      <c r="S73" s="56"/>
+      <c r="T73" s="56"/>
+      <c r="U73" s="56"/>
+      <c r="V73" s="56"/>
+      <c r="W73" s="56"/>
+      <c r="X73" s="56"/>
+      <c r="Y73" s="56"/>
+      <c r="Z73" s="56"/>
+    </row>
+    <row r="74" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="56"/>
+      <c r="B74" s="56"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+      <c r="G74" s="56"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="56"/>
+      <c r="J74" s="56"/>
+      <c r="K74" s="56"/>
+      <c r="L74" s="56"/>
+      <c r="M74" s="56"/>
+      <c r="N74" s="56"/>
+      <c r="O74" s="56"/>
+      <c r="P74" s="56"/>
+      <c r="Q74" s="56"/>
+      <c r="R74" s="56"/>
+      <c r="S74" s="56"/>
+      <c r="T74" s="56"/>
+      <c r="U74" s="56"/>
+      <c r="V74" s="56"/>
+      <c r="W74" s="56"/>
+      <c r="X74" s="56"/>
+      <c r="Y74" s="56"/>
+      <c r="Z74" s="56"/>
+    </row>
+    <row r="75" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="56"/>
+      <c r="B75" s="56"/>
+      <c r="C75" s="56"/>
+      <c r="D75" s="56"/>
+      <c r="E75" s="56"/>
+      <c r="F75" s="56"/>
+      <c r="G75" s="56"/>
+      <c r="H75" s="56"/>
+      <c r="I75" s="56"/>
+      <c r="J75" s="56"/>
+      <c r="K75" s="56"/>
+      <c r="L75" s="56"/>
+      <c r="M75" s="56"/>
+      <c r="N75" s="56"/>
+      <c r="O75" s="56"/>
+      <c r="P75" s="56"/>
+      <c r="Q75" s="56"/>
+      <c r="R75" s="56"/>
+      <c r="S75" s="56"/>
+      <c r="T75" s="56"/>
+      <c r="U75" s="56"/>
+      <c r="V75" s="56"/>
+      <c r="W75" s="56"/>
+      <c r="X75" s="56"/>
+      <c r="Y75" s="56"/>
+      <c r="Z75" s="56"/>
+    </row>
+    <row r="76" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="56"/>
+      <c r="B76" s="56"/>
+      <c r="C76" s="56"/>
+      <c r="D76" s="56"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="56"/>
+      <c r="H76" s="56"/>
+      <c r="I76" s="56"/>
+      <c r="J76" s="56"/>
+      <c r="K76" s="56"/>
+      <c r="L76" s="56"/>
+      <c r="M76" s="56"/>
+      <c r="N76" s="56"/>
+      <c r="O76" s="56"/>
+      <c r="P76" s="56"/>
+      <c r="Q76" s="56"/>
+      <c r="R76" s="56"/>
+      <c r="S76" s="56"/>
+      <c r="T76" s="56"/>
+      <c r="U76" s="56"/>
+      <c r="V76" s="56"/>
+      <c r="W76" s="56"/>
+      <c r="X76" s="56"/>
+      <c r="Y76" s="56"/>
+      <c r="Z76" s="56"/>
+    </row>
+    <row r="77" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="56"/>
+      <c r="B77" s="56"/>
+      <c r="C77" s="56"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="56"/>
+      <c r="F77" s="56"/>
+      <c r="G77" s="56"/>
+      <c r="H77" s="56"/>
+      <c r="I77" s="56"/>
+      <c r="J77" s="56"/>
+      <c r="K77" s="56"/>
+      <c r="L77" s="56"/>
+      <c r="M77" s="56"/>
+      <c r="N77" s="56"/>
+      <c r="O77" s="56"/>
+      <c r="P77" s="56"/>
+      <c r="Q77" s="56"/>
+      <c r="R77" s="56"/>
+      <c r="S77" s="56"/>
+      <c r="T77" s="56"/>
+      <c r="U77" s="56"/>
+      <c r="V77" s="56"/>
+      <c r="W77" s="56"/>
+      <c r="X77" s="56"/>
+      <c r="Y77" s="56"/>
+      <c r="Z77" s="56"/>
+    </row>
+    <row r="78" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="56"/>
+      <c r="B78" s="56"/>
+      <c r="C78" s="56"/>
+      <c r="D78" s="56"/>
+      <c r="E78" s="56"/>
+      <c r="F78" s="56"/>
+      <c r="G78" s="56"/>
+      <c r="H78" s="56"/>
+      <c r="I78" s="56"/>
+      <c r="J78" s="56"/>
+      <c r="K78" s="56"/>
+      <c r="L78" s="56"/>
+      <c r="M78" s="56"/>
+      <c r="N78" s="56"/>
+      <c r="O78" s="56"/>
+      <c r="P78" s="56"/>
+      <c r="Q78" s="56"/>
+      <c r="R78" s="56"/>
+      <c r="S78" s="56"/>
+      <c r="T78" s="56"/>
+      <c r="U78" s="56"/>
+      <c r="V78" s="56"/>
+      <c r="W78" s="56"/>
+      <c r="X78" s="56"/>
+      <c r="Y78" s="56"/>
+      <c r="Z78" s="56"/>
+    </row>
+    <row r="79" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="56"/>
+      <c r="B79" s="56"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="56"/>
+      <c r="E79" s="56"/>
+      <c r="F79" s="56"/>
+      <c r="G79" s="56"/>
+      <c r="H79" s="56"/>
+      <c r="I79" s="56"/>
+      <c r="J79" s="56"/>
+      <c r="K79" s="56"/>
+      <c r="L79" s="56"/>
+      <c r="M79" s="56"/>
+      <c r="N79" s="56"/>
+      <c r="O79" s="56"/>
+      <c r="P79" s="56"/>
+      <c r="Q79" s="56"/>
+      <c r="R79" s="56"/>
+      <c r="S79" s="56"/>
+      <c r="T79" s="56"/>
+      <c r="U79" s="56"/>
+      <c r="V79" s="56"/>
+      <c r="W79" s="56"/>
+      <c r="X79" s="56"/>
+      <c r="Y79" s="56"/>
+      <c r="Z79" s="56"/>
+    </row>
+    <row r="80" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="56"/>
+      <c r="B80" s="56"/>
+      <c r="C80" s="56"/>
+      <c r="D80" s="56"/>
+      <c r="E80" s="56"/>
+      <c r="F80" s="56"/>
+      <c r="G80" s="56"/>
+      <c r="H80" s="56"/>
+      <c r="I80" s="56"/>
+      <c r="J80" s="56"/>
+      <c r="K80" s="56"/>
+      <c r="L80" s="56"/>
+      <c r="M80" s="56"/>
+      <c r="N80" s="56"/>
+      <c r="O80" s="56"/>
+      <c r="P80" s="56"/>
+      <c r="Q80" s="56"/>
+      <c r="R80" s="56"/>
+      <c r="S80" s="56"/>
+      <c r="T80" s="56"/>
+      <c r="U80" s="56"/>
+      <c r="V80" s="56"/>
+      <c r="W80" s="56"/>
+      <c r="X80" s="56"/>
+      <c r="Y80" s="56"/>
+      <c r="Z80" s="56"/>
+    </row>
+    <row r="81" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="56"/>
+      <c r="B81" s="56"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="56"/>
+      <c r="E81" s="56"/>
+      <c r="F81" s="56"/>
+      <c r="G81" s="56"/>
+      <c r="H81" s="56"/>
+      <c r="I81" s="56"/>
+      <c r="J81" s="56"/>
+      <c r="K81" s="56"/>
+      <c r="L81" s="56"/>
+      <c r="M81" s="56"/>
+      <c r="N81" s="56"/>
+      <c r="O81" s="56"/>
+      <c r="P81" s="56"/>
+      <c r="Q81" s="56"/>
+      <c r="R81" s="56"/>
+      <c r="S81" s="56"/>
+      <c r="T81" s="56"/>
+      <c r="U81" s="56"/>
+      <c r="V81" s="56"/>
+      <c r="W81" s="56"/>
+      <c r="X81" s="56"/>
+      <c r="Y81" s="56"/>
+      <c r="Z81" s="56"/>
+    </row>
+    <row r="82" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="56"/>
+      <c r="B82" s="56"/>
+      <c r="C82" s="56"/>
+      <c r="D82" s="56"/>
+      <c r="E82" s="56"/>
+      <c r="F82" s="56"/>
+      <c r="G82" s="56"/>
+      <c r="H82" s="56"/>
+      <c r="I82" s="56"/>
+      <c r="J82" s="56"/>
+      <c r="K82" s="56"/>
+      <c r="L82" s="56"/>
+      <c r="M82" s="56"/>
+      <c r="N82" s="56"/>
+      <c r="O82" s="56"/>
+      <c r="P82" s="56"/>
+      <c r="Q82" s="56"/>
+      <c r="R82" s="56"/>
+      <c r="S82" s="56"/>
+      <c r="T82" s="56"/>
+      <c r="U82" s="56"/>
+      <c r="V82" s="56"/>
+      <c r="W82" s="56"/>
+      <c r="X82" s="56"/>
+      <c r="Y82" s="56"/>
+      <c r="Z82" s="56"/>
+    </row>
+    <row r="83" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="56"/>
+      <c r="B83" s="56"/>
+      <c r="C83" s="56"/>
+      <c r="D83" s="56"/>
+      <c r="E83" s="56"/>
+      <c r="F83" s="56"/>
+      <c r="G83" s="56"/>
+      <c r="H83" s="56"/>
+      <c r="I83" s="56"/>
+      <c r="J83" s="56"/>
+      <c r="K83" s="56"/>
+      <c r="L83" s="56"/>
+      <c r="M83" s="56"/>
+      <c r="N83" s="56"/>
+      <c r="O83" s="56"/>
+      <c r="P83" s="56"/>
+      <c r="Q83" s="56"/>
+      <c r="R83" s="56"/>
+      <c r="S83" s="56"/>
+      <c r="T83" s="56"/>
+      <c r="U83" s="56"/>
+      <c r="V83" s="56"/>
+      <c r="W83" s="56"/>
+      <c r="X83" s="56"/>
+      <c r="Y83" s="56"/>
+      <c r="Z83" s="56"/>
+    </row>
+    <row r="84" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="56"/>
+      <c r="B84" s="56"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="56"/>
+      <c r="E84" s="56"/>
+      <c r="F84" s="56"/>
+      <c r="G84" s="56"/>
+      <c r="H84" s="56"/>
+      <c r="I84" s="56"/>
+      <c r="J84" s="56"/>
+      <c r="K84" s="56"/>
+      <c r="L84" s="56"/>
+      <c r="M84" s="56"/>
+      <c r="N84" s="56"/>
+      <c r="O84" s="56"/>
+      <c r="P84" s="56"/>
+      <c r="Q84" s="56"/>
+      <c r="R84" s="56"/>
+      <c r="S84" s="56"/>
+      <c r="T84" s="56"/>
+      <c r="U84" s="56"/>
+      <c r="V84" s="56"/>
+      <c r="W84" s="56"/>
+      <c r="X84" s="56"/>
+      <c r="Y84" s="56"/>
+      <c r="Z84" s="56"/>
+    </row>
+    <row r="85" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="56"/>
+      <c r="B85" s="56"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56"/>
+      <c r="J85" s="56"/>
+      <c r="K85" s="56"/>
+      <c r="L85" s="56"/>
+      <c r="M85" s="56"/>
+      <c r="N85" s="56"/>
+      <c r="O85" s="56"/>
+      <c r="P85" s="56"/>
+      <c r="Q85" s="56"/>
+      <c r="R85" s="56"/>
+      <c r="S85" s="56"/>
+      <c r="T85" s="56"/>
+      <c r="U85" s="56"/>
+      <c r="V85" s="56"/>
+      <c r="W85" s="56"/>
+      <c r="X85" s="56"/>
+      <c r="Y85" s="56"/>
+      <c r="Z85" s="56"/>
+    </row>
+    <row r="86" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="56"/>
+      <c r="B86" s="56"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="56"/>
+      <c r="E86" s="56"/>
+      <c r="F86" s="56"/>
+      <c r="G86" s="56"/>
+      <c r="H86" s="56"/>
+      <c r="I86" s="56"/>
+      <c r="J86" s="56"/>
+      <c r="K86" s="56"/>
+      <c r="L86" s="56"/>
+      <c r="M86" s="56"/>
+      <c r="N86" s="56"/>
+      <c r="O86" s="56"/>
+      <c r="P86" s="56"/>
+      <c r="Q86" s="56"/>
+      <c r="R86" s="56"/>
+      <c r="S86" s="56"/>
+      <c r="T86" s="56"/>
+      <c r="U86" s="56"/>
+      <c r="V86" s="56"/>
+      <c r="W86" s="56"/>
+      <c r="X86" s="56"/>
+      <c r="Y86" s="56"/>
+      <c r="Z86" s="56"/>
+    </row>
+    <row r="87" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="56"/>
+      <c r="B87" s="56"/>
+      <c r="C87" s="56"/>
+      <c r="D87" s="56"/>
+      <c r="E87" s="56"/>
+      <c r="F87" s="56"/>
+      <c r="G87" s="56"/>
+      <c r="H87" s="56"/>
+      <c r="I87" s="56"/>
+      <c r="J87" s="56"/>
+      <c r="K87" s="56"/>
+      <c r="L87" s="56"/>
+      <c r="M87" s="56"/>
+      <c r="N87" s="56"/>
+      <c r="O87" s="56"/>
+      <c r="P87" s="56"/>
+      <c r="Q87" s="56"/>
+      <c r="R87" s="56"/>
+      <c r="S87" s="56"/>
+      <c r="T87" s="56"/>
+      <c r="U87" s="56"/>
+      <c r="V87" s="56"/>
+      <c r="W87" s="56"/>
+      <c r="X87" s="56"/>
+      <c r="Y87" s="56"/>
+      <c r="Z87" s="56"/>
+    </row>
+    <row r="88" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="56"/>
+      <c r="B88" s="56"/>
+      <c r="C88" s="56"/>
+      <c r="D88" s="56"/>
+      <c r="E88" s="56"/>
+      <c r="F88" s="56"/>
+      <c r="G88" s="56"/>
+      <c r="H88" s="56"/>
+      <c r="I88" s="56"/>
+      <c r="J88" s="56"/>
+      <c r="K88" s="56"/>
+      <c r="L88" s="56"/>
+      <c r="M88" s="56"/>
+      <c r="N88" s="56"/>
+      <c r="O88" s="56"/>
+      <c r="P88" s="56"/>
+      <c r="Q88" s="56"/>
+      <c r="R88" s="56"/>
+      <c r="S88" s="56"/>
+      <c r="T88" s="56"/>
+      <c r="U88" s="56"/>
+      <c r="V88" s="56"/>
+      <c r="W88" s="56"/>
+      <c r="X88" s="56"/>
+      <c r="Y88" s="56"/>
+      <c r="Z88" s="56"/>
+    </row>
+    <row r="89" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="56"/>
+      <c r="B89" s="56"/>
+      <c r="C89" s="56"/>
+      <c r="D89" s="56"/>
+      <c r="E89" s="56"/>
+      <c r="F89" s="56"/>
+      <c r="G89" s="56"/>
+      <c r="H89" s="56"/>
+      <c r="I89" s="56"/>
+      <c r="J89" s="56"/>
+      <c r="K89" s="56"/>
+      <c r="L89" s="56"/>
+      <c r="M89" s="56"/>
+      <c r="N89" s="56"/>
+      <c r="O89" s="56"/>
+      <c r="P89" s="56"/>
+      <c r="Q89" s="56"/>
+      <c r="R89" s="56"/>
+      <c r="S89" s="56"/>
+      <c r="T89" s="56"/>
+      <c r="U89" s="56"/>
+      <c r="V89" s="56"/>
+      <c r="W89" s="56"/>
+      <c r="X89" s="56"/>
+      <c r="Y89" s="56"/>
+      <c r="Z89" s="56"/>
+    </row>
+    <row r="90" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="56"/>
+      <c r="B90" s="56"/>
+      <c r="C90" s="56"/>
+      <c r="D90" s="56"/>
+      <c r="E90" s="56"/>
+      <c r="F90" s="56"/>
+      <c r="G90" s="56"/>
+      <c r="H90" s="56"/>
+      <c r="I90" s="56"/>
+      <c r="J90" s="56"/>
+      <c r="K90" s="56"/>
+      <c r="L90" s="56"/>
+      <c r="M90" s="56"/>
+      <c r="N90" s="56"/>
+      <c r="O90" s="56"/>
+      <c r="P90" s="56"/>
+      <c r="Q90" s="56"/>
+      <c r="R90" s="56"/>
+      <c r="S90" s="56"/>
+      <c r="T90" s="56"/>
+      <c r="U90" s="56"/>
+      <c r="V90" s="56"/>
+      <c r="W90" s="56"/>
+      <c r="X90" s="56"/>
+      <c r="Y90" s="56"/>
+      <c r="Z90" s="56"/>
+    </row>
+    <row r="91" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="56"/>
+      <c r="B91" s="56"/>
+      <c r="C91" s="56"/>
+      <c r="D91" s="56"/>
+      <c r="E91" s="56"/>
+      <c r="F91" s="56"/>
+      <c r="G91" s="56"/>
+      <c r="H91" s="56"/>
+      <c r="I91" s="56"/>
+      <c r="J91" s="56"/>
+      <c r="K91" s="56"/>
+      <c r="L91" s="56"/>
+      <c r="M91" s="56"/>
+      <c r="N91" s="56"/>
+      <c r="O91" s="56"/>
+      <c r="P91" s="56"/>
+      <c r="Q91" s="56"/>
+      <c r="R91" s="56"/>
+      <c r="S91" s="56"/>
+      <c r="T91" s="56"/>
+      <c r="U91" s="56"/>
+      <c r="V91" s="56"/>
+      <c r="W91" s="56"/>
+      <c r="X91" s="56"/>
+      <c r="Y91" s="56"/>
+      <c r="Z91" s="56"/>
+    </row>
+    <row r="92" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="56"/>
+      <c r="B92" s="56"/>
+      <c r="C92" s="56"/>
+      <c r="D92" s="56"/>
+      <c r="E92" s="56"/>
+      <c r="F92" s="56"/>
+      <c r="G92" s="56"/>
+      <c r="H92" s="56"/>
+      <c r="I92" s="56"/>
+      <c r="J92" s="56"/>
+      <c r="K92" s="56"/>
+      <c r="L92" s="56"/>
+      <c r="M92" s="56"/>
+      <c r="N92" s="56"/>
+      <c r="O92" s="56"/>
+      <c r="P92" s="56"/>
+      <c r="Q92" s="56"/>
+      <c r="R92" s="56"/>
+      <c r="S92" s="56"/>
+      <c r="T92" s="56"/>
+      <c r="U92" s="56"/>
+      <c r="V92" s="56"/>
+      <c r="W92" s="56"/>
+      <c r="X92" s="56"/>
+      <c r="Y92" s="56"/>
+      <c r="Z92" s="56"/>
+    </row>
+    <row r="93" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="56"/>
+      <c r="B93" s="56"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="56"/>
+      <c r="G93" s="56"/>
+      <c r="H93" s="56"/>
+      <c r="I93" s="56"/>
+      <c r="J93" s="56"/>
+      <c r="K93" s="56"/>
+      <c r="L93" s="56"/>
+      <c r="M93" s="56"/>
+      <c r="N93" s="56"/>
+      <c r="O93" s="56"/>
+      <c r="P93" s="56"/>
+      <c r="Q93" s="56"/>
+      <c r="R93" s="56"/>
+      <c r="S93" s="56"/>
+      <c r="T93" s="56"/>
+      <c r="U93" s="56"/>
+      <c r="V93" s="56"/>
+      <c r="W93" s="56"/>
+      <c r="X93" s="56"/>
+      <c r="Y93" s="56"/>
+      <c r="Z93" s="56"/>
+    </row>
+    <row r="94" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="56"/>
+      <c r="B94" s="56"/>
+      <c r="C94" s="56"/>
+      <c r="D94" s="56"/>
+      <c r="E94" s="56"/>
+      <c r="F94" s="56"/>
+      <c r="G94" s="56"/>
+      <c r="H94" s="56"/>
+      <c r="I94" s="56"/>
+      <c r="J94" s="56"/>
+      <c r="K94" s="56"/>
+      <c r="L94" s="56"/>
+      <c r="M94" s="56"/>
+      <c r="N94" s="56"/>
+      <c r="O94" s="56"/>
+      <c r="P94" s="56"/>
+      <c r="Q94" s="56"/>
+      <c r="R94" s="56"/>
+      <c r="S94" s="56"/>
+      <c r="T94" s="56"/>
+      <c r="U94" s="56"/>
+      <c r="V94" s="56"/>
+      <c r="W94" s="56"/>
+      <c r="X94" s="56"/>
+      <c r="Y94" s="56"/>
+      <c r="Z94" s="56"/>
+    </row>
+    <row r="95" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="56"/>
+      <c r="B95" s="56"/>
+      <c r="C95" s="56"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="56"/>
+      <c r="G95" s="56"/>
+      <c r="H95" s="56"/>
+      <c r="I95" s="56"/>
+      <c r="J95" s="56"/>
+      <c r="K95" s="56"/>
+      <c r="L95" s="56"/>
+      <c r="M95" s="56"/>
+      <c r="N95" s="56"/>
+      <c r="O95" s="56"/>
+      <c r="P95" s="56"/>
+      <c r="Q95" s="56"/>
+      <c r="R95" s="56"/>
+      <c r="S95" s="56"/>
+      <c r="T95" s="56"/>
+      <c r="U95" s="56"/>
+      <c r="V95" s="56"/>
+      <c r="W95" s="56"/>
+      <c r="X95" s="56"/>
+      <c r="Y95" s="56"/>
+      <c r="Z95" s="56"/>
+    </row>
+    <row r="96" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="56"/>
+      <c r="B96" s="56"/>
+      <c r="C96" s="56"/>
+      <c r="D96" s="56"/>
+      <c r="E96" s="56"/>
+      <c r="F96" s="56"/>
+      <c r="G96" s="56"/>
+      <c r="H96" s="56"/>
+      <c r="I96" s="56"/>
+      <c r="J96" s="56"/>
+      <c r="K96" s="56"/>
+      <c r="L96" s="56"/>
+      <c r="M96" s="56"/>
+      <c r="N96" s="56"/>
+      <c r="O96" s="56"/>
+      <c r="P96" s="56"/>
+      <c r="Q96" s="56"/>
+      <c r="R96" s="56"/>
+      <c r="S96" s="56"/>
+      <c r="T96" s="56"/>
+      <c r="U96" s="56"/>
+      <c r="V96" s="56"/>
+      <c r="W96" s="56"/>
+      <c r="X96" s="56"/>
+      <c r="Y96" s="56"/>
+      <c r="Z96" s="56"/>
+    </row>
+    <row r="97" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="56"/>
+      <c r="B97" s="56"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="56"/>
+      <c r="E97" s="56"/>
+      <c r="F97" s="56"/>
+      <c r="G97" s="56"/>
+      <c r="H97" s="56"/>
+      <c r="I97" s="56"/>
+      <c r="J97" s="56"/>
+      <c r="K97" s="56"/>
+      <c r="L97" s="56"/>
+      <c r="M97" s="56"/>
+      <c r="N97" s="56"/>
+      <c r="O97" s="56"/>
+      <c r="P97" s="56"/>
+      <c r="Q97" s="56"/>
+      <c r="R97" s="56"/>
+      <c r="S97" s="56"/>
+      <c r="T97" s="56"/>
+      <c r="U97" s="56"/>
+      <c r="V97" s="56"/>
+      <c r="W97" s="56"/>
+      <c r="X97" s="56"/>
+      <c r="Y97" s="56"/>
+      <c r="Z97" s="56"/>
+    </row>
+    <row r="98" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="56"/>
+      <c r="B98" s="56"/>
+      <c r="C98" s="56"/>
+      <c r="D98" s="56"/>
+      <c r="E98" s="56"/>
+      <c r="F98" s="56"/>
+      <c r="G98" s="56"/>
+      <c r="H98" s="56"/>
+      <c r="I98" s="56"/>
+      <c r="J98" s="56"/>
+      <c r="K98" s="56"/>
+      <c r="L98" s="56"/>
+      <c r="M98" s="56"/>
+      <c r="N98" s="56"/>
+      <c r="O98" s="56"/>
+      <c r="P98" s="56"/>
+      <c r="Q98" s="56"/>
+      <c r="R98" s="56"/>
+      <c r="S98" s="56"/>
+      <c r="T98" s="56"/>
+      <c r="U98" s="56"/>
+      <c r="V98" s="56"/>
+      <c r="W98" s="56"/>
+      <c r="X98" s="56"/>
+      <c r="Y98" s="56"/>
+      <c r="Z98" s="56"/>
+    </row>
+    <row r="99" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="56"/>
+      <c r="B99" s="56"/>
+      <c r="C99" s="56"/>
+      <c r="D99" s="56"/>
+      <c r="E99" s="56"/>
+      <c r="F99" s="56"/>
+      <c r="G99" s="56"/>
+      <c r="H99" s="56"/>
+      <c r="I99" s="56"/>
+      <c r="J99" s="56"/>
+      <c r="K99" s="56"/>
+      <c r="L99" s="56"/>
+      <c r="M99" s="56"/>
+      <c r="N99" s="56"/>
+      <c r="O99" s="56"/>
+      <c r="P99" s="56"/>
+      <c r="Q99" s="56"/>
+      <c r="R99" s="56"/>
+      <c r="S99" s="56"/>
+      <c r="T99" s="56"/>
+      <c r="U99" s="56"/>
+      <c r="V99" s="56"/>
+      <c r="W99" s="56"/>
+      <c r="X99" s="56"/>
+      <c r="Y99" s="56"/>
+      <c r="Z99" s="56"/>
+    </row>
+    <row r="100" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="56"/>
+      <c r="B100" s="56"/>
+      <c r="C100" s="56"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="56"/>
+      <c r="F100" s="56"/>
+      <c r="G100" s="56"/>
+      <c r="H100" s="56"/>
+      <c r="I100" s="56"/>
+      <c r="J100" s="56"/>
+      <c r="K100" s="56"/>
+      <c r="L100" s="56"/>
+      <c r="M100" s="56"/>
+      <c r="N100" s="56"/>
+      <c r="O100" s="56"/>
+      <c r="P100" s="56"/>
+      <c r="Q100" s="56"/>
+      <c r="R100" s="56"/>
+      <c r="S100" s="56"/>
+      <c r="T100" s="56"/>
+      <c r="U100" s="56"/>
+      <c r="V100" s="56"/>
+      <c r="W100" s="56"/>
+      <c r="X100" s="56"/>
+      <c r="Y100" s="56"/>
+      <c r="Z100" s="56"/>
+    </row>
+    <row r="101" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="56"/>
+      <c r="B101" s="56"/>
+      <c r="C101" s="56"/>
+      <c r="D101" s="56"/>
+      <c r="E101" s="56"/>
+      <c r="F101" s="56"/>
+      <c r="G101" s="56"/>
+      <c r="H101" s="56"/>
+      <c r="I101" s="56"/>
+      <c r="J101" s="56"/>
+      <c r="K101" s="56"/>
+      <c r="L101" s="56"/>
+      <c r="M101" s="56"/>
+      <c r="N101" s="56"/>
+      <c r="O101" s="56"/>
+      <c r="P101" s="56"/>
+      <c r="Q101" s="56"/>
+      <c r="R101" s="56"/>
+      <c r="S101" s="56"/>
+      <c r="T101" s="56"/>
+      <c r="U101" s="56"/>
+      <c r="V101" s="56"/>
+      <c r="W101" s="56"/>
+      <c r="X101" s="56"/>
+      <c r="Y101" s="56"/>
+      <c r="Z101" s="56"/>
+    </row>
+    <row r="102" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="56"/>
+      <c r="B102" s="56"/>
+      <c r="C102" s="56"/>
+      <c r="D102" s="56"/>
+      <c r="E102" s="56"/>
+      <c r="F102" s="56"/>
+      <c r="G102" s="56"/>
+      <c r="H102" s="56"/>
+      <c r="I102" s="56"/>
+      <c r="J102" s="56"/>
+      <c r="K102" s="56"/>
+      <c r="L102" s="56"/>
+      <c r="M102" s="56"/>
+      <c r="N102" s="56"/>
+      <c r="O102" s="56"/>
+      <c r="P102" s="56"/>
+      <c r="Q102" s="56"/>
+      <c r="R102" s="56"/>
+      <c r="S102" s="56"/>
+      <c r="T102" s="56"/>
+      <c r="U102" s="56"/>
+      <c r="V102" s="56"/>
+      <c r="W102" s="56"/>
+      <c r="X102" s="56"/>
+      <c r="Y102" s="56"/>
+      <c r="Z102" s="56"/>
+    </row>
+    <row r="103" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="56"/>
+      <c r="B103" s="56"/>
+      <c r="C103" s="56"/>
+      <c r="D103" s="56"/>
+      <c r="E103" s="56"/>
+      <c r="F103" s="56"/>
+      <c r="G103" s="56"/>
+      <c r="H103" s="56"/>
+      <c r="I103" s="56"/>
+      <c r="J103" s="56"/>
+      <c r="K103" s="56"/>
+      <c r="L103" s="56"/>
+      <c r="M103" s="56"/>
+      <c r="N103" s="56"/>
+      <c r="O103" s="56"/>
+      <c r="P103" s="56"/>
+      <c r="Q103" s="56"/>
+      <c r="R103" s="56"/>
+      <c r="S103" s="56"/>
+      <c r="T103" s="56"/>
+      <c r="U103" s="56"/>
+      <c r="V103" s="56"/>
+      <c r="W103" s="56"/>
+      <c r="X103" s="56"/>
+      <c r="Y103" s="56"/>
+      <c r="Z103" s="56"/>
+    </row>
+    <row r="104" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="56"/>
+      <c r="B104" s="56"/>
+      <c r="C104" s="56"/>
+      <c r="D104" s="56"/>
+      <c r="E104" s="56"/>
+      <c r="F104" s="56"/>
+      <c r="G104" s="56"/>
+      <c r="H104" s="56"/>
+      <c r="I104" s="56"/>
+      <c r="J104" s="56"/>
+      <c r="K104" s="56"/>
+      <c r="L104" s="56"/>
+      <c r="M104" s="56"/>
+      <c r="N104" s="56"/>
+      <c r="O104" s="56"/>
+      <c r="P104" s="56"/>
+      <c r="Q104" s="56"/>
+      <c r="R104" s="56"/>
+      <c r="S104" s="56"/>
+      <c r="T104" s="56"/>
+      <c r="U104" s="56"/>
+      <c r="V104" s="56"/>
+      <c r="W104" s="56"/>
+      <c r="X104" s="56"/>
+      <c r="Y104" s="56"/>
+      <c r="Z104" s="56"/>
+    </row>
+    <row r="105" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="56"/>
+      <c r="B105" s="56"/>
+      <c r="C105" s="56"/>
+      <c r="D105" s="56"/>
+      <c r="E105" s="56"/>
+      <c r="F105" s="56"/>
+      <c r="G105" s="56"/>
+      <c r="H105" s="56"/>
+      <c r="I105" s="56"/>
+      <c r="J105" s="56"/>
+      <c r="K105" s="56"/>
+      <c r="L105" s="56"/>
+      <c r="M105" s="56"/>
+      <c r="N105" s="56"/>
+      <c r="O105" s="56"/>
+      <c r="P105" s="56"/>
+      <c r="Q105" s="56"/>
+      <c r="R105" s="56"/>
+      <c r="S105" s="56"/>
+      <c r="T105" s="56"/>
+      <c r="U105" s="56"/>
+      <c r="V105" s="56"/>
+      <c r="W105" s="56"/>
+      <c r="X105" s="56"/>
+      <c r="Y105" s="56"/>
+      <c r="Z105" s="56"/>
+    </row>
+    <row r="106" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="56"/>
+      <c r="B106" s="56"/>
+      <c r="C106" s="56"/>
+      <c r="D106" s="56"/>
+      <c r="E106" s="56"/>
+      <c r="F106" s="56"/>
+      <c r="G106" s="56"/>
+      <c r="H106" s="56"/>
+      <c r="I106" s="56"/>
+      <c r="J106" s="56"/>
+      <c r="K106" s="56"/>
+      <c r="L106" s="56"/>
+      <c r="M106" s="56"/>
+      <c r="N106" s="56"/>
+      <c r="O106" s="56"/>
+      <c r="P106" s="56"/>
+      <c r="Q106" s="56"/>
+      <c r="R106" s="56"/>
+      <c r="S106" s="56"/>
+      <c r="T106" s="56"/>
+      <c r="U106" s="56"/>
+      <c r="V106" s="56"/>
+      <c r="W106" s="56"/>
+      <c r="X106" s="56"/>
+      <c r="Y106" s="56"/>
+      <c r="Z106" s="56"/>
+    </row>
+    <row r="107" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="56"/>
+      <c r="B107" s="56"/>
+      <c r="C107" s="56"/>
+      <c r="D107" s="56"/>
+      <c r="E107" s="56"/>
+      <c r="F107" s="56"/>
+      <c r="G107" s="56"/>
+      <c r="H107" s="56"/>
+      <c r="I107" s="56"/>
+      <c r="J107" s="56"/>
+      <c r="K107" s="56"/>
+      <c r="L107" s="56"/>
+      <c r="M107" s="56"/>
+      <c r="N107" s="56"/>
+      <c r="O107" s="56"/>
+      <c r="P107" s="56"/>
+      <c r="Q107" s="56"/>
+      <c r="R107" s="56"/>
+      <c r="S107" s="56"/>
+      <c r="T107" s="56"/>
+      <c r="U107" s="56"/>
+      <c r="V107" s="56"/>
+      <c r="W107" s="56"/>
+      <c r="X107" s="56"/>
+      <c r="Y107" s="56"/>
+      <c r="Z107" s="56"/>
+    </row>
+    <row r="108" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="56"/>
+      <c r="B108" s="56"/>
+      <c r="C108" s="56"/>
+      <c r="D108" s="56"/>
+      <c r="E108" s="56"/>
+      <c r="F108" s="56"/>
+      <c r="G108" s="56"/>
+      <c r="H108" s="56"/>
+      <c r="I108" s="56"/>
+      <c r="J108" s="56"/>
+      <c r="K108" s="56"/>
+      <c r="L108" s="56"/>
+      <c r="M108" s="56"/>
+      <c r="N108" s="56"/>
+      <c r="O108" s="56"/>
+      <c r="P108" s="56"/>
+      <c r="Q108" s="56"/>
+      <c r="R108" s="56"/>
+      <c r="S108" s="56"/>
+      <c r="T108" s="56"/>
+      <c r="U108" s="56"/>
+      <c r="V108" s="56"/>
+      <c r="W108" s="56"/>
+      <c r="X108" s="56"/>
+      <c r="Y108" s="56"/>
+      <c r="Z108" s="56"/>
+    </row>
+    <row r="109" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="56"/>
+      <c r="B109" s="56"/>
+      <c r="C109" s="56"/>
+      <c r="D109" s="56"/>
+      <c r="E109" s="56"/>
+      <c r="F109" s="56"/>
+      <c r="G109" s="56"/>
+      <c r="H109" s="56"/>
+      <c r="I109" s="56"/>
+      <c r="J109" s="56"/>
+      <c r="K109" s="56"/>
+      <c r="L109" s="56"/>
+      <c r="M109" s="56"/>
+      <c r="N109" s="56"/>
+      <c r="O109" s="56"/>
+      <c r="P109" s="56"/>
+      <c r="Q109" s="56"/>
+      <c r="R109" s="56"/>
+      <c r="S109" s="56"/>
+      <c r="T109" s="56"/>
+      <c r="U109" s="56"/>
+      <c r="V109" s="56"/>
+      <c r="W109" s="56"/>
+      <c r="X109" s="56"/>
+      <c r="Y109" s="56"/>
+      <c r="Z109" s="56"/>
+    </row>
+    <row r="110" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="56"/>
+      <c r="B110" s="56"/>
+      <c r="C110" s="56"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="56"/>
+      <c r="F110" s="56"/>
+      <c r="G110" s="56"/>
+      <c r="H110" s="56"/>
+      <c r="I110" s="56"/>
+      <c r="J110" s="56"/>
+      <c r="K110" s="56"/>
+      <c r="L110" s="56"/>
+      <c r="M110" s="56"/>
+      <c r="N110" s="56"/>
+      <c r="O110" s="56"/>
+      <c r="P110" s="56"/>
+      <c r="Q110" s="56"/>
+      <c r="R110" s="56"/>
+      <c r="S110" s="56"/>
+      <c r="T110" s="56"/>
+      <c r="U110" s="56"/>
+      <c r="V110" s="56"/>
+      <c r="W110" s="56"/>
+      <c r="X110" s="56"/>
+      <c r="Y110" s="56"/>
+      <c r="Z110" s="56"/>
+    </row>
+    <row r="111" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="56"/>
+      <c r="B111" s="56"/>
+      <c r="C111" s="56"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="56"/>
+      <c r="F111" s="56"/>
+      <c r="G111" s="56"/>
+      <c r="H111" s="56"/>
+      <c r="I111" s="56"/>
+      <c r="J111" s="56"/>
+      <c r="K111" s="56"/>
+      <c r="L111" s="56"/>
+      <c r="M111" s="56"/>
+      <c r="N111" s="56"/>
+      <c r="O111" s="56"/>
+      <c r="P111" s="56"/>
+      <c r="Q111" s="56"/>
+      <c r="R111" s="56"/>
+      <c r="S111" s="56"/>
+      <c r="T111" s="56"/>
+      <c r="U111" s="56"/>
+      <c r="V111" s="56"/>
+      <c r="W111" s="56"/>
+      <c r="X111" s="56"/>
+      <c r="Y111" s="56"/>
+      <c r="Z111" s="56"/>
+    </row>
+    <row r="112" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="56"/>
+      <c r="B112" s="56"/>
+      <c r="C112" s="56"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="56"/>
+      <c r="F112" s="56"/>
+      <c r="G112" s="56"/>
+      <c r="H112" s="56"/>
+      <c r="I112" s="56"/>
+      <c r="J112" s="56"/>
+      <c r="K112" s="56"/>
+      <c r="L112" s="56"/>
+      <c r="M112" s="56"/>
+      <c r="N112" s="56"/>
+      <c r="O112" s="56"/>
+      <c r="P112" s="56"/>
+      <c r="Q112" s="56"/>
+      <c r="R112" s="56"/>
+      <c r="S112" s="56"/>
+      <c r="T112" s="56"/>
+      <c r="U112" s="56"/>
+      <c r="V112" s="56"/>
+      <c r="W112" s="56"/>
+      <c r="X112" s="56"/>
+      <c r="Y112" s="56"/>
+      <c r="Z112" s="56"/>
+    </row>
+    <row r="113" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="56"/>
+      <c r="B113" s="56"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="56"/>
+      <c r="F113" s="56"/>
+      <c r="G113" s="56"/>
+      <c r="H113" s="56"/>
+      <c r="I113" s="56"/>
+      <c r="J113" s="56"/>
+      <c r="K113" s="56"/>
+      <c r="L113" s="56"/>
+      <c r="M113" s="56"/>
+      <c r="N113" s="56"/>
+      <c r="O113" s="56"/>
+      <c r="P113" s="56"/>
+      <c r="Q113" s="56"/>
+      <c r="R113" s="56"/>
+      <c r="S113" s="56"/>
+      <c r="T113" s="56"/>
+      <c r="U113" s="56"/>
+      <c r="V113" s="56"/>
+      <c r="W113" s="56"/>
+      <c r="X113" s="56"/>
+      <c r="Y113" s="56"/>
+      <c r="Z113" s="56"/>
+    </row>
+    <row r="114" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="56"/>
+      <c r="B114" s="56"/>
+      <c r="C114" s="56"/>
+      <c r="D114" s="56"/>
+      <c r="E114" s="56"/>
+      <c r="F114" s="56"/>
+      <c r="G114" s="56"/>
+      <c r="H114" s="56"/>
+      <c r="I114" s="56"/>
+      <c r="J114" s="56"/>
+      <c r="K114" s="56"/>
+      <c r="L114" s="56"/>
+      <c r="M114" s="56"/>
+      <c r="N114" s="56"/>
+      <c r="O114" s="56"/>
+      <c r="P114" s="56"/>
+      <c r="Q114" s="56"/>
+      <c r="R114" s="56"/>
+      <c r="S114" s="56"/>
+      <c r="T114" s="56"/>
+      <c r="U114" s="56"/>
+      <c r="V114" s="56"/>
+      <c r="W114" s="56"/>
+      <c r="X114" s="56"/>
+      <c r="Y114" s="56"/>
+      <c r="Z114" s="56"/>
+    </row>
+    <row r="115" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="56"/>
+      <c r="B115" s="56"/>
+      <c r="C115" s="56"/>
+      <c r="D115" s="56"/>
+      <c r="E115" s="56"/>
+      <c r="F115" s="56"/>
+      <c r="G115" s="56"/>
+      <c r="H115" s="56"/>
+      <c r="I115" s="56"/>
+      <c r="J115" s="56"/>
+      <c r="K115" s="56"/>
+      <c r="L115" s="56"/>
+      <c r="M115" s="56"/>
+      <c r="N115" s="56"/>
+      <c r="O115" s="56"/>
+      <c r="P115" s="56"/>
+      <c r="Q115" s="56"/>
+      <c r="R115" s="56"/>
+      <c r="S115" s="56"/>
+      <c r="T115" s="56"/>
+      <c r="U115" s="56"/>
+      <c r="V115" s="56"/>
+      <c r="W115" s="56"/>
+      <c r="X115" s="56"/>
+      <c r="Y115" s="56"/>
+      <c r="Z115" s="56"/>
+    </row>
+    <row r="116" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="56"/>
+      <c r="B116" s="56"/>
+      <c r="C116" s="56"/>
+      <c r="D116" s="56"/>
+      <c r="E116" s="56"/>
+      <c r="F116" s="56"/>
+      <c r="G116" s="56"/>
+      <c r="H116" s="56"/>
+      <c r="I116" s="56"/>
+      <c r="J116" s="56"/>
+      <c r="K116" s="56"/>
+      <c r="L116" s="56"/>
+      <c r="M116" s="56"/>
+      <c r="N116" s="56"/>
+      <c r="O116" s="56"/>
+      <c r="P116" s="56"/>
+      <c r="Q116" s="56"/>
+      <c r="R116" s="56"/>
+      <c r="S116" s="56"/>
+      <c r="T116" s="56"/>
+      <c r="U116" s="56"/>
+      <c r="V116" s="56"/>
+      <c r="W116" s="56"/>
+      <c r="X116" s="56"/>
+      <c r="Y116" s="56"/>
+      <c r="Z116" s="56"/>
+    </row>
+    <row r="117" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="56"/>
+      <c r="B117" s="56"/>
+      <c r="C117" s="56"/>
+      <c r="D117" s="56"/>
+      <c r="E117" s="56"/>
+      <c r="F117" s="56"/>
+      <c r="G117" s="56"/>
+      <c r="H117" s="56"/>
+      <c r="I117" s="56"/>
+      <c r="J117" s="56"/>
+      <c r="K117" s="56"/>
+      <c r="L117" s="56"/>
+      <c r="M117" s="56"/>
+      <c r="N117" s="56"/>
+      <c r="O117" s="56"/>
+      <c r="P117" s="56"/>
+      <c r="Q117" s="56"/>
+      <c r="R117" s="56"/>
+      <c r="S117" s="56"/>
+      <c r="T117" s="56"/>
+      <c r="U117" s="56"/>
+      <c r="V117" s="56"/>
+      <c r="W117" s="56"/>
+      <c r="X117" s="56"/>
+      <c r="Y117" s="56"/>
+      <c r="Z117" s="56"/>
+    </row>
+    <row r="118" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="56"/>
+      <c r="B118" s="56"/>
+      <c r="C118" s="56"/>
+      <c r="D118" s="56"/>
+      <c r="E118" s="56"/>
+      <c r="F118" s="56"/>
+      <c r="G118" s="56"/>
+      <c r="H118" s="56"/>
+      <c r="I118" s="56"/>
+      <c r="J118" s="56"/>
+      <c r="K118" s="56"/>
+      <c r="L118" s="56"/>
+      <c r="M118" s="56"/>
+      <c r="N118" s="56"/>
+      <c r="O118" s="56"/>
+      <c r="P118" s="56"/>
+      <c r="Q118" s="56"/>
+      <c r="R118" s="56"/>
+      <c r="S118" s="56"/>
+      <c r="T118" s="56"/>
+      <c r="U118" s="56"/>
+      <c r="V118" s="56"/>
+      <c r="W118" s="56"/>
+      <c r="X118" s="56"/>
+      <c r="Y118" s="56"/>
+      <c r="Z118" s="56"/>
+    </row>
+    <row r="119" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="56"/>
+      <c r="B119" s="56"/>
+      <c r="C119" s="56"/>
+      <c r="D119" s="56"/>
+      <c r="E119" s="56"/>
+      <c r="F119" s="56"/>
+      <c r="G119" s="56"/>
+      <c r="H119" s="56"/>
+      <c r="I119" s="56"/>
+      <c r="J119" s="56"/>
+      <c r="K119" s="56"/>
+      <c r="L119" s="56"/>
+      <c r="M119" s="56"/>
+      <c r="N119" s="56"/>
+      <c r="O119" s="56"/>
+      <c r="P119" s="56"/>
+      <c r="Q119" s="56"/>
+      <c r="R119" s="56"/>
+      <c r="S119" s="56"/>
+      <c r="T119" s="56"/>
+      <c r="U119" s="56"/>
+      <c r="V119" s="56"/>
+      <c r="W119" s="56"/>
+      <c r="X119" s="56"/>
+      <c r="Y119" s="56"/>
+      <c r="Z119" s="56"/>
+    </row>
+    <row r="120" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="56"/>
+      <c r="B120" s="56"/>
+      <c r="C120" s="56"/>
+      <c r="D120" s="56"/>
+      <c r="E120" s="56"/>
+      <c r="F120" s="56"/>
+      <c r="G120" s="56"/>
+      <c r="H120" s="56"/>
+      <c r="I120" s="56"/>
+      <c r="J120" s="56"/>
+      <c r="K120" s="56"/>
+      <c r="L120" s="56"/>
+      <c r="M120" s="56"/>
+      <c r="N120" s="56"/>
+      <c r="O120" s="56"/>
+      <c r="P120" s="56"/>
+      <c r="Q120" s="56"/>
+      <c r="R120" s="56"/>
+      <c r="S120" s="56"/>
+      <c r="T120" s="56"/>
+      <c r="U120" s="56"/>
+      <c r="V120" s="56"/>
+      <c r="W120" s="56"/>
+      <c r="X120" s="56"/>
+      <c r="Y120" s="56"/>
+      <c r="Z120" s="56"/>
+    </row>
+    <row r="121" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="56"/>
+      <c r="B121" s="56"/>
+      <c r="C121" s="56"/>
+      <c r="D121" s="56"/>
+      <c r="E121" s="56"/>
+      <c r="F121" s="56"/>
+      <c r="G121" s="56"/>
+      <c r="H121" s="56"/>
+      <c r="I121" s="56"/>
+      <c r="J121" s="56"/>
+      <c r="K121" s="56"/>
+      <c r="L121" s="56"/>
+      <c r="M121" s="56"/>
+      <c r="N121" s="56"/>
+      <c r="O121" s="56"/>
+      <c r="P121" s="56"/>
+      <c r="Q121" s="56"/>
+      <c r="R121" s="56"/>
+      <c r="S121" s="56"/>
+      <c r="T121" s="56"/>
+      <c r="U121" s="56"/>
+      <c r="V121" s="56"/>
+      <c r="W121" s="56"/>
+      <c r="X121" s="56"/>
+      <c r="Y121" s="56"/>
+      <c r="Z121" s="56"/>
+    </row>
+    <row r="122" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="56"/>
+      <c r="B122" s="56"/>
+      <c r="C122" s="56"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="56"/>
+      <c r="F122" s="56"/>
+      <c r="G122" s="56"/>
+      <c r="H122" s="56"/>
+      <c r="I122" s="56"/>
+      <c r="J122" s="56"/>
+      <c r="K122" s="56"/>
+      <c r="L122" s="56"/>
+      <c r="M122" s="56"/>
+      <c r="N122" s="56"/>
+      <c r="O122" s="56"/>
+      <c r="P122" s="56"/>
+      <c r="Q122" s="56"/>
+      <c r="R122" s="56"/>
+      <c r="S122" s="56"/>
+      <c r="T122" s="56"/>
+      <c r="U122" s="56"/>
+      <c r="V122" s="56"/>
+      <c r="W122" s="56"/>
+      <c r="X122" s="56"/>
+      <c r="Y122" s="56"/>
+      <c r="Z122" s="56"/>
+    </row>
+    <row r="123" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="56"/>
+      <c r="B123" s="56"/>
+      <c r="C123" s="56"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="56"/>
+      <c r="F123" s="56"/>
+      <c r="G123" s="56"/>
+      <c r="H123" s="56"/>
+      <c r="I123" s="56"/>
+      <c r="J123" s="56"/>
+      <c r="K123" s="56"/>
+      <c r="L123" s="56"/>
+      <c r="M123" s="56"/>
+      <c r="N123" s="56"/>
+      <c r="O123" s="56"/>
+      <c r="P123" s="56"/>
+      <c r="Q123" s="56"/>
+      <c r="R123" s="56"/>
+      <c r="S123" s="56"/>
+      <c r="T123" s="56"/>
+      <c r="U123" s="56"/>
+      <c r="V123" s="56"/>
+      <c r="W123" s="56"/>
+      <c r="X123" s="56"/>
+      <c r="Y123" s="56"/>
+      <c r="Z123" s="56"/>
+    </row>
+    <row r="124" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="56"/>
+      <c r="B124" s="56"/>
+      <c r="C124" s="56"/>
+      <c r="D124" s="56"/>
+      <c r="E124" s="56"/>
+      <c r="F124" s="56"/>
+      <c r="G124" s="56"/>
+      <c r="H124" s="56"/>
+      <c r="I124" s="56"/>
+      <c r="J124" s="56"/>
+      <c r="K124" s="56"/>
+      <c r="L124" s="56"/>
+      <c r="M124" s="56"/>
+      <c r="N124" s="56"/>
+      <c r="O124" s="56"/>
+      <c r="P124" s="56"/>
+      <c r="Q124" s="56"/>
+      <c r="R124" s="56"/>
+      <c r="S124" s="56"/>
+      <c r="T124" s="56"/>
+      <c r="U124" s="56"/>
+      <c r="V124" s="56"/>
+      <c r="W124" s="56"/>
+      <c r="X124" s="56"/>
+      <c r="Y124" s="56"/>
+      <c r="Z124" s="56"/>
+    </row>
+    <row r="125" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="56"/>
+      <c r="B125" s="56"/>
+      <c r="C125" s="56"/>
+      <c r="D125" s="56"/>
+      <c r="E125" s="56"/>
+      <c r="F125" s="56"/>
+      <c r="G125" s="56"/>
+      <c r="H125" s="56"/>
+      <c r="I125" s="56"/>
+      <c r="J125" s="56"/>
+      <c r="K125" s="56"/>
+      <c r="L125" s="56"/>
+      <c r="M125" s="56"/>
+      <c r="N125" s="56"/>
+      <c r="O125" s="56"/>
+      <c r="P125" s="56"/>
+      <c r="Q125" s="56"/>
+      <c r="R125" s="56"/>
+      <c r="S125" s="56"/>
+      <c r="T125" s="56"/>
+      <c r="U125" s="56"/>
+      <c r="V125" s="56"/>
+      <c r="W125" s="56"/>
+      <c r="X125" s="56"/>
+      <c r="Y125" s="56"/>
+      <c r="Z125" s="56"/>
+    </row>
+    <row r="126" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="56"/>
+      <c r="B126" s="56"/>
+      <c r="C126" s="56"/>
+      <c r="D126" s="56"/>
+      <c r="E126" s="56"/>
+      <c r="F126" s="56"/>
+      <c r="G126" s="56"/>
+      <c r="H126" s="56"/>
+      <c r="I126" s="56"/>
+      <c r="J126" s="56"/>
+      <c r="K126" s="56"/>
+      <c r="L126" s="56"/>
+      <c r="M126" s="56"/>
+      <c r="N126" s="56"/>
+      <c r="O126" s="56"/>
+      <c r="P126" s="56"/>
+      <c r="Q126" s="56"/>
+      <c r="R126" s="56"/>
+      <c r="S126" s="56"/>
+      <c r="T126" s="56"/>
+      <c r="U126" s="56"/>
+      <c r="V126" s="56"/>
+      <c r="W126" s="56"/>
+      <c r="X126" s="56"/>
+      <c r="Y126" s="56"/>
+      <c r="Z126" s="56"/>
+    </row>
+    <row r="127" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="56"/>
+      <c r="B127" s="56"/>
+      <c r="C127" s="56"/>
+      <c r="D127" s="56"/>
+      <c r="E127" s="56"/>
+      <c r="F127" s="56"/>
+      <c r="G127" s="56"/>
+      <c r="H127" s="56"/>
+      <c r="I127" s="56"/>
+      <c r="J127" s="56"/>
+      <c r="K127" s="56"/>
+      <c r="L127" s="56"/>
+      <c r="M127" s="56"/>
+      <c r="N127" s="56"/>
+      <c r="O127" s="56"/>
+      <c r="P127" s="56"/>
+      <c r="Q127" s="56"/>
+      <c r="R127" s="56"/>
+      <c r="S127" s="56"/>
+      <c r="T127" s="56"/>
+      <c r="U127" s="56"/>
+      <c r="V127" s="56"/>
+      <c r="W127" s="56"/>
+      <c r="X127" s="56"/>
+      <c r="Y127" s="56"/>
+      <c r="Z127" s="56"/>
+    </row>
+    <row r="128" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="56"/>
+      <c r="B128" s="56"/>
+      <c r="C128" s="56"/>
+      <c r="D128" s="56"/>
+      <c r="E128" s="56"/>
+      <c r="F128" s="56"/>
+      <c r="G128" s="56"/>
+      <c r="H128" s="56"/>
+      <c r="I128" s="56"/>
+      <c r="J128" s="56"/>
+      <c r="K128" s="56"/>
+      <c r="L128" s="56"/>
+      <c r="M128" s="56"/>
+      <c r="N128" s="56"/>
+      <c r="O128" s="56"/>
+      <c r="P128" s="56"/>
+      <c r="Q128" s="56"/>
+      <c r="R128" s="56"/>
+      <c r="S128" s="56"/>
+      <c r="T128" s="56"/>
+      <c r="U128" s="56"/>
+      <c r="V128" s="56"/>
+      <c r="W128" s="56"/>
+      <c r="X128" s="56"/>
+      <c r="Y128" s="56"/>
+      <c r="Z128" s="56"/>
+    </row>
+    <row r="129" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="56"/>
+      <c r="B129" s="56"/>
+      <c r="C129" s="56"/>
+      <c r="D129" s="56"/>
+      <c r="E129" s="56"/>
+      <c r="F129" s="56"/>
+      <c r="G129" s="56"/>
+      <c r="H129" s="56"/>
+      <c r="I129" s="56"/>
+      <c r="J129" s="56"/>
+      <c r="K129" s="56"/>
+      <c r="L129" s="56"/>
+      <c r="M129" s="56"/>
+      <c r="N129" s="56"/>
+      <c r="O129" s="56"/>
+      <c r="P129" s="56"/>
+      <c r="Q129" s="56"/>
+      <c r="R129" s="56"/>
+      <c r="S129" s="56"/>
+      <c r="T129" s="56"/>
+      <c r="U129" s="56"/>
+      <c r="V129" s="56"/>
+      <c r="W129" s="56"/>
+      <c r="X129" s="56"/>
+      <c r="Y129" s="56"/>
+      <c r="Z129" s="56"/>
+    </row>
+    <row r="130" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="56"/>
+      <c r="B130" s="56"/>
+      <c r="C130" s="56"/>
+      <c r="D130" s="56"/>
+      <c r="E130" s="56"/>
+      <c r="F130" s="56"/>
+      <c r="G130" s="56"/>
+      <c r="H130" s="56"/>
+      <c r="I130" s="56"/>
+      <c r="J130" s="56"/>
+      <c r="K130" s="56"/>
+      <c r="L130" s="56"/>
+      <c r="M130" s="56"/>
+      <c r="N130" s="56"/>
+      <c r="O130" s="56"/>
+      <c r="P130" s="56"/>
+      <c r="Q130" s="56"/>
+      <c r="R130" s="56"/>
+      <c r="S130" s="56"/>
+      <c r="T130" s="56"/>
+      <c r="U130" s="56"/>
+      <c r="V130" s="56"/>
+      <c r="W130" s="56"/>
+      <c r="X130" s="56"/>
+      <c r="Y130" s="56"/>
+      <c r="Z130" s="56"/>
+    </row>
+    <row r="131" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="56"/>
+      <c r="B131" s="56"/>
+      <c r="C131" s="56"/>
+      <c r="D131" s="56"/>
+      <c r="E131" s="56"/>
+      <c r="F131" s="56"/>
+      <c r="G131" s="56"/>
+      <c r="H131" s="56"/>
+      <c r="I131" s="56"/>
+      <c r="J131" s="56"/>
+      <c r="K131" s="56"/>
+      <c r="L131" s="56"/>
+      <c r="M131" s="56"/>
+      <c r="N131" s="56"/>
+      <c r="O131" s="56"/>
+      <c r="P131" s="56"/>
+      <c r="Q131" s="56"/>
+      <c r="R131" s="56"/>
+      <c r="S131" s="56"/>
+      <c r="T131" s="56"/>
+      <c r="U131" s="56"/>
+      <c r="V131" s="56"/>
+      <c r="W131" s="56"/>
+      <c r="X131" s="56"/>
+      <c r="Y131" s="56"/>
+      <c r="Z131" s="56"/>
+    </row>
+    <row r="132" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="56"/>
+      <c r="B132" s="56"/>
+      <c r="C132" s="56"/>
+      <c r="D132" s="56"/>
+      <c r="E132" s="56"/>
+      <c r="F132" s="56"/>
+      <c r="G132" s="56"/>
+      <c r="H132" s="56"/>
+      <c r="I132" s="56"/>
+      <c r="J132" s="56"/>
+      <c r="K132" s="56"/>
+      <c r="L132" s="56"/>
+      <c r="M132" s="56"/>
+      <c r="N132" s="56"/>
+      <c r="O132" s="56"/>
+      <c r="P132" s="56"/>
+      <c r="Q132" s="56"/>
+      <c r="R132" s="56"/>
+      <c r="S132" s="56"/>
+      <c r="T132" s="56"/>
+      <c r="U132" s="56"/>
+      <c r="V132" s="56"/>
+      <c r="W132" s="56"/>
+      <c r="X132" s="56"/>
+      <c r="Y132" s="56"/>
+      <c r="Z132" s="56"/>
+    </row>
     <row r="133" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="56"/>
       <c r="B133" s="56"/>
@@ -25955,1816 +27693,12 @@
       <c r="Y924" s="56"/>
       <c r="Z924" s="56"/>
     </row>
-    <row r="925" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A925" s="56"/>
-      <c r="B925" s="56"/>
-      <c r="C925" s="56"/>
-      <c r="D925" s="56"/>
-      <c r="E925" s="56"/>
-      <c r="F925" s="56"/>
-      <c r="G925" s="56"/>
-      <c r="H925" s="56"/>
-      <c r="I925" s="56"/>
-      <c r="J925" s="56"/>
-      <c r="K925" s="56"/>
-      <c r="L925" s="56"/>
-      <c r="M925" s="56"/>
-      <c r="N925" s="56"/>
-      <c r="O925" s="56"/>
-      <c r="P925" s="56"/>
-      <c r="Q925" s="56"/>
-      <c r="R925" s="56"/>
-      <c r="S925" s="56"/>
-      <c r="T925" s="56"/>
-      <c r="U925" s="56"/>
-      <c r="V925" s="56"/>
-      <c r="W925" s="56"/>
-      <c r="X925" s="56"/>
-      <c r="Y925" s="56"/>
-      <c r="Z925" s="56"/>
-    </row>
-    <row r="926" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A926" s="56"/>
-      <c r="B926" s="56"/>
-      <c r="C926" s="56"/>
-      <c r="D926" s="56"/>
-      <c r="E926" s="56"/>
-      <c r="F926" s="56"/>
-      <c r="G926" s="56"/>
-      <c r="H926" s="56"/>
-      <c r="I926" s="56"/>
-      <c r="J926" s="56"/>
-      <c r="K926" s="56"/>
-      <c r="L926" s="56"/>
-      <c r="M926" s="56"/>
-      <c r="N926" s="56"/>
-      <c r="O926" s="56"/>
-      <c r="P926" s="56"/>
-      <c r="Q926" s="56"/>
-      <c r="R926" s="56"/>
-      <c r="S926" s="56"/>
-      <c r="T926" s="56"/>
-      <c r="U926" s="56"/>
-      <c r="V926" s="56"/>
-      <c r="W926" s="56"/>
-      <c r="X926" s="56"/>
-      <c r="Y926" s="56"/>
-      <c r="Z926" s="56"/>
-    </row>
-    <row r="927" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A927" s="56"/>
-      <c r="B927" s="56"/>
-      <c r="C927" s="56"/>
-      <c r="D927" s="56"/>
-      <c r="E927" s="56"/>
-      <c r="F927" s="56"/>
-      <c r="G927" s="56"/>
-      <c r="H927" s="56"/>
-      <c r="I927" s="56"/>
-      <c r="J927" s="56"/>
-      <c r="K927" s="56"/>
-      <c r="L927" s="56"/>
-      <c r="M927" s="56"/>
-      <c r="N927" s="56"/>
-      <c r="O927" s="56"/>
-      <c r="P927" s="56"/>
-      <c r="Q927" s="56"/>
-      <c r="R927" s="56"/>
-      <c r="S927" s="56"/>
-      <c r="T927" s="56"/>
-      <c r="U927" s="56"/>
-      <c r="V927" s="56"/>
-      <c r="W927" s="56"/>
-      <c r="X927" s="56"/>
-      <c r="Y927" s="56"/>
-      <c r="Z927" s="56"/>
-    </row>
-    <row r="928" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A928" s="56"/>
-      <c r="B928" s="56"/>
-      <c r="C928" s="56"/>
-      <c r="D928" s="56"/>
-      <c r="E928" s="56"/>
-      <c r="F928" s="56"/>
-      <c r="G928" s="56"/>
-      <c r="H928" s="56"/>
-      <c r="I928" s="56"/>
-      <c r="J928" s="56"/>
-      <c r="K928" s="56"/>
-      <c r="L928" s="56"/>
-      <c r="M928" s="56"/>
-      <c r="N928" s="56"/>
-      <c r="O928" s="56"/>
-      <c r="P928" s="56"/>
-      <c r="Q928" s="56"/>
-      <c r="R928" s="56"/>
-      <c r="S928" s="56"/>
-      <c r="T928" s="56"/>
-      <c r="U928" s="56"/>
-      <c r="V928" s="56"/>
-      <c r="W928" s="56"/>
-      <c r="X928" s="56"/>
-      <c r="Y928" s="56"/>
-      <c r="Z928" s="56"/>
-    </row>
-    <row r="929" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A929" s="56"/>
-      <c r="B929" s="56"/>
-      <c r="C929" s="56"/>
-      <c r="D929" s="56"/>
-      <c r="E929" s="56"/>
-      <c r="F929" s="56"/>
-      <c r="G929" s="56"/>
-      <c r="H929" s="56"/>
-      <c r="I929" s="56"/>
-      <c r="J929" s="56"/>
-      <c r="K929" s="56"/>
-      <c r="L929" s="56"/>
-      <c r="M929" s="56"/>
-      <c r="N929" s="56"/>
-      <c r="O929" s="56"/>
-      <c r="P929" s="56"/>
-      <c r="Q929" s="56"/>
-      <c r="R929" s="56"/>
-      <c r="S929" s="56"/>
-      <c r="T929" s="56"/>
-      <c r="U929" s="56"/>
-      <c r="V929" s="56"/>
-      <c r="W929" s="56"/>
-      <c r="X929" s="56"/>
-      <c r="Y929" s="56"/>
-      <c r="Z929" s="56"/>
-    </row>
-    <row r="930" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A930" s="56"/>
-      <c r="B930" s="56"/>
-      <c r="C930" s="56"/>
-      <c r="D930" s="56"/>
-      <c r="E930" s="56"/>
-      <c r="F930" s="56"/>
-      <c r="G930" s="56"/>
-      <c r="H930" s="56"/>
-      <c r="I930" s="56"/>
-      <c r="J930" s="56"/>
-      <c r="K930" s="56"/>
-      <c r="L930" s="56"/>
-      <c r="M930" s="56"/>
-      <c r="N930" s="56"/>
-      <c r="O930" s="56"/>
-      <c r="P930" s="56"/>
-      <c r="Q930" s="56"/>
-      <c r="R930" s="56"/>
-      <c r="S930" s="56"/>
-      <c r="T930" s="56"/>
-      <c r="U930" s="56"/>
-      <c r="V930" s="56"/>
-      <c r="W930" s="56"/>
-      <c r="X930" s="56"/>
-      <c r="Y930" s="56"/>
-      <c r="Z930" s="56"/>
-    </row>
-    <row r="931" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A931" s="56"/>
-      <c r="B931" s="56"/>
-      <c r="C931" s="56"/>
-      <c r="D931" s="56"/>
-      <c r="E931" s="56"/>
-      <c r="F931" s="56"/>
-      <c r="G931" s="56"/>
-      <c r="H931" s="56"/>
-      <c r="I931" s="56"/>
-      <c r="J931" s="56"/>
-      <c r="K931" s="56"/>
-      <c r="L931" s="56"/>
-      <c r="M931" s="56"/>
-      <c r="N931" s="56"/>
-      <c r="O931" s="56"/>
-      <c r="P931" s="56"/>
-      <c r="Q931" s="56"/>
-      <c r="R931" s="56"/>
-      <c r="S931" s="56"/>
-      <c r="T931" s="56"/>
-      <c r="U931" s="56"/>
-      <c r="V931" s="56"/>
-      <c r="W931" s="56"/>
-      <c r="X931" s="56"/>
-      <c r="Y931" s="56"/>
-      <c r="Z931" s="56"/>
-    </row>
-    <row r="932" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A932" s="56"/>
-      <c r="B932" s="56"/>
-      <c r="C932" s="56"/>
-      <c r="D932" s="56"/>
-      <c r="E932" s="56"/>
-      <c r="F932" s="56"/>
-      <c r="G932" s="56"/>
-      <c r="H932" s="56"/>
-      <c r="I932" s="56"/>
-      <c r="J932" s="56"/>
-      <c r="K932" s="56"/>
-      <c r="L932" s="56"/>
-      <c r="M932" s="56"/>
-      <c r="N932" s="56"/>
-      <c r="O932" s="56"/>
-      <c r="P932" s="56"/>
-      <c r="Q932" s="56"/>
-      <c r="R932" s="56"/>
-      <c r="S932" s="56"/>
-      <c r="T932" s="56"/>
-      <c r="U932" s="56"/>
-      <c r="V932" s="56"/>
-      <c r="W932" s="56"/>
-      <c r="X932" s="56"/>
-      <c r="Y932" s="56"/>
-      <c r="Z932" s="56"/>
-    </row>
-    <row r="933" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A933" s="56"/>
-      <c r="B933" s="56"/>
-      <c r="C933" s="56"/>
-      <c r="D933" s="56"/>
-      <c r="E933" s="56"/>
-      <c r="F933" s="56"/>
-      <c r="G933" s="56"/>
-      <c r="H933" s="56"/>
-      <c r="I933" s="56"/>
-      <c r="J933" s="56"/>
-      <c r="K933" s="56"/>
-      <c r="L933" s="56"/>
-      <c r="M933" s="56"/>
-      <c r="N933" s="56"/>
-      <c r="O933" s="56"/>
-      <c r="P933" s="56"/>
-      <c r="Q933" s="56"/>
-      <c r="R933" s="56"/>
-      <c r="S933" s="56"/>
-      <c r="T933" s="56"/>
-      <c r="U933" s="56"/>
-      <c r="V933" s="56"/>
-      <c r="W933" s="56"/>
-      <c r="X933" s="56"/>
-      <c r="Y933" s="56"/>
-      <c r="Z933" s="56"/>
-    </row>
-    <row r="934" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A934" s="56"/>
-      <c r="B934" s="56"/>
-      <c r="C934" s="56"/>
-      <c r="D934" s="56"/>
-      <c r="E934" s="56"/>
-      <c r="F934" s="56"/>
-      <c r="G934" s="56"/>
-      <c r="H934" s="56"/>
-      <c r="I934" s="56"/>
-      <c r="J934" s="56"/>
-      <c r="K934" s="56"/>
-      <c r="L934" s="56"/>
-      <c r="M934" s="56"/>
-      <c r="N934" s="56"/>
-      <c r="O934" s="56"/>
-      <c r="P934" s="56"/>
-      <c r="Q934" s="56"/>
-      <c r="R934" s="56"/>
-      <c r="S934" s="56"/>
-      <c r="T934" s="56"/>
-      <c r="U934" s="56"/>
-      <c r="V934" s="56"/>
-      <c r="W934" s="56"/>
-      <c r="X934" s="56"/>
-      <c r="Y934" s="56"/>
-      <c r="Z934" s="56"/>
-    </row>
-    <row r="935" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A935" s="56"/>
-      <c r="B935" s="56"/>
-      <c r="C935" s="56"/>
-      <c r="D935" s="56"/>
-      <c r="E935" s="56"/>
-      <c r="F935" s="56"/>
-      <c r="G935" s="56"/>
-      <c r="H935" s="56"/>
-      <c r="I935" s="56"/>
-      <c r="J935" s="56"/>
-      <c r="K935" s="56"/>
-      <c r="L935" s="56"/>
-      <c r="M935" s="56"/>
-      <c r="N935" s="56"/>
-      <c r="O935" s="56"/>
-      <c r="P935" s="56"/>
-      <c r="Q935" s="56"/>
-      <c r="R935" s="56"/>
-      <c r="S935" s="56"/>
-      <c r="T935" s="56"/>
-      <c r="U935" s="56"/>
-      <c r="V935" s="56"/>
-      <c r="W935" s="56"/>
-      <c r="X935" s="56"/>
-      <c r="Y935" s="56"/>
-      <c r="Z935" s="56"/>
-    </row>
-    <row r="936" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A936" s="56"/>
-      <c r="B936" s="56"/>
-      <c r="C936" s="56"/>
-      <c r="D936" s="56"/>
-      <c r="E936" s="56"/>
-      <c r="F936" s="56"/>
-      <c r="G936" s="56"/>
-      <c r="H936" s="56"/>
-      <c r="I936" s="56"/>
-      <c r="J936" s="56"/>
-      <c r="K936" s="56"/>
-      <c r="L936" s="56"/>
-      <c r="M936" s="56"/>
-      <c r="N936" s="56"/>
-      <c r="O936" s="56"/>
-      <c r="P936" s="56"/>
-      <c r="Q936" s="56"/>
-      <c r="R936" s="56"/>
-      <c r="S936" s="56"/>
-      <c r="T936" s="56"/>
-      <c r="U936" s="56"/>
-      <c r="V936" s="56"/>
-      <c r="W936" s="56"/>
-      <c r="X936" s="56"/>
-      <c r="Y936" s="56"/>
-      <c r="Z936" s="56"/>
-    </row>
-    <row r="937" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A937" s="56"/>
-      <c r="B937" s="56"/>
-      <c r="C937" s="56"/>
-      <c r="D937" s="56"/>
-      <c r="E937" s="56"/>
-      <c r="F937" s="56"/>
-      <c r="G937" s="56"/>
-      <c r="H937" s="56"/>
-      <c r="I937" s="56"/>
-      <c r="J937" s="56"/>
-      <c r="K937" s="56"/>
-      <c r="L937" s="56"/>
-      <c r="M937" s="56"/>
-      <c r="N937" s="56"/>
-      <c r="O937" s="56"/>
-      <c r="P937" s="56"/>
-      <c r="Q937" s="56"/>
-      <c r="R937" s="56"/>
-      <c r="S937" s="56"/>
-      <c r="T937" s="56"/>
-      <c r="U937" s="56"/>
-      <c r="V937" s="56"/>
-      <c r="W937" s="56"/>
-      <c r="X937" s="56"/>
-      <c r="Y937" s="56"/>
-      <c r="Z937" s="56"/>
-    </row>
-    <row r="938" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A938" s="56"/>
-      <c r="B938" s="56"/>
-      <c r="C938" s="56"/>
-      <c r="D938" s="56"/>
-      <c r="E938" s="56"/>
-      <c r="F938" s="56"/>
-      <c r="G938" s="56"/>
-      <c r="H938" s="56"/>
-      <c r="I938" s="56"/>
-      <c r="J938" s="56"/>
-      <c r="K938" s="56"/>
-      <c r="L938" s="56"/>
-      <c r="M938" s="56"/>
-      <c r="N938" s="56"/>
-      <c r="O938" s="56"/>
-      <c r="P938" s="56"/>
-      <c r="Q938" s="56"/>
-      <c r="R938" s="56"/>
-      <c r="S938" s="56"/>
-      <c r="T938" s="56"/>
-      <c r="U938" s="56"/>
-      <c r="V938" s="56"/>
-      <c r="W938" s="56"/>
-      <c r="X938" s="56"/>
-      <c r="Y938" s="56"/>
-      <c r="Z938" s="56"/>
-    </row>
-    <row r="939" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A939" s="56"/>
-      <c r="B939" s="56"/>
-      <c r="C939" s="56"/>
-      <c r="D939" s="56"/>
-      <c r="E939" s="56"/>
-      <c r="F939" s="56"/>
-      <c r="G939" s="56"/>
-      <c r="H939" s="56"/>
-      <c r="I939" s="56"/>
-      <c r="J939" s="56"/>
-      <c r="K939" s="56"/>
-      <c r="L939" s="56"/>
-      <c r="M939" s="56"/>
-      <c r="N939" s="56"/>
-      <c r="O939" s="56"/>
-      <c r="P939" s="56"/>
-      <c r="Q939" s="56"/>
-      <c r="R939" s="56"/>
-      <c r="S939" s="56"/>
-      <c r="T939" s="56"/>
-      <c r="U939" s="56"/>
-      <c r="V939" s="56"/>
-      <c r="W939" s="56"/>
-      <c r="X939" s="56"/>
-      <c r="Y939" s="56"/>
-      <c r="Z939" s="56"/>
-    </row>
-    <row r="940" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A940" s="56"/>
-      <c r="B940" s="56"/>
-      <c r="C940" s="56"/>
-      <c r="D940" s="56"/>
-      <c r="E940" s="56"/>
-      <c r="F940" s="56"/>
-      <c r="G940" s="56"/>
-      <c r="H940" s="56"/>
-      <c r="I940" s="56"/>
-      <c r="J940" s="56"/>
-      <c r="K940" s="56"/>
-      <c r="L940" s="56"/>
-      <c r="M940" s="56"/>
-      <c r="N940" s="56"/>
-      <c r="O940" s="56"/>
-      <c r="P940" s="56"/>
-      <c r="Q940" s="56"/>
-      <c r="R940" s="56"/>
-      <c r="S940" s="56"/>
-      <c r="T940" s="56"/>
-      <c r="U940" s="56"/>
-      <c r="V940" s="56"/>
-      <c r="W940" s="56"/>
-      <c r="X940" s="56"/>
-      <c r="Y940" s="56"/>
-      <c r="Z940" s="56"/>
-    </row>
-    <row r="941" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A941" s="56"/>
-      <c r="B941" s="56"/>
-      <c r="C941" s="56"/>
-      <c r="D941" s="56"/>
-      <c r="E941" s="56"/>
-      <c r="F941" s="56"/>
-      <c r="G941" s="56"/>
-      <c r="H941" s="56"/>
-      <c r="I941" s="56"/>
-      <c r="J941" s="56"/>
-      <c r="K941" s="56"/>
-      <c r="L941" s="56"/>
-      <c r="M941" s="56"/>
-      <c r="N941" s="56"/>
-      <c r="O941" s="56"/>
-      <c r="P941" s="56"/>
-      <c r="Q941" s="56"/>
-      <c r="R941" s="56"/>
-      <c r="S941" s="56"/>
-      <c r="T941" s="56"/>
-      <c r="U941" s="56"/>
-      <c r="V941" s="56"/>
-      <c r="W941" s="56"/>
-      <c r="X941" s="56"/>
-      <c r="Y941" s="56"/>
-      <c r="Z941" s="56"/>
-    </row>
-    <row r="942" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A942" s="56"/>
-      <c r="B942" s="56"/>
-      <c r="C942" s="56"/>
-      <c r="D942" s="56"/>
-      <c r="E942" s="56"/>
-      <c r="F942" s="56"/>
-      <c r="G942" s="56"/>
-      <c r="H942" s="56"/>
-      <c r="I942" s="56"/>
-      <c r="J942" s="56"/>
-      <c r="K942" s="56"/>
-      <c r="L942" s="56"/>
-      <c r="M942" s="56"/>
-      <c r="N942" s="56"/>
-      <c r="O942" s="56"/>
-      <c r="P942" s="56"/>
-      <c r="Q942" s="56"/>
-      <c r="R942" s="56"/>
-      <c r="S942" s="56"/>
-      <c r="T942" s="56"/>
-      <c r="U942" s="56"/>
-      <c r="V942" s="56"/>
-      <c r="W942" s="56"/>
-      <c r="X942" s="56"/>
-      <c r="Y942" s="56"/>
-      <c r="Z942" s="56"/>
-    </row>
-    <row r="943" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A943" s="56"/>
-      <c r="B943" s="56"/>
-      <c r="C943" s="56"/>
-      <c r="D943" s="56"/>
-      <c r="E943" s="56"/>
-      <c r="F943" s="56"/>
-      <c r="G943" s="56"/>
-      <c r="H943" s="56"/>
-      <c r="I943" s="56"/>
-      <c r="J943" s="56"/>
-      <c r="K943" s="56"/>
-      <c r="L943" s="56"/>
-      <c r="M943" s="56"/>
-      <c r="N943" s="56"/>
-      <c r="O943" s="56"/>
-      <c r="P943" s="56"/>
-      <c r="Q943" s="56"/>
-      <c r="R943" s="56"/>
-      <c r="S943" s="56"/>
-      <c r="T943" s="56"/>
-      <c r="U943" s="56"/>
-      <c r="V943" s="56"/>
-      <c r="W943" s="56"/>
-      <c r="X943" s="56"/>
-      <c r="Y943" s="56"/>
-      <c r="Z943" s="56"/>
-    </row>
-    <row r="944" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A944" s="56"/>
-      <c r="B944" s="56"/>
-      <c r="C944" s="56"/>
-      <c r="D944" s="56"/>
-      <c r="E944" s="56"/>
-      <c r="F944" s="56"/>
-      <c r="G944" s="56"/>
-      <c r="H944" s="56"/>
-      <c r="I944" s="56"/>
-      <c r="J944" s="56"/>
-      <c r="K944" s="56"/>
-      <c r="L944" s="56"/>
-      <c r="M944" s="56"/>
-      <c r="N944" s="56"/>
-      <c r="O944" s="56"/>
-      <c r="P944" s="56"/>
-      <c r="Q944" s="56"/>
-      <c r="R944" s="56"/>
-      <c r="S944" s="56"/>
-      <c r="T944" s="56"/>
-      <c r="U944" s="56"/>
-      <c r="V944" s="56"/>
-      <c r="W944" s="56"/>
-      <c r="X944" s="56"/>
-      <c r="Y944" s="56"/>
-      <c r="Z944" s="56"/>
-    </row>
-    <row r="945" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A945" s="56"/>
-      <c r="B945" s="56"/>
-      <c r="C945" s="56"/>
-      <c r="D945" s="56"/>
-      <c r="E945" s="56"/>
-      <c r="F945" s="56"/>
-      <c r="G945" s="56"/>
-      <c r="H945" s="56"/>
-      <c r="I945" s="56"/>
-      <c r="J945" s="56"/>
-      <c r="K945" s="56"/>
-      <c r="L945" s="56"/>
-      <c r="M945" s="56"/>
-      <c r="N945" s="56"/>
-      <c r="O945" s="56"/>
-      <c r="P945" s="56"/>
-      <c r="Q945" s="56"/>
-      <c r="R945" s="56"/>
-      <c r="S945" s="56"/>
-      <c r="T945" s="56"/>
-      <c r="U945" s="56"/>
-      <c r="V945" s="56"/>
-      <c r="W945" s="56"/>
-      <c r="X945" s="56"/>
-      <c r="Y945" s="56"/>
-      <c r="Z945" s="56"/>
-    </row>
-    <row r="946" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A946" s="56"/>
-      <c r="B946" s="56"/>
-      <c r="C946" s="56"/>
-      <c r="D946" s="56"/>
-      <c r="E946" s="56"/>
-      <c r="F946" s="56"/>
-      <c r="G946" s="56"/>
-      <c r="H946" s="56"/>
-      <c r="I946" s="56"/>
-      <c r="J946" s="56"/>
-      <c r="K946" s="56"/>
-      <c r="L946" s="56"/>
-      <c r="M946" s="56"/>
-      <c r="N946" s="56"/>
-      <c r="O946" s="56"/>
-      <c r="P946" s="56"/>
-      <c r="Q946" s="56"/>
-      <c r="R946" s="56"/>
-      <c r="S946" s="56"/>
-      <c r="T946" s="56"/>
-      <c r="U946" s="56"/>
-      <c r="V946" s="56"/>
-      <c r="W946" s="56"/>
-      <c r="X946" s="56"/>
-      <c r="Y946" s="56"/>
-      <c r="Z946" s="56"/>
-    </row>
-    <row r="947" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A947" s="56"/>
-      <c r="B947" s="56"/>
-      <c r="C947" s="56"/>
-      <c r="D947" s="56"/>
-      <c r="E947" s="56"/>
-      <c r="F947" s="56"/>
-      <c r="G947" s="56"/>
-      <c r="H947" s="56"/>
-      <c r="I947" s="56"/>
-      <c r="J947" s="56"/>
-      <c r="K947" s="56"/>
-      <c r="L947" s="56"/>
-      <c r="M947" s="56"/>
-      <c r="N947" s="56"/>
-      <c r="O947" s="56"/>
-      <c r="P947" s="56"/>
-      <c r="Q947" s="56"/>
-      <c r="R947" s="56"/>
-      <c r="S947" s="56"/>
-      <c r="T947" s="56"/>
-      <c r="U947" s="56"/>
-      <c r="V947" s="56"/>
-      <c r="W947" s="56"/>
-      <c r="X947" s="56"/>
-      <c r="Y947" s="56"/>
-      <c r="Z947" s="56"/>
-    </row>
-    <row r="948" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A948" s="56"/>
-      <c r="B948" s="56"/>
-      <c r="C948" s="56"/>
-      <c r="D948" s="56"/>
-      <c r="E948" s="56"/>
-      <c r="F948" s="56"/>
-      <c r="G948" s="56"/>
-      <c r="H948" s="56"/>
-      <c r="I948" s="56"/>
-      <c r="J948" s="56"/>
-      <c r="K948" s="56"/>
-      <c r="L948" s="56"/>
-      <c r="M948" s="56"/>
-      <c r="N948" s="56"/>
-      <c r="O948" s="56"/>
-      <c r="P948" s="56"/>
-      <c r="Q948" s="56"/>
-      <c r="R948" s="56"/>
-      <c r="S948" s="56"/>
-      <c r="T948" s="56"/>
-      <c r="U948" s="56"/>
-      <c r="V948" s="56"/>
-      <c r="W948" s="56"/>
-      <c r="X948" s="56"/>
-      <c r="Y948" s="56"/>
-      <c r="Z948" s="56"/>
-    </row>
-    <row r="949" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A949" s="56"/>
-      <c r="B949" s="56"/>
-      <c r="C949" s="56"/>
-      <c r="D949" s="56"/>
-      <c r="E949" s="56"/>
-      <c r="F949" s="56"/>
-      <c r="G949" s="56"/>
-      <c r="H949" s="56"/>
-      <c r="I949" s="56"/>
-      <c r="J949" s="56"/>
-      <c r="K949" s="56"/>
-      <c r="L949" s="56"/>
-      <c r="M949" s="56"/>
-      <c r="N949" s="56"/>
-      <c r="O949" s="56"/>
-      <c r="P949" s="56"/>
-      <c r="Q949" s="56"/>
-      <c r="R949" s="56"/>
-      <c r="S949" s="56"/>
-      <c r="T949" s="56"/>
-      <c r="U949" s="56"/>
-      <c r="V949" s="56"/>
-      <c r="W949" s="56"/>
-      <c r="X949" s="56"/>
-      <c r="Y949" s="56"/>
-      <c r="Z949" s="56"/>
-    </row>
-    <row r="950" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A950" s="56"/>
-      <c r="B950" s="56"/>
-      <c r="C950" s="56"/>
-      <c r="D950" s="56"/>
-      <c r="E950" s="56"/>
-      <c r="F950" s="56"/>
-      <c r="G950" s="56"/>
-      <c r="H950" s="56"/>
-      <c r="I950" s="56"/>
-      <c r="J950" s="56"/>
-      <c r="K950" s="56"/>
-      <c r="L950" s="56"/>
-      <c r="M950" s="56"/>
-      <c r="N950" s="56"/>
-      <c r="O950" s="56"/>
-      <c r="P950" s="56"/>
-      <c r="Q950" s="56"/>
-      <c r="R950" s="56"/>
-      <c r="S950" s="56"/>
-      <c r="T950" s="56"/>
-      <c r="U950" s="56"/>
-      <c r="V950" s="56"/>
-      <c r="W950" s="56"/>
-      <c r="X950" s="56"/>
-      <c r="Y950" s="56"/>
-      <c r="Z950" s="56"/>
-    </row>
-    <row r="951" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A951" s="56"/>
-      <c r="B951" s="56"/>
-      <c r="C951" s="56"/>
-      <c r="D951" s="56"/>
-      <c r="E951" s="56"/>
-      <c r="F951" s="56"/>
-      <c r="G951" s="56"/>
-      <c r="H951" s="56"/>
-      <c r="I951" s="56"/>
-      <c r="J951" s="56"/>
-      <c r="K951" s="56"/>
-      <c r="L951" s="56"/>
-      <c r="M951" s="56"/>
-      <c r="N951" s="56"/>
-      <c r="O951" s="56"/>
-      <c r="P951" s="56"/>
-      <c r="Q951" s="56"/>
-      <c r="R951" s="56"/>
-      <c r="S951" s="56"/>
-      <c r="T951" s="56"/>
-      <c r="U951" s="56"/>
-      <c r="V951" s="56"/>
-      <c r="W951" s="56"/>
-      <c r="X951" s="56"/>
-      <c r="Y951" s="56"/>
-      <c r="Z951" s="56"/>
-    </row>
-    <row r="952" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A952" s="56"/>
-      <c r="B952" s="56"/>
-      <c r="C952" s="56"/>
-      <c r="D952" s="56"/>
-      <c r="E952" s="56"/>
-      <c r="F952" s="56"/>
-      <c r="G952" s="56"/>
-      <c r="H952" s="56"/>
-      <c r="I952" s="56"/>
-      <c r="J952" s="56"/>
-      <c r="K952" s="56"/>
-      <c r="L952" s="56"/>
-      <c r="M952" s="56"/>
-      <c r="N952" s="56"/>
-      <c r="O952" s="56"/>
-      <c r="P952" s="56"/>
-      <c r="Q952" s="56"/>
-      <c r="R952" s="56"/>
-      <c r="S952" s="56"/>
-      <c r="T952" s="56"/>
-      <c r="U952" s="56"/>
-      <c r="V952" s="56"/>
-      <c r="W952" s="56"/>
-      <c r="X952" s="56"/>
-      <c r="Y952" s="56"/>
-      <c r="Z952" s="56"/>
-    </row>
-    <row r="953" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A953" s="56"/>
-      <c r="B953" s="56"/>
-      <c r="C953" s="56"/>
-      <c r="D953" s="56"/>
-      <c r="E953" s="56"/>
-      <c r="F953" s="56"/>
-      <c r="G953" s="56"/>
-      <c r="H953" s="56"/>
-      <c r="I953" s="56"/>
-      <c r="J953" s="56"/>
-      <c r="K953" s="56"/>
-      <c r="L953" s="56"/>
-      <c r="M953" s="56"/>
-      <c r="N953" s="56"/>
-      <c r="O953" s="56"/>
-      <c r="P953" s="56"/>
-      <c r="Q953" s="56"/>
-      <c r="R953" s="56"/>
-      <c r="S953" s="56"/>
-      <c r="T953" s="56"/>
-      <c r="U953" s="56"/>
-      <c r="V953" s="56"/>
-      <c r="W953" s="56"/>
-      <c r="X953" s="56"/>
-      <c r="Y953" s="56"/>
-      <c r="Z953" s="56"/>
-    </row>
-    <row r="954" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A954" s="56"/>
-      <c r="B954" s="56"/>
-      <c r="C954" s="56"/>
-      <c r="D954" s="56"/>
-      <c r="E954" s="56"/>
-      <c r="F954" s="56"/>
-      <c r="G954" s="56"/>
-      <c r="H954" s="56"/>
-      <c r="I954" s="56"/>
-      <c r="J954" s="56"/>
-      <c r="K954" s="56"/>
-      <c r="L954" s="56"/>
-      <c r="M954" s="56"/>
-      <c r="N954" s="56"/>
-      <c r="O954" s="56"/>
-      <c r="P954" s="56"/>
-      <c r="Q954" s="56"/>
-      <c r="R954" s="56"/>
-      <c r="S954" s="56"/>
-      <c r="T954" s="56"/>
-      <c r="U954" s="56"/>
-      <c r="V954" s="56"/>
-      <c r="W954" s="56"/>
-      <c r="X954" s="56"/>
-      <c r="Y954" s="56"/>
-      <c r="Z954" s="56"/>
-    </row>
-    <row r="955" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A955" s="56"/>
-      <c r="B955" s="56"/>
-      <c r="C955" s="56"/>
-      <c r="D955" s="56"/>
-      <c r="E955" s="56"/>
-      <c r="F955" s="56"/>
-      <c r="G955" s="56"/>
-      <c r="H955" s="56"/>
-      <c r="I955" s="56"/>
-      <c r="J955" s="56"/>
-      <c r="K955" s="56"/>
-      <c r="L955" s="56"/>
-      <c r="M955" s="56"/>
-      <c r="N955" s="56"/>
-      <c r="O955" s="56"/>
-      <c r="P955" s="56"/>
-      <c r="Q955" s="56"/>
-      <c r="R955" s="56"/>
-      <c r="S955" s="56"/>
-      <c r="T955" s="56"/>
-      <c r="U955" s="56"/>
-      <c r="V955" s="56"/>
-      <c r="W955" s="56"/>
-      <c r="X955" s="56"/>
-      <c r="Y955" s="56"/>
-      <c r="Z955" s="56"/>
-    </row>
-    <row r="956" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A956" s="56"/>
-      <c r="B956" s="56"/>
-      <c r="C956" s="56"/>
-      <c r="D956" s="56"/>
-      <c r="E956" s="56"/>
-      <c r="F956" s="56"/>
-      <c r="G956" s="56"/>
-      <c r="H956" s="56"/>
-      <c r="I956" s="56"/>
-      <c r="J956" s="56"/>
-      <c r="K956" s="56"/>
-      <c r="L956" s="56"/>
-      <c r="M956" s="56"/>
-      <c r="N956" s="56"/>
-      <c r="O956" s="56"/>
-      <c r="P956" s="56"/>
-      <c r="Q956" s="56"/>
-      <c r="R956" s="56"/>
-      <c r="S956" s="56"/>
-      <c r="T956" s="56"/>
-      <c r="U956" s="56"/>
-      <c r="V956" s="56"/>
-      <c r="W956" s="56"/>
-      <c r="X956" s="56"/>
-      <c r="Y956" s="56"/>
-      <c r="Z956" s="56"/>
-    </row>
-    <row r="957" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A957" s="56"/>
-      <c r="B957" s="56"/>
-      <c r="C957" s="56"/>
-      <c r="D957" s="56"/>
-      <c r="E957" s="56"/>
-      <c r="F957" s="56"/>
-      <c r="G957" s="56"/>
-      <c r="H957" s="56"/>
-      <c r="I957" s="56"/>
-      <c r="J957" s="56"/>
-      <c r="K957" s="56"/>
-      <c r="L957" s="56"/>
-      <c r="M957" s="56"/>
-      <c r="N957" s="56"/>
-      <c r="O957" s="56"/>
-      <c r="P957" s="56"/>
-      <c r="Q957" s="56"/>
-      <c r="R957" s="56"/>
-      <c r="S957" s="56"/>
-      <c r="T957" s="56"/>
-      <c r="U957" s="56"/>
-      <c r="V957" s="56"/>
-      <c r="W957" s="56"/>
-      <c r="X957" s="56"/>
-      <c r="Y957" s="56"/>
-      <c r="Z957" s="56"/>
-    </row>
-    <row r="958" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A958" s="56"/>
-      <c r="B958" s="56"/>
-      <c r="C958" s="56"/>
-      <c r="D958" s="56"/>
-      <c r="E958" s="56"/>
-      <c r="F958" s="56"/>
-      <c r="G958" s="56"/>
-      <c r="H958" s="56"/>
-      <c r="I958" s="56"/>
-      <c r="J958" s="56"/>
-      <c r="K958" s="56"/>
-      <c r="L958" s="56"/>
-      <c r="M958" s="56"/>
-      <c r="N958" s="56"/>
-      <c r="O958" s="56"/>
-      <c r="P958" s="56"/>
-      <c r="Q958" s="56"/>
-      <c r="R958" s="56"/>
-      <c r="S958" s="56"/>
-      <c r="T958" s="56"/>
-      <c r="U958" s="56"/>
-      <c r="V958" s="56"/>
-      <c r="W958" s="56"/>
-      <c r="X958" s="56"/>
-      <c r="Y958" s="56"/>
-      <c r="Z958" s="56"/>
-    </row>
-    <row r="959" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A959" s="56"/>
-      <c r="B959" s="56"/>
-      <c r="C959" s="56"/>
-      <c r="D959" s="56"/>
-      <c r="E959" s="56"/>
-      <c r="F959" s="56"/>
-      <c r="G959" s="56"/>
-      <c r="H959" s="56"/>
-      <c r="I959" s="56"/>
-      <c r="J959" s="56"/>
-      <c r="K959" s="56"/>
-      <c r="L959" s="56"/>
-      <c r="M959" s="56"/>
-      <c r="N959" s="56"/>
-      <c r="O959" s="56"/>
-      <c r="P959" s="56"/>
-      <c r="Q959" s="56"/>
-      <c r="R959" s="56"/>
-      <c r="S959" s="56"/>
-      <c r="T959" s="56"/>
-      <c r="U959" s="56"/>
-      <c r="V959" s="56"/>
-      <c r="W959" s="56"/>
-      <c r="X959" s="56"/>
-      <c r="Y959" s="56"/>
-      <c r="Z959" s="56"/>
-    </row>
-    <row r="960" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A960" s="56"/>
-      <c r="B960" s="56"/>
-      <c r="C960" s="56"/>
-      <c r="D960" s="56"/>
-      <c r="E960" s="56"/>
-      <c r="F960" s="56"/>
-      <c r="G960" s="56"/>
-      <c r="H960" s="56"/>
-      <c r="I960" s="56"/>
-      <c r="J960" s="56"/>
-      <c r="K960" s="56"/>
-      <c r="L960" s="56"/>
-      <c r="M960" s="56"/>
-      <c r="N960" s="56"/>
-      <c r="O960" s="56"/>
-      <c r="P960" s="56"/>
-      <c r="Q960" s="56"/>
-      <c r="R960" s="56"/>
-      <c r="S960" s="56"/>
-      <c r="T960" s="56"/>
-      <c r="U960" s="56"/>
-      <c r="V960" s="56"/>
-      <c r="W960" s="56"/>
-      <c r="X960" s="56"/>
-      <c r="Y960" s="56"/>
-      <c r="Z960" s="56"/>
-    </row>
-    <row r="961" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A961" s="56"/>
-      <c r="B961" s="56"/>
-      <c r="C961" s="56"/>
-      <c r="D961" s="56"/>
-      <c r="E961" s="56"/>
-      <c r="F961" s="56"/>
-      <c r="G961" s="56"/>
-      <c r="H961" s="56"/>
-      <c r="I961" s="56"/>
-      <c r="J961" s="56"/>
-      <c r="K961" s="56"/>
-      <c r="L961" s="56"/>
-      <c r="M961" s="56"/>
-      <c r="N961" s="56"/>
-      <c r="O961" s="56"/>
-      <c r="P961" s="56"/>
-      <c r="Q961" s="56"/>
-      <c r="R961" s="56"/>
-      <c r="S961" s="56"/>
-      <c r="T961" s="56"/>
-      <c r="U961" s="56"/>
-      <c r="V961" s="56"/>
-      <c r="W961" s="56"/>
-      <c r="X961" s="56"/>
-      <c r="Y961" s="56"/>
-      <c r="Z961" s="56"/>
-    </row>
-    <row r="962" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A962" s="56"/>
-      <c r="B962" s="56"/>
-      <c r="C962" s="56"/>
-      <c r="D962" s="56"/>
-      <c r="E962" s="56"/>
-      <c r="F962" s="56"/>
-      <c r="G962" s="56"/>
-      <c r="H962" s="56"/>
-      <c r="I962" s="56"/>
-      <c r="J962" s="56"/>
-      <c r="K962" s="56"/>
-      <c r="L962" s="56"/>
-      <c r="M962" s="56"/>
-      <c r="N962" s="56"/>
-      <c r="O962" s="56"/>
-      <c r="P962" s="56"/>
-      <c r="Q962" s="56"/>
-      <c r="R962" s="56"/>
-      <c r="S962" s="56"/>
-      <c r="T962" s="56"/>
-      <c r="U962" s="56"/>
-      <c r="V962" s="56"/>
-      <c r="W962" s="56"/>
-      <c r="X962" s="56"/>
-      <c r="Y962" s="56"/>
-      <c r="Z962" s="56"/>
-    </row>
-    <row r="963" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A963" s="56"/>
-      <c r="B963" s="56"/>
-      <c r="C963" s="56"/>
-      <c r="D963" s="56"/>
-      <c r="E963" s="56"/>
-      <c r="F963" s="56"/>
-      <c r="G963" s="56"/>
-      <c r="H963" s="56"/>
-      <c r="I963" s="56"/>
-      <c r="J963" s="56"/>
-      <c r="K963" s="56"/>
-      <c r="L963" s="56"/>
-      <c r="M963" s="56"/>
-      <c r="N963" s="56"/>
-      <c r="O963" s="56"/>
-      <c r="P963" s="56"/>
-      <c r="Q963" s="56"/>
-      <c r="R963" s="56"/>
-      <c r="S963" s="56"/>
-      <c r="T963" s="56"/>
-      <c r="U963" s="56"/>
-      <c r="V963" s="56"/>
-      <c r="W963" s="56"/>
-      <c r="X963" s="56"/>
-      <c r="Y963" s="56"/>
-      <c r="Z963" s="56"/>
-    </row>
-    <row r="964" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A964" s="56"/>
-      <c r="B964" s="56"/>
-      <c r="C964" s="56"/>
-      <c r="D964" s="56"/>
-      <c r="E964" s="56"/>
-      <c r="F964" s="56"/>
-      <c r="G964" s="56"/>
-      <c r="H964" s="56"/>
-      <c r="I964" s="56"/>
-      <c r="J964" s="56"/>
-      <c r="K964" s="56"/>
-      <c r="L964" s="56"/>
-      <c r="M964" s="56"/>
-      <c r="N964" s="56"/>
-      <c r="O964" s="56"/>
-      <c r="P964" s="56"/>
-      <c r="Q964" s="56"/>
-      <c r="R964" s="56"/>
-      <c r="S964" s="56"/>
-      <c r="T964" s="56"/>
-      <c r="U964" s="56"/>
-      <c r="V964" s="56"/>
-      <c r="W964" s="56"/>
-      <c r="X964" s="56"/>
-      <c r="Y964" s="56"/>
-      <c r="Z964" s="56"/>
-    </row>
-    <row r="965" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A965" s="56"/>
-      <c r="B965" s="56"/>
-      <c r="C965" s="56"/>
-      <c r="D965" s="56"/>
-      <c r="E965" s="56"/>
-      <c r="F965" s="56"/>
-      <c r="G965" s="56"/>
-      <c r="H965" s="56"/>
-      <c r="I965" s="56"/>
-      <c r="J965" s="56"/>
-      <c r="K965" s="56"/>
-      <c r="L965" s="56"/>
-      <c r="M965" s="56"/>
-      <c r="N965" s="56"/>
-      <c r="O965" s="56"/>
-      <c r="P965" s="56"/>
-      <c r="Q965" s="56"/>
-      <c r="R965" s="56"/>
-      <c r="S965" s="56"/>
-      <c r="T965" s="56"/>
-      <c r="U965" s="56"/>
-      <c r="V965" s="56"/>
-      <c r="W965" s="56"/>
-      <c r="X965" s="56"/>
-      <c r="Y965" s="56"/>
-      <c r="Z965" s="56"/>
-    </row>
-    <row r="966" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A966" s="56"/>
-      <c r="B966" s="56"/>
-      <c r="C966" s="56"/>
-      <c r="D966" s="56"/>
-      <c r="E966" s="56"/>
-      <c r="F966" s="56"/>
-      <c r="G966" s="56"/>
-      <c r="H966" s="56"/>
-      <c r="I966" s="56"/>
-      <c r="J966" s="56"/>
-      <c r="K966" s="56"/>
-      <c r="L966" s="56"/>
-      <c r="M966" s="56"/>
-      <c r="N966" s="56"/>
-      <c r="O966" s="56"/>
-      <c r="P966" s="56"/>
-      <c r="Q966" s="56"/>
-      <c r="R966" s="56"/>
-      <c r="S966" s="56"/>
-      <c r="T966" s="56"/>
-      <c r="U966" s="56"/>
-      <c r="V966" s="56"/>
-      <c r="W966" s="56"/>
-      <c r="X966" s="56"/>
-      <c r="Y966" s="56"/>
-      <c r="Z966" s="56"/>
-    </row>
-    <row r="967" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A967" s="56"/>
-      <c r="B967" s="56"/>
-      <c r="C967" s="56"/>
-      <c r="D967" s="56"/>
-      <c r="E967" s="56"/>
-      <c r="F967" s="56"/>
-      <c r="G967" s="56"/>
-      <c r="H967" s="56"/>
-      <c r="I967" s="56"/>
-      <c r="J967" s="56"/>
-      <c r="K967" s="56"/>
-      <c r="L967" s="56"/>
-      <c r="M967" s="56"/>
-      <c r="N967" s="56"/>
-      <c r="O967" s="56"/>
-      <c r="P967" s="56"/>
-      <c r="Q967" s="56"/>
-      <c r="R967" s="56"/>
-      <c r="S967" s="56"/>
-      <c r="T967" s="56"/>
-      <c r="U967" s="56"/>
-      <c r="V967" s="56"/>
-      <c r="W967" s="56"/>
-      <c r="X967" s="56"/>
-      <c r="Y967" s="56"/>
-      <c r="Z967" s="56"/>
-    </row>
-    <row r="968" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A968" s="56"/>
-      <c r="B968" s="56"/>
-      <c r="C968" s="56"/>
-      <c r="D968" s="56"/>
-      <c r="E968" s="56"/>
-      <c r="F968" s="56"/>
-      <c r="G968" s="56"/>
-      <c r="H968" s="56"/>
-      <c r="I968" s="56"/>
-      <c r="J968" s="56"/>
-      <c r="K968" s="56"/>
-      <c r="L968" s="56"/>
-      <c r="M968" s="56"/>
-      <c r="N968" s="56"/>
-      <c r="O968" s="56"/>
-      <c r="P968" s="56"/>
-      <c r="Q968" s="56"/>
-      <c r="R968" s="56"/>
-      <c r="S968" s="56"/>
-      <c r="T968" s="56"/>
-      <c r="U968" s="56"/>
-      <c r="V968" s="56"/>
-      <c r="W968" s="56"/>
-      <c r="X968" s="56"/>
-      <c r="Y968" s="56"/>
-      <c r="Z968" s="56"/>
-    </row>
-    <row r="969" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A969" s="56"/>
-      <c r="B969" s="56"/>
-      <c r="C969" s="56"/>
-      <c r="D969" s="56"/>
-      <c r="E969" s="56"/>
-      <c r="F969" s="56"/>
-      <c r="G969" s="56"/>
-      <c r="H969" s="56"/>
-      <c r="I969" s="56"/>
-      <c r="J969" s="56"/>
-      <c r="K969" s="56"/>
-      <c r="L969" s="56"/>
-      <c r="M969" s="56"/>
-      <c r="N969" s="56"/>
-      <c r="O969" s="56"/>
-      <c r="P969" s="56"/>
-      <c r="Q969" s="56"/>
-      <c r="R969" s="56"/>
-      <c r="S969" s="56"/>
-      <c r="T969" s="56"/>
-      <c r="U969" s="56"/>
-      <c r="V969" s="56"/>
-      <c r="W969" s="56"/>
-      <c r="X969" s="56"/>
-      <c r="Y969" s="56"/>
-      <c r="Z969" s="56"/>
-    </row>
-    <row r="970" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A970" s="56"/>
-      <c r="B970" s="56"/>
-      <c r="C970" s="56"/>
-      <c r="D970" s="56"/>
-      <c r="E970" s="56"/>
-      <c r="F970" s="56"/>
-      <c r="G970" s="56"/>
-      <c r="H970" s="56"/>
-      <c r="I970" s="56"/>
-      <c r="J970" s="56"/>
-      <c r="K970" s="56"/>
-      <c r="L970" s="56"/>
-      <c r="M970" s="56"/>
-      <c r="N970" s="56"/>
-      <c r="O970" s="56"/>
-      <c r="P970" s="56"/>
-      <c r="Q970" s="56"/>
-      <c r="R970" s="56"/>
-      <c r="S970" s="56"/>
-      <c r="T970" s="56"/>
-      <c r="U970" s="56"/>
-      <c r="V970" s="56"/>
-      <c r="W970" s="56"/>
-      <c r="X970" s="56"/>
-      <c r="Y970" s="56"/>
-      <c r="Z970" s="56"/>
-    </row>
-    <row r="971" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A971" s="56"/>
-      <c r="B971" s="56"/>
-      <c r="C971" s="56"/>
-      <c r="D971" s="56"/>
-      <c r="E971" s="56"/>
-      <c r="F971" s="56"/>
-      <c r="G971" s="56"/>
-      <c r="H971" s="56"/>
-      <c r="I971" s="56"/>
-      <c r="J971" s="56"/>
-      <c r="K971" s="56"/>
-      <c r="L971" s="56"/>
-      <c r="M971" s="56"/>
-      <c r="N971" s="56"/>
-      <c r="O971" s="56"/>
-      <c r="P971" s="56"/>
-      <c r="Q971" s="56"/>
-      <c r="R971" s="56"/>
-      <c r="S971" s="56"/>
-      <c r="T971" s="56"/>
-      <c r="U971" s="56"/>
-      <c r="V971" s="56"/>
-      <c r="W971" s="56"/>
-      <c r="X971" s="56"/>
-      <c r="Y971" s="56"/>
-      <c r="Z971" s="56"/>
-    </row>
-    <row r="972" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A972" s="56"/>
-      <c r="B972" s="56"/>
-      <c r="C972" s="56"/>
-      <c r="D972" s="56"/>
-      <c r="E972" s="56"/>
-      <c r="F972" s="56"/>
-      <c r="G972" s="56"/>
-      <c r="H972" s="56"/>
-      <c r="I972" s="56"/>
-      <c r="J972" s="56"/>
-      <c r="K972" s="56"/>
-      <c r="L972" s="56"/>
-      <c r="M972" s="56"/>
-      <c r="N972" s="56"/>
-      <c r="O972" s="56"/>
-      <c r="P972" s="56"/>
-      <c r="Q972" s="56"/>
-      <c r="R972" s="56"/>
-      <c r="S972" s="56"/>
-      <c r="T972" s="56"/>
-      <c r="U972" s="56"/>
-      <c r="V972" s="56"/>
-      <c r="W972" s="56"/>
-      <c r="X972" s="56"/>
-      <c r="Y972" s="56"/>
-      <c r="Z972" s="56"/>
-    </row>
-    <row r="973" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A973" s="56"/>
-      <c r="B973" s="56"/>
-      <c r="C973" s="56"/>
-      <c r="D973" s="56"/>
-      <c r="E973" s="56"/>
-      <c r="F973" s="56"/>
-      <c r="G973" s="56"/>
-      <c r="H973" s="56"/>
-      <c r="I973" s="56"/>
-      <c r="J973" s="56"/>
-      <c r="K973" s="56"/>
-      <c r="L973" s="56"/>
-      <c r="M973" s="56"/>
-      <c r="N973" s="56"/>
-      <c r="O973" s="56"/>
-      <c r="P973" s="56"/>
-      <c r="Q973" s="56"/>
-      <c r="R973" s="56"/>
-      <c r="S973" s="56"/>
-      <c r="T973" s="56"/>
-      <c r="U973" s="56"/>
-      <c r="V973" s="56"/>
-      <c r="W973" s="56"/>
-      <c r="X973" s="56"/>
-      <c r="Y973" s="56"/>
-      <c r="Z973" s="56"/>
-    </row>
-    <row r="974" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A974" s="56"/>
-      <c r="B974" s="56"/>
-      <c r="C974" s="56"/>
-      <c r="D974" s="56"/>
-      <c r="E974" s="56"/>
-      <c r="F974" s="56"/>
-      <c r="G974" s="56"/>
-      <c r="H974" s="56"/>
-      <c r="I974" s="56"/>
-      <c r="J974" s="56"/>
-      <c r="K974" s="56"/>
-      <c r="L974" s="56"/>
-      <c r="M974" s="56"/>
-      <c r="N974" s="56"/>
-      <c r="O974" s="56"/>
-      <c r="P974" s="56"/>
-      <c r="Q974" s="56"/>
-      <c r="R974" s="56"/>
-      <c r="S974" s="56"/>
-      <c r="T974" s="56"/>
-      <c r="U974" s="56"/>
-      <c r="V974" s="56"/>
-      <c r="W974" s="56"/>
-      <c r="X974" s="56"/>
-      <c r="Y974" s="56"/>
-      <c r="Z974" s="56"/>
-    </row>
-    <row r="975" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A975" s="56"/>
-      <c r="B975" s="56"/>
-      <c r="C975" s="56"/>
-      <c r="D975" s="56"/>
-      <c r="E975" s="56"/>
-      <c r="F975" s="56"/>
-      <c r="G975" s="56"/>
-      <c r="H975" s="56"/>
-      <c r="I975" s="56"/>
-      <c r="J975" s="56"/>
-      <c r="K975" s="56"/>
-      <c r="L975" s="56"/>
-      <c r="M975" s="56"/>
-      <c r="N975" s="56"/>
-      <c r="O975" s="56"/>
-      <c r="P975" s="56"/>
-      <c r="Q975" s="56"/>
-      <c r="R975" s="56"/>
-      <c r="S975" s="56"/>
-      <c r="T975" s="56"/>
-      <c r="U975" s="56"/>
-      <c r="V975" s="56"/>
-      <c r="W975" s="56"/>
-      <c r="X975" s="56"/>
-      <c r="Y975" s="56"/>
-      <c r="Z975" s="56"/>
-    </row>
-    <row r="976" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A976" s="56"/>
-      <c r="B976" s="56"/>
-      <c r="C976" s="56"/>
-      <c r="D976" s="56"/>
-      <c r="E976" s="56"/>
-      <c r="F976" s="56"/>
-      <c r="G976" s="56"/>
-      <c r="H976" s="56"/>
-      <c r="I976" s="56"/>
-      <c r="J976" s="56"/>
-      <c r="K976" s="56"/>
-      <c r="L976" s="56"/>
-      <c r="M976" s="56"/>
-      <c r="N976" s="56"/>
-      <c r="O976" s="56"/>
-      <c r="P976" s="56"/>
-      <c r="Q976" s="56"/>
-      <c r="R976" s="56"/>
-      <c r="S976" s="56"/>
-      <c r="T976" s="56"/>
-      <c r="U976" s="56"/>
-      <c r="V976" s="56"/>
-      <c r="W976" s="56"/>
-      <c r="X976" s="56"/>
-      <c r="Y976" s="56"/>
-      <c r="Z976" s="56"/>
-    </row>
-    <row r="977" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A977" s="56"/>
-      <c r="B977" s="56"/>
-      <c r="C977" s="56"/>
-      <c r="D977" s="56"/>
-      <c r="E977" s="56"/>
-      <c r="F977" s="56"/>
-      <c r="G977" s="56"/>
-      <c r="H977" s="56"/>
-      <c r="I977" s="56"/>
-      <c r="J977" s="56"/>
-      <c r="K977" s="56"/>
-      <c r="L977" s="56"/>
-      <c r="M977" s="56"/>
-      <c r="N977" s="56"/>
-      <c r="O977" s="56"/>
-      <c r="P977" s="56"/>
-      <c r="Q977" s="56"/>
-      <c r="R977" s="56"/>
-      <c r="S977" s="56"/>
-      <c r="T977" s="56"/>
-      <c r="U977" s="56"/>
-      <c r="V977" s="56"/>
-      <c r="W977" s="56"/>
-      <c r="X977" s="56"/>
-      <c r="Y977" s="56"/>
-      <c r="Z977" s="56"/>
-    </row>
-    <row r="978" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A978" s="56"/>
-      <c r="B978" s="56"/>
-      <c r="C978" s="56"/>
-      <c r="D978" s="56"/>
-      <c r="E978" s="56"/>
-      <c r="F978" s="56"/>
-      <c r="G978" s="56"/>
-      <c r="H978" s="56"/>
-      <c r="I978" s="56"/>
-      <c r="J978" s="56"/>
-      <c r="K978" s="56"/>
-      <c r="L978" s="56"/>
-      <c r="M978" s="56"/>
-      <c r="N978" s="56"/>
-      <c r="O978" s="56"/>
-      <c r="P978" s="56"/>
-      <c r="Q978" s="56"/>
-      <c r="R978" s="56"/>
-      <c r="S978" s="56"/>
-      <c r="T978" s="56"/>
-      <c r="U978" s="56"/>
-      <c r="V978" s="56"/>
-      <c r="W978" s="56"/>
-      <c r="X978" s="56"/>
-      <c r="Y978" s="56"/>
-      <c r="Z978" s="56"/>
-    </row>
-    <row r="979" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A979" s="56"/>
-      <c r="B979" s="56"/>
-      <c r="C979" s="56"/>
-      <c r="D979" s="56"/>
-      <c r="E979" s="56"/>
-      <c r="F979" s="56"/>
-      <c r="G979" s="56"/>
-      <c r="H979" s="56"/>
-      <c r="I979" s="56"/>
-      <c r="J979" s="56"/>
-      <c r="K979" s="56"/>
-      <c r="L979" s="56"/>
-      <c r="M979" s="56"/>
-      <c r="N979" s="56"/>
-      <c r="O979" s="56"/>
-      <c r="P979" s="56"/>
-      <c r="Q979" s="56"/>
-      <c r="R979" s="56"/>
-      <c r="S979" s="56"/>
-      <c r="T979" s="56"/>
-      <c r="U979" s="56"/>
-      <c r="V979" s="56"/>
-      <c r="W979" s="56"/>
-      <c r="X979" s="56"/>
-      <c r="Y979" s="56"/>
-      <c r="Z979" s="56"/>
-    </row>
-    <row r="980" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A980" s="56"/>
-      <c r="B980" s="56"/>
-      <c r="C980" s="56"/>
-      <c r="D980" s="56"/>
-      <c r="E980" s="56"/>
-      <c r="F980" s="56"/>
-      <c r="G980" s="56"/>
-      <c r="H980" s="56"/>
-      <c r="I980" s="56"/>
-      <c r="J980" s="56"/>
-      <c r="K980" s="56"/>
-      <c r="L980" s="56"/>
-      <c r="M980" s="56"/>
-      <c r="N980" s="56"/>
-      <c r="O980" s="56"/>
-      <c r="P980" s="56"/>
-      <c r="Q980" s="56"/>
-      <c r="R980" s="56"/>
-      <c r="S980" s="56"/>
-      <c r="T980" s="56"/>
-      <c r="U980" s="56"/>
-      <c r="V980" s="56"/>
-      <c r="W980" s="56"/>
-      <c r="X980" s="56"/>
-      <c r="Y980" s="56"/>
-      <c r="Z980" s="56"/>
-    </row>
-    <row r="981" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A981" s="56"/>
-      <c r="B981" s="56"/>
-      <c r="C981" s="56"/>
-      <c r="D981" s="56"/>
-      <c r="E981" s="56"/>
-      <c r="F981" s="56"/>
-      <c r="G981" s="56"/>
-      <c r="H981" s="56"/>
-      <c r="I981" s="56"/>
-      <c r="J981" s="56"/>
-      <c r="K981" s="56"/>
-      <c r="L981" s="56"/>
-      <c r="M981" s="56"/>
-      <c r="N981" s="56"/>
-      <c r="O981" s="56"/>
-      <c r="P981" s="56"/>
-      <c r="Q981" s="56"/>
-      <c r="R981" s="56"/>
-      <c r="S981" s="56"/>
-      <c r="T981" s="56"/>
-      <c r="U981" s="56"/>
-      <c r="V981" s="56"/>
-      <c r="W981" s="56"/>
-      <c r="X981" s="56"/>
-      <c r="Y981" s="56"/>
-      <c r="Z981" s="56"/>
-    </row>
-    <row r="982" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A982" s="56"/>
-      <c r="B982" s="56"/>
-      <c r="C982" s="56"/>
-      <c r="D982" s="56"/>
-      <c r="E982" s="56"/>
-      <c r="F982" s="56"/>
-      <c r="G982" s="56"/>
-      <c r="H982" s="56"/>
-      <c r="I982" s="56"/>
-      <c r="J982" s="56"/>
-      <c r="K982" s="56"/>
-      <c r="L982" s="56"/>
-      <c r="M982" s="56"/>
-      <c r="N982" s="56"/>
-      <c r="O982" s="56"/>
-      <c r="P982" s="56"/>
-      <c r="Q982" s="56"/>
-      <c r="R982" s="56"/>
-      <c r="S982" s="56"/>
-      <c r="T982" s="56"/>
-      <c r="U982" s="56"/>
-      <c r="V982" s="56"/>
-      <c r="W982" s="56"/>
-      <c r="X982" s="56"/>
-      <c r="Y982" s="56"/>
-      <c r="Z982" s="56"/>
-    </row>
-    <row r="983" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A983" s="56"/>
-      <c r="B983" s="56"/>
-      <c r="C983" s="56"/>
-      <c r="D983" s="56"/>
-      <c r="E983" s="56"/>
-      <c r="F983" s="56"/>
-      <c r="G983" s="56"/>
-      <c r="H983" s="56"/>
-      <c r="I983" s="56"/>
-      <c r="J983" s="56"/>
-      <c r="K983" s="56"/>
-      <c r="L983" s="56"/>
-      <c r="M983" s="56"/>
-      <c r="N983" s="56"/>
-      <c r="O983" s="56"/>
-      <c r="P983" s="56"/>
-      <c r="Q983" s="56"/>
-      <c r="R983" s="56"/>
-      <c r="S983" s="56"/>
-      <c r="T983" s="56"/>
-      <c r="U983" s="56"/>
-      <c r="V983" s="56"/>
-      <c r="W983" s="56"/>
-      <c r="X983" s="56"/>
-      <c r="Y983" s="56"/>
-      <c r="Z983" s="56"/>
-    </row>
-    <row r="984" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A984" s="56"/>
-      <c r="B984" s="56"/>
-      <c r="C984" s="56"/>
-      <c r="D984" s="56"/>
-      <c r="E984" s="56"/>
-      <c r="F984" s="56"/>
-      <c r="G984" s="56"/>
-      <c r="H984" s="56"/>
-      <c r="I984" s="56"/>
-      <c r="J984" s="56"/>
-      <c r="K984" s="56"/>
-      <c r="L984" s="56"/>
-      <c r="M984" s="56"/>
-      <c r="N984" s="56"/>
-      <c r="O984" s="56"/>
-      <c r="P984" s="56"/>
-      <c r="Q984" s="56"/>
-      <c r="R984" s="56"/>
-      <c r="S984" s="56"/>
-      <c r="T984" s="56"/>
-      <c r="U984" s="56"/>
-      <c r="V984" s="56"/>
-      <c r="W984" s="56"/>
-      <c r="X984" s="56"/>
-      <c r="Y984" s="56"/>
-      <c r="Z984" s="56"/>
-    </row>
-    <row r="985" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A985" s="56"/>
-      <c r="B985" s="56"/>
-      <c r="C985" s="56"/>
-      <c r="D985" s="56"/>
-      <c r="E985" s="56"/>
-      <c r="F985" s="56"/>
-      <c r="G985" s="56"/>
-      <c r="H985" s="56"/>
-      <c r="I985" s="56"/>
-      <c r="J985" s="56"/>
-      <c r="K985" s="56"/>
-      <c r="L985" s="56"/>
-      <c r="M985" s="56"/>
-      <c r="N985" s="56"/>
-      <c r="O985" s="56"/>
-      <c r="P985" s="56"/>
-      <c r="Q985" s="56"/>
-      <c r="R985" s="56"/>
-      <c r="S985" s="56"/>
-      <c r="T985" s="56"/>
-      <c r="U985" s="56"/>
-      <c r="V985" s="56"/>
-      <c r="W985" s="56"/>
-      <c r="X985" s="56"/>
-      <c r="Y985" s="56"/>
-      <c r="Z985" s="56"/>
-    </row>
-    <row r="986" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A986" s="56"/>
-      <c r="B986" s="56"/>
-      <c r="C986" s="56"/>
-      <c r="D986" s="56"/>
-      <c r="E986" s="56"/>
-      <c r="F986" s="56"/>
-      <c r="G986" s="56"/>
-      <c r="H986" s="56"/>
-      <c r="I986" s="56"/>
-      <c r="J986" s="56"/>
-      <c r="K986" s="56"/>
-      <c r="L986" s="56"/>
-      <c r="M986" s="56"/>
-      <c r="N986" s="56"/>
-      <c r="O986" s="56"/>
-      <c r="P986" s="56"/>
-      <c r="Q986" s="56"/>
-      <c r="R986" s="56"/>
-      <c r="S986" s="56"/>
-      <c r="T986" s="56"/>
-      <c r="U986" s="56"/>
-      <c r="V986" s="56"/>
-      <c r="W986" s="56"/>
-      <c r="X986" s="56"/>
-      <c r="Y986" s="56"/>
-      <c r="Z986" s="56"/>
-    </row>
-    <row r="987" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A987" s="56"/>
-      <c r="B987" s="56"/>
-      <c r="C987" s="56"/>
-      <c r="D987" s="56"/>
-      <c r="E987" s="56"/>
-      <c r="F987" s="56"/>
-      <c r="G987" s="56"/>
-      <c r="H987" s="56"/>
-      <c r="I987" s="56"/>
-      <c r="J987" s="56"/>
-      <c r="K987" s="56"/>
-      <c r="L987" s="56"/>
-      <c r="M987" s="56"/>
-      <c r="N987" s="56"/>
-      <c r="O987" s="56"/>
-      <c r="P987" s="56"/>
-      <c r="Q987" s="56"/>
-      <c r="R987" s="56"/>
-      <c r="S987" s="56"/>
-      <c r="T987" s="56"/>
-      <c r="U987" s="56"/>
-      <c r="V987" s="56"/>
-      <c r="W987" s="56"/>
-      <c r="X987" s="56"/>
-      <c r="Y987" s="56"/>
-      <c r="Z987" s="56"/>
-    </row>
-    <row r="988" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A988" s="56"/>
-      <c r="B988" s="56"/>
-      <c r="C988" s="56"/>
-      <c r="D988" s="56"/>
-      <c r="E988" s="56"/>
-      <c r="F988" s="56"/>
-      <c r="G988" s="56"/>
-      <c r="H988" s="56"/>
-      <c r="I988" s="56"/>
-      <c r="J988" s="56"/>
-      <c r="K988" s="56"/>
-      <c r="L988" s="56"/>
-      <c r="M988" s="56"/>
-      <c r="N988" s="56"/>
-      <c r="O988" s="56"/>
-      <c r="P988" s="56"/>
-      <c r="Q988" s="56"/>
-      <c r="R988" s="56"/>
-      <c r="S988" s="56"/>
-      <c r="T988" s="56"/>
-      <c r="U988" s="56"/>
-      <c r="V988" s="56"/>
-      <c r="W988" s="56"/>
-      <c r="X988" s="56"/>
-      <c r="Y988" s="56"/>
-      <c r="Z988" s="56"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="14">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4589180C-9127-844B-B3AB-26B52318E969}">
-          <x14:formula1>
-            <xm:f>Lists!$G$2:$G$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>B23 B28 B39 B44 B55 B60</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{C159AD43-387F-8A44-88E8-16412071B24C}">
-          <x14:formula1>
-            <xm:f>Lists!$C$2:$C$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>B20 B36 B52</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="20">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9269EC84-DF31-1A4B-A990-FD99E0DF6A37}">
           <x14:formula1>
             <xm:f>Lists!$F$2:$F$10</xm:f>
@@ -27779,9 +27713,9 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{88820E64-3962-FE4A-91C9-191EA451FB88}">
           <x14:formula1>
-            <xm:f>Lists!$H$2:$H$8</xm:f>
+            <xm:f>Lists!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B39 B23 B17 B52 B55 B49 B33 B36</xm:sqref>
+          <xm:sqref>B39 B44 B55 B60</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{4DE4111E-DA5E-784E-9D6F-05103F7D2493}">
           <x14:formula1>
@@ -27811,31 +27745,79 @@
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$6</xm:f>
           </x14:formula1>
-          <xm:sqref>B25 B30 B57 B41 B46 B62 B37 B53 B21</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{970994F8-0C5A-954C-8A5B-082DB9E55E96}">
-          <x14:formula1>
-            <xm:f>Lists!$B$2:$B$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>B50 B18 B34</xm:sqref>
+          <xm:sqref>B25 B30 B41 B46 B37 B21 B57 B62 B53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{209ABDC6-7A4F-1043-BD31-F5067EDD9592}">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$22</xm:f>
           </x14:formula1>
-          <xm:sqref>B18:B20 B34:B36 B50:B52</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E36366AC-D6BD-7D4B-94C1-F87AEC17F439}">
-          <x14:formula1>
-            <xm:f>Lists!$B$2:$B$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>B50 B34</xm:sqref>
+          <xm:sqref>B19 B35 B51</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{8B68413C-BA2E-3E4F-BCCD-63E54D16131E}">
           <x14:formula1>
             <xm:f>Lists!$M$2:$M$3</xm:f>
           </x14:formula1>
           <xm:sqref>B6</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{970994F8-0C5A-954C-8A5B-082DB9E55E96}">
+          <x14:formula1>
+            <xm:f>Lists!$B$2:$B$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>B50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E36366AC-D6BD-7D4B-94C1-F87AEC17F439}">
+          <x14:formula1>
+            <xm:f>Lists!$B$3:$B$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>B34 B50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{C159AD43-387F-8A44-88E8-16412071B24C}">
+          <x14:formula1>
+            <xm:f>Lists!$C$2:$C$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>B52</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4589180C-9127-844B-B3AB-26B52318E969}">
+          <x14:formula1>
+            <xm:f>Lists!$G$3:$G$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>B39 B55</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8F92160A-7435-3B42-84F3-7B849CE421F0}">
+          <x14:formula1>
+            <xm:f>Lists!$H$2:$H$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>B33 B17 B49</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF158337-349C-AE45-9DC7-81D1DD942C51}">
+          <x14:formula1>
+            <xm:f>Lists!$C$2:$C$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>B36 B20 B52</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F9DEF641-EE3D-B047-8D16-CAC81DB4BCBD}">
+          <x14:formula1>
+            <xm:f>Lists!$B$2:$B$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>B18 B34 B50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BA29BD18-C8F7-C346-9651-7A8BCFA8C632}">
+          <x14:formula1>
+            <xm:f>Lists!$G$2:$G$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>B23 B28</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{8127A0B6-250B-4348-B13B-ADE932112953}">
+          <x14:formula1>
+            <xm:f>Lists!$B$2:$B$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>B18 B34</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{1F1C9D61-2705-6E46-9905-EC33BDC0596D}">
+          <x14:formula1>
+            <xm:f>Lists!$C$2:$C$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>B20 B36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -27910,22 +27892,22 @@
         <v>47</v>
       </c>
       <c r="B2" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="G2" s="42" t="s">
         <v>163</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>167</v>
       </c>
       <c r="H2" s="41"/>
       <c r="I2" s="42"/>
@@ -27939,22 +27921,22 @@
         <v>48</v>
       </c>
       <c r="B3" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="F3" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="G3" s="41" t="s">
         <v>169</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>173</v>
       </c>
       <c r="H3" s="42"/>
       <c r="I3" s="41"/>
@@ -27968,22 +27950,22 @@
         <v>49</v>
       </c>
       <c r="B4" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="F4" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="G4" s="42" t="s">
         <v>175</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="G4" s="42" t="s">
-        <v>179</v>
       </c>
       <c r="H4" s="41"/>
       <c r="I4" s="42"/>
@@ -27997,22 +27979,22 @@
         <v>50</v>
       </c>
       <c r="B5" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="42" t="s">
         <v>180</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="G5" s="41" t="s">
         <v>181</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="G5" s="41" t="s">
-        <v>185</v>
       </c>
       <c r="H5" s="42"/>
       <c r="I5" s="41"/>
@@ -28027,19 +28009,19 @@
       </c>
       <c r="B6" s="41"/>
       <c r="C6" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="G6" s="42" t="s">
         <v>186</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>190</v>
       </c>
       <c r="H6" s="41"/>
       <c r="I6" s="42"/>
@@ -28054,19 +28036,19 @@
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="G7" s="41" t="s">
         <v>191</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="G7" s="41" t="s">
-        <v>195</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="41"/>
@@ -28080,10 +28062,10 @@
         <v>53</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D8" s="41"/>
       <c r="E8" s="42"/>
@@ -31231,7 +31213,7 @@
       </c>
       <c r="B6" s="41"/>
       <c r="C6" s="42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D6" s="41"/>
       <c r="E6" s="42"/>
@@ -37473,25 +37455,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="93"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="97"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
     </row>
@@ -37502,17 +37484,17 @@
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="96"/>
+      <c r="I2" s="96"/>
+      <c r="J2" s="96"/>
+      <c r="K2" s="97"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -37596,11 +37578,11 @@
       <c r="B6" s="15">
         <v>16.5</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="C6" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="88"/>
-      <c r="E6" s="88"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="92"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
@@ -37616,9 +37598,9 @@
       <c r="B7" s="15">
         <v>5.5</v>
       </c>
-      <c r="C7" s="88"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
@@ -37635,9 +37617,9 @@
         <f>SUM(B6:B7)</f>
         <v>22</v>
       </c>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="92"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -37653,9 +37635,9 @@
       <c r="B9" s="15">
         <v>20</v>
       </c>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
-      <c r="E9" s="88"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
@@ -37679,12 +37661,12 @@
       <c r="L10" s="13"/>
     </row>
     <row r="11" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="93"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="97"/>
       <c r="E11" s="17"/>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
@@ -37748,7 +37730,7 @@
       <c r="C15" s="22">
         <v>0.5</v>
       </c>
-      <c r="D15" s="96">
+      <c r="D15" s="100">
         <v>40</v>
       </c>
     </row>
@@ -37762,7 +37744,7 @@
       <c r="C16" s="22">
         <v>1</v>
       </c>
-      <c r="D16" s="97"/>
+      <c r="D16" s="101"/>
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
@@ -37785,12 +37767,12 @@
       <c r="D18" s="17"/>
     </row>
     <row r="19" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="84" t="s">
+      <c r="A19" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="86"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="90"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
@@ -37831,18 +37813,18 @@
         <f>COUNTIF(Samples!B2:M9,"&lt;&gt;"&amp;"")</f>
         <v>36</v>
       </c>
-      <c r="C24" s="87" t="s">
+      <c r="C24" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="92"/>
     </row>
     <row r="25" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="28" t="s">
@@ -37879,10 +37861,10 @@
       <c r="L26" s="13"/>
     </row>
     <row r="27" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="89" t="s">
+      <c r="A27" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="90"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="30"/>
       <c r="D27" s="30"/>
       <c r="E27" s="17"/>
@@ -39011,60 +38993,60 @@
         <v>56</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D1" s="43" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E1" s="44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G1" s="44" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H1" s="43" t="s">
         <v>57</v>
       </c>
       <c r="I1" s="43" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J1" s="44" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K1" s="43" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L1" s="43" t="s">
         <v>58</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="45" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>118</v>
+      <c r="A2" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="102" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" s="102" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="102" t="s">
+        <v>217</v>
+      </c>
+      <c r="G2" s="102" t="s">
+        <v>217</v>
       </c>
       <c r="H2" s="45" t="s">
         <v>61</v>
@@ -39073,39 +39055,39 @@
         <v>70</v>
       </c>
       <c r="J2" s="47" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="K2" s="49" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L2" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="M2" s="98" t="s">
-        <v>215</v>
+      <c r="M2" s="84" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>95</v>
+      <c r="A3" s="102" t="s">
+        <v>216</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>80</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D3" s="51" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H3" s="45" t="s">
         <v>63</v>
@@ -39114,39 +39096,39 @@
         <v>71</v>
       </c>
       <c r="J3" s="47" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K3" s="45" t="s">
         <v>64</v>
       </c>
       <c r="L3" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="M3" s="98" t="s">
-        <v>216</v>
+        <v>84</v>
+      </c>
+      <c r="M3" s="84" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="46" t="s">
-        <v>96</v>
+      <c r="B4" s="102" t="s">
+        <v>214</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D4" s="51" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>113</v>
       </c>
       <c r="H4" s="45" t="s">
         <v>66</v>
@@ -39158,30 +39140,32 @@
         <v>72</v>
       </c>
       <c r="K4" s="49" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L4" s="45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="45"/>
       <c r="B5" s="46" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D5" s="51" t="s">
         <v>51</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="G5" s="46"/>
+        <v>118</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>72</v>
+      </c>
       <c r="H5" s="45" t="s">
         <v>67</v>
       </c>
@@ -39191,19 +39175,19 @@
         <v>72</v>
       </c>
       <c r="L5" s="45" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="45"/>
-      <c r="B6" s="49" t="s">
-        <v>132</v>
+      <c r="B6" s="46" t="s">
+        <v>94</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>72</v>
@@ -39219,19 +39203,19 @@
       <c r="J6" s="45"/>
       <c r="K6" s="45"/>
       <c r="L6" s="45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="45"/>
       <c r="B7" s="49" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D7" s="51" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E7" s="45"/>
       <c r="F7" s="45" t="s">
@@ -39244,89 +39228,93 @@
       <c r="J7" s="45"/>
       <c r="K7" s="45"/>
       <c r="L7" s="45" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45"/>
-      <c r="B8" s="45" t="s">
-        <v>65</v>
+      <c r="B8" s="49" t="s">
+        <v>132</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E8" s="45"/>
       <c r="F8" s="45" t="s">
         <v>65</v>
       </c>
       <c r="G8" s="45"/>
-      <c r="H8" s="46" t="s">
-        <v>72</v>
+      <c r="H8" s="102" t="s">
+        <v>218</v>
       </c>
       <c r="I8" s="45"/>
       <c r="J8" s="45"/>
       <c r="K8" s="45"/>
       <c r="L8" s="45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="45"/>
-      <c r="B9" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>72</v>
+      <c r="B9" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>127</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E9" s="45"/>
       <c r="F9" s="48" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
+      <c r="H9" s="102" t="s">
+        <v>219</v>
+      </c>
       <c r="I9" s="45"/>
       <c r="J9" s="45"/>
       <c r="K9" s="45"/>
       <c r="L9" s="45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="45"/>
-      <c r="B10" s="49" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" s="45"/>
+      <c r="B10" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>72</v>
+      </c>
       <c r="D10" s="51" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E10" s="45"/>
       <c r="F10" s="46" t="s">
         <v>72</v>
       </c>
       <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
+      <c r="H10" s="102"/>
       <c r="I10" s="45"/>
       <c r="J10" s="45"/>
       <c r="K10" s="45"/>
       <c r="L10" s="45" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="45"/>
       <c r="B11" s="49" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C11" s="45"/>
       <c r="D11" s="51" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F11" s="45"/>
       <c r="G11" s="45"/>
@@ -39335,15 +39323,17 @@
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
       <c r="L11" s="45" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="45"/>
-      <c r="B12" s="45"/>
+      <c r="B12" s="49" t="s">
+        <v>72</v>
+      </c>
       <c r="C12" s="45"/>
       <c r="D12" s="51" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E12" s="45"/>
       <c r="F12" s="45"/>
@@ -39361,7 +39351,7 @@
       <c r="B13" s="45"/>
       <c r="C13" s="45"/>
       <c r="D13" s="51" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E13" s="45"/>
       <c r="F13" s="45"/>
@@ -39371,7 +39361,7 @@
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
       <c r="L13" s="45" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -39379,7 +39369,7 @@
       <c r="B14" s="45"/>
       <c r="C14" s="45"/>
       <c r="D14" s="51" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E14" s="45"/>
       <c r="F14" s="45"/>
@@ -39397,7 +39387,7 @@
       <c r="B15" s="45"/>
       <c r="C15" s="45"/>
       <c r="D15" s="46" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E15" s="45"/>
       <c r="F15" s="45"/>
@@ -39415,7 +39405,7 @@
       <c r="B16" s="45"/>
       <c r="C16" s="45"/>
       <c r="D16" s="46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E16" s="45"/>
       <c r="F16" s="45"/>
@@ -39433,7 +39423,7 @@
       <c r="B17" s="45"/>
       <c r="C17" s="45"/>
       <c r="D17" s="46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E17" s="45"/>
       <c r="F17" s="45"/>
@@ -39448,7 +39438,7 @@
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D18" s="51" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="L18" s="45" t="s">
         <v>77</v>
@@ -39464,7 +39454,7 @@
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D20" s="50" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">

--- a/analysis/TEST/ABATCH.v2.0.0.xlsx
+++ b/analysis/TEST/ABATCH.v2.0.0.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40913497-018A-6844-BCCA-BD640B1F1250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3088D7D-3B44-C946-9C1E-890E8EA1F530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="6" r:id="rId1"/>
-    <sheet name="Samples" sheetId="3" r:id="rId2"/>
-    <sheet name="Comments" sheetId="4" r:id="rId3"/>
-    <sheet name="Volume Overrides" sheetId="8" r:id="rId4"/>
-    <sheet name="Run Setup" sheetId="2" r:id="rId5"/>
-    <sheet name="Lists" sheetId="5" r:id="rId6"/>
+    <sheet name="Sample IDs" sheetId="3" r:id="rId2"/>
+    <sheet name="Extraction IDs" sheetId="9" r:id="rId3"/>
+    <sheet name="Comments" sheetId="4" r:id="rId4"/>
+    <sheet name="Volume Overrides" sheetId="8" r:id="rId5"/>
+    <sheet name="Run Setup" sheetId="2" r:id="rId6"/>
+    <sheet name="Lists" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="220">
   <si>
     <t>Assay</t>
   </si>
@@ -1508,6 +1509,7 @@
     <xf numFmtId="0" fontId="25" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1536,7 +1538,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27698,7 +27699,7 @@
   <pageSetup orientation="landscape"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="20">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="17">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9269EC84-DF31-1A4B-A990-FD99E0DF6A37}">
           <x14:formula1>
             <xm:f>Lists!$F$2:$F$10</xm:f>
@@ -27715,7 +27716,7 @@
           <x14:formula1>
             <xm:f>Lists!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B39 B44 B55 B60</xm:sqref>
+          <xm:sqref>B39 B44 B55 B60 B23 B28</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{4DE4111E-DA5E-784E-9D6F-05103F7D2493}">
           <x14:formula1>
@@ -27763,7 +27764,7 @@
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>B50</xm:sqref>
+          <xm:sqref>B50 B18 B34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E36366AC-D6BD-7D4B-94C1-F87AEC17F439}">
           <x14:formula1>
@@ -27775,7 +27776,7 @@
           <x14:formula1>
             <xm:f>Lists!$C$2:$C$10</xm:f>
           </x14:formula1>
-          <xm:sqref>B52</xm:sqref>
+          <xm:sqref>B52 B20 B36</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4589180C-9127-844B-B3AB-26B52318E969}">
           <x14:formula1>
@@ -27800,24 +27801,6 @@
             <xm:f>Lists!$B$2:$B$12</xm:f>
           </x14:formula1>
           <xm:sqref>B18 B34 B50</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BA29BD18-C8F7-C346-9651-7A8BCFA8C632}">
-          <x14:formula1>
-            <xm:f>Lists!$G$2:$G$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>B23 B28</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{8127A0B6-250B-4348-B13B-ADE932112953}">
-          <x14:formula1>
-            <xm:f>Lists!$B$2:$B$12</xm:f>
-          </x14:formula1>
-          <xm:sqref>B18 B34</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{1F1C9D61-2705-6E46-9905-EC33BDC0596D}">
-          <x14:formula1>
-            <xm:f>Lists!$C$2:$C$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>B20 B36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -31078,6 +31061,3186 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53192ABE-EA6D-C845-A3D8-64418E07B119}">
+  <dimension ref="A1:Z1001"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="13" width="20.5703125" customWidth="1"/>
+    <col min="14" max="26" width="10.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="52"/>
+      <c r="B1" s="52">
+        <v>1</v>
+      </c>
+      <c r="C1" s="52">
+        <v>2</v>
+      </c>
+      <c r="D1" s="52">
+        <v>3</v>
+      </c>
+      <c r="E1" s="52">
+        <v>4</v>
+      </c>
+      <c r="F1" s="52">
+        <v>5</v>
+      </c>
+      <c r="G1" s="52">
+        <v>6</v>
+      </c>
+      <c r="H1" s="52">
+        <v>7</v>
+      </c>
+      <c r="I1" s="52">
+        <v>8</v>
+      </c>
+      <c r="J1" s="52">
+        <v>9</v>
+      </c>
+      <c r="K1" s="52">
+        <v>10</v>
+      </c>
+      <c r="L1" s="52">
+        <v>11</v>
+      </c>
+      <c r="M1" s="52">
+        <v>12</v>
+      </c>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+    </row>
+    <row r="2" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="42"/>
+    </row>
+    <row r="3" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="42"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="41"/>
+    </row>
+    <row r="4" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="42"/>
+    </row>
+    <row r="5" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="41"/>
+    </row>
+    <row r="6" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="41"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="42"/>
+    </row>
+    <row r="7" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="42"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="41"/>
+    </row>
+    <row r="8" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="42"/>
+    </row>
+    <row r="9" spans="1:26" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="42"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="41"/>
+    </row>
+    <row r="10" spans="1:26" ht="31" x14ac:dyDescent="0.2">
+      <c r="A10" s="40"/>
+    </row>
+    <row r="11" spans="1:26" ht="31" x14ac:dyDescent="0.2">
+      <c r="A11" s="40"/>
+    </row>
+    <row r="12" spans="1:26" ht="31" x14ac:dyDescent="0.2">
+      <c r="A12" s="40"/>
+    </row>
+    <row r="13" spans="1:26" ht="31" x14ac:dyDescent="0.2">
+      <c r="A13" s="40"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="40"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="40"/>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="40"/>
+    </row>
+    <row r="17" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="40"/>
+    </row>
+    <row r="18" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="40"/>
+    </row>
+    <row r="19" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="40"/>
+    </row>
+    <row r="20" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="40"/>
+    </row>
+    <row r="21" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="40"/>
+    </row>
+    <row r="22" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="40"/>
+    </row>
+    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="40"/>
+    </row>
+    <row r="24" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="40"/>
+    </row>
+    <row r="25" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="40"/>
+    </row>
+    <row r="26" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="40"/>
+    </row>
+    <row r="27" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="40"/>
+    </row>
+    <row r="28" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="40"/>
+    </row>
+    <row r="29" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="40"/>
+    </row>
+    <row r="30" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="40"/>
+    </row>
+    <row r="31" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="40"/>
+    </row>
+    <row r="32" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="40"/>
+    </row>
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="40"/>
+    </row>
+    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="40"/>
+    </row>
+    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="40"/>
+    </row>
+    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="40"/>
+    </row>
+    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="40"/>
+    </row>
+    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="40"/>
+    </row>
+    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="40"/>
+    </row>
+    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="40"/>
+    </row>
+    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="40"/>
+    </row>
+    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="40"/>
+    </row>
+    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="40"/>
+    </row>
+    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="40"/>
+    </row>
+    <row r="45" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="40"/>
+    </row>
+    <row r="46" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="40"/>
+    </row>
+    <row r="47" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="40"/>
+    </row>
+    <row r="48" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="40"/>
+    </row>
+    <row r="49" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="40"/>
+    </row>
+    <row r="50" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="40"/>
+    </row>
+    <row r="51" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="40"/>
+    </row>
+    <row r="52" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="40"/>
+    </row>
+    <row r="53" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="40"/>
+    </row>
+    <row r="54" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="40"/>
+    </row>
+    <row r="55" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="40"/>
+    </row>
+    <row r="56" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="40"/>
+    </row>
+    <row r="57" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="40"/>
+    </row>
+    <row r="58" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="40"/>
+    </row>
+    <row r="59" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="40"/>
+    </row>
+    <row r="60" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="40"/>
+    </row>
+    <row r="61" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="40"/>
+    </row>
+    <row r="62" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="40"/>
+    </row>
+    <row r="63" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="40"/>
+    </row>
+    <row r="64" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="40"/>
+    </row>
+    <row r="65" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="40"/>
+    </row>
+    <row r="66" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="40"/>
+    </row>
+    <row r="67" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="40"/>
+    </row>
+    <row r="68" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="40"/>
+    </row>
+    <row r="69" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="40"/>
+    </row>
+    <row r="70" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="40"/>
+    </row>
+    <row r="71" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="40"/>
+    </row>
+    <row r="72" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="40"/>
+    </row>
+    <row r="73" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="40"/>
+    </row>
+    <row r="74" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="40"/>
+    </row>
+    <row r="75" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="40"/>
+    </row>
+    <row r="76" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="40"/>
+    </row>
+    <row r="77" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="40"/>
+    </row>
+    <row r="78" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="40"/>
+    </row>
+    <row r="79" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="40"/>
+    </row>
+    <row r="80" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="40"/>
+    </row>
+    <row r="81" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="40"/>
+    </row>
+    <row r="82" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="40"/>
+    </row>
+    <row r="83" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="40"/>
+    </row>
+    <row r="84" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="40"/>
+    </row>
+    <row r="85" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="40"/>
+    </row>
+    <row r="86" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="40"/>
+    </row>
+    <row r="87" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="40"/>
+    </row>
+    <row r="88" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="40"/>
+    </row>
+    <row r="89" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="40"/>
+    </row>
+    <row r="90" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="40"/>
+    </row>
+    <row r="91" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="40"/>
+    </row>
+    <row r="92" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="40"/>
+    </row>
+    <row r="93" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="40"/>
+    </row>
+    <row r="94" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="40"/>
+    </row>
+    <row r="95" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="40"/>
+    </row>
+    <row r="96" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="40"/>
+    </row>
+    <row r="97" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="40"/>
+    </row>
+    <row r="98" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="40"/>
+    </row>
+    <row r="99" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="40"/>
+    </row>
+    <row r="100" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="40"/>
+    </row>
+    <row r="101" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="40"/>
+    </row>
+    <row r="102" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="40"/>
+    </row>
+    <row r="103" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="40"/>
+    </row>
+    <row r="104" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="40"/>
+    </row>
+    <row r="105" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="40"/>
+    </row>
+    <row r="106" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="40"/>
+    </row>
+    <row r="107" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="40"/>
+    </row>
+    <row r="108" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="40"/>
+    </row>
+    <row r="109" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="40"/>
+    </row>
+    <row r="110" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="40"/>
+    </row>
+    <row r="111" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="40"/>
+    </row>
+    <row r="112" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="40"/>
+    </row>
+    <row r="113" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="40"/>
+    </row>
+    <row r="114" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="40"/>
+    </row>
+    <row r="115" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="40"/>
+    </row>
+    <row r="116" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="40"/>
+    </row>
+    <row r="117" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="40"/>
+    </row>
+    <row r="118" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="40"/>
+    </row>
+    <row r="119" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="40"/>
+    </row>
+    <row r="120" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="40"/>
+    </row>
+    <row r="121" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="40"/>
+    </row>
+    <row r="122" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="40"/>
+    </row>
+    <row r="123" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="40"/>
+    </row>
+    <row r="124" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="40"/>
+    </row>
+    <row r="125" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="40"/>
+    </row>
+    <row r="126" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" s="40"/>
+    </row>
+    <row r="127" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" s="40"/>
+    </row>
+    <row r="128" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="40"/>
+    </row>
+    <row r="129" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="40"/>
+    </row>
+    <row r="130" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="40"/>
+    </row>
+    <row r="131" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="40"/>
+    </row>
+    <row r="132" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="40"/>
+    </row>
+    <row r="133" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="40"/>
+    </row>
+    <row r="134" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="40"/>
+    </row>
+    <row r="135" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="40"/>
+    </row>
+    <row r="136" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="40"/>
+    </row>
+    <row r="137" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="40"/>
+    </row>
+    <row r="138" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="40"/>
+    </row>
+    <row r="139" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="40"/>
+    </row>
+    <row r="140" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" s="40"/>
+    </row>
+    <row r="141" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="40"/>
+    </row>
+    <row r="142" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="40"/>
+    </row>
+    <row r="143" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="40"/>
+    </row>
+    <row r="144" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="40"/>
+    </row>
+    <row r="145" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="40"/>
+    </row>
+    <row r="146" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="40"/>
+    </row>
+    <row r="147" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="40"/>
+    </row>
+    <row r="148" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="40"/>
+    </row>
+    <row r="149" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="40"/>
+    </row>
+    <row r="150" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="40"/>
+    </row>
+    <row r="151" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="40"/>
+    </row>
+    <row r="152" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="40"/>
+    </row>
+    <row r="153" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="40"/>
+    </row>
+    <row r="154" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="40"/>
+    </row>
+    <row r="155" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="40"/>
+    </row>
+    <row r="156" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="40"/>
+    </row>
+    <row r="157" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="40"/>
+    </row>
+    <row r="158" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="40"/>
+    </row>
+    <row r="159" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="40"/>
+    </row>
+    <row r="160" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="40"/>
+    </row>
+    <row r="161" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="40"/>
+    </row>
+    <row r="162" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="40"/>
+    </row>
+    <row r="163" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="40"/>
+    </row>
+    <row r="164" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="40"/>
+    </row>
+    <row r="165" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="40"/>
+    </row>
+    <row r="166" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="40"/>
+    </row>
+    <row r="167" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="40"/>
+    </row>
+    <row r="168" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="40"/>
+    </row>
+    <row r="169" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A169" s="40"/>
+    </row>
+    <row r="170" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="40"/>
+    </row>
+    <row r="171" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="40"/>
+    </row>
+    <row r="172" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" s="40"/>
+    </row>
+    <row r="173" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" s="40"/>
+    </row>
+    <row r="174" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" s="40"/>
+    </row>
+    <row r="175" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" s="40"/>
+    </row>
+    <row r="176" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" s="40"/>
+    </row>
+    <row r="177" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" s="40"/>
+    </row>
+    <row r="178" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" s="40"/>
+    </row>
+    <row r="179" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" s="40"/>
+    </row>
+    <row r="180" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" s="40"/>
+    </row>
+    <row r="181" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="40"/>
+    </row>
+    <row r="182" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="40"/>
+    </row>
+    <row r="183" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" s="40"/>
+    </row>
+    <row r="184" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" s="40"/>
+    </row>
+    <row r="185" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" s="40"/>
+    </row>
+    <row r="186" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" s="40"/>
+    </row>
+    <row r="187" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" s="40"/>
+    </row>
+    <row r="188" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A188" s="40"/>
+    </row>
+    <row r="189" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A189" s="40"/>
+    </row>
+    <row r="190" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A190" s="40"/>
+    </row>
+    <row r="191" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A191" s="40"/>
+    </row>
+    <row r="192" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A192" s="40"/>
+    </row>
+    <row r="193" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A193" s="40"/>
+    </row>
+    <row r="194" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A194" s="40"/>
+    </row>
+    <row r="195" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A195" s="40"/>
+    </row>
+    <row r="196" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A196" s="40"/>
+    </row>
+    <row r="197" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A197" s="40"/>
+    </row>
+    <row r="198" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A198" s="40"/>
+    </row>
+    <row r="199" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A199" s="40"/>
+    </row>
+    <row r="200" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A200" s="40"/>
+    </row>
+    <row r="201" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A201" s="40"/>
+    </row>
+    <row r="202" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A202" s="40"/>
+    </row>
+    <row r="203" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A203" s="40"/>
+    </row>
+    <row r="204" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A204" s="40"/>
+    </row>
+    <row r="205" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A205" s="40"/>
+    </row>
+    <row r="206" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A206" s="40"/>
+    </row>
+    <row r="207" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A207" s="40"/>
+    </row>
+    <row r="208" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A208" s="40"/>
+    </row>
+    <row r="209" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A209" s="40"/>
+    </row>
+    <row r="210" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A210" s="40"/>
+    </row>
+    <row r="211" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A211" s="40"/>
+    </row>
+    <row r="212" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="40"/>
+    </row>
+    <row r="213" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="40"/>
+    </row>
+    <row r="214" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A214" s="40"/>
+    </row>
+    <row r="215" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A215" s="40"/>
+    </row>
+    <row r="216" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A216" s="40"/>
+    </row>
+    <row r="217" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A217" s="40"/>
+    </row>
+    <row r="218" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A218" s="40"/>
+    </row>
+    <row r="219" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="40"/>
+    </row>
+    <row r="220" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A220" s="40"/>
+    </row>
+    <row r="221" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A221" s="40"/>
+    </row>
+    <row r="222" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="40"/>
+    </row>
+    <row r="223" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="40"/>
+    </row>
+    <row r="224" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="40"/>
+    </row>
+    <row r="225" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="40"/>
+    </row>
+    <row r="226" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="40"/>
+    </row>
+    <row r="227" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="40"/>
+    </row>
+    <row r="228" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="40"/>
+    </row>
+    <row r="229" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="40"/>
+    </row>
+    <row r="230" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="40"/>
+    </row>
+    <row r="231" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="40"/>
+    </row>
+    <row r="232" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="40"/>
+    </row>
+    <row r="233" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="40"/>
+    </row>
+    <row r="234" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="40"/>
+    </row>
+    <row r="235" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="40"/>
+    </row>
+    <row r="236" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="40"/>
+    </row>
+    <row r="237" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="40"/>
+    </row>
+    <row r="238" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="40"/>
+    </row>
+    <row r="239" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="40"/>
+    </row>
+    <row r="240" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="40"/>
+    </row>
+    <row r="241" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="40"/>
+    </row>
+    <row r="242" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A242" s="40"/>
+    </row>
+    <row r="243" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A243" s="40"/>
+    </row>
+    <row r="244" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A244" s="40"/>
+    </row>
+    <row r="245" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A245" s="40"/>
+    </row>
+    <row r="246" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A246" s="40"/>
+    </row>
+    <row r="247" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A247" s="40"/>
+    </row>
+    <row r="248" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A248" s="40"/>
+    </row>
+    <row r="249" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="40"/>
+    </row>
+    <row r="250" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A250" s="40"/>
+    </row>
+    <row r="251" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A251" s="40"/>
+    </row>
+    <row r="252" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A252" s="40"/>
+    </row>
+    <row r="253" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A253" s="40"/>
+    </row>
+    <row r="254" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A254" s="40"/>
+    </row>
+    <row r="255" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="40"/>
+    </row>
+    <row r="256" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A256" s="40"/>
+    </row>
+    <row r="257" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="40"/>
+    </row>
+    <row r="258" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A258" s="40"/>
+    </row>
+    <row r="259" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="40"/>
+    </row>
+    <row r="260" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A260" s="40"/>
+    </row>
+    <row r="261" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="40"/>
+    </row>
+    <row r="262" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A262" s="40"/>
+    </row>
+    <row r="263" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="40"/>
+    </row>
+    <row r="264" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A264" s="40"/>
+    </row>
+    <row r="265" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A265" s="40"/>
+    </row>
+    <row r="266" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A266" s="40"/>
+    </row>
+    <row r="267" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="40"/>
+    </row>
+    <row r="268" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A268" s="40"/>
+    </row>
+    <row r="269" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A269" s="40"/>
+    </row>
+    <row r="270" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A270" s="40"/>
+    </row>
+    <row r="271" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A271" s="40"/>
+    </row>
+    <row r="272" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A272" s="40"/>
+    </row>
+    <row r="273" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" s="40"/>
+    </row>
+    <row r="274" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A274" s="40"/>
+    </row>
+    <row r="275" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" s="40"/>
+    </row>
+    <row r="276" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A276" s="40"/>
+    </row>
+    <row r="277" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A277" s="40"/>
+    </row>
+    <row r="278" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A278" s="40"/>
+    </row>
+    <row r="279" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A279" s="40"/>
+    </row>
+    <row r="280" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" s="40"/>
+    </row>
+    <row r="281" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A281" s="40"/>
+    </row>
+    <row r="282" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="40"/>
+    </row>
+    <row r="283" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A283" s="40"/>
+    </row>
+    <row r="284" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="40"/>
+    </row>
+    <row r="285" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A285" s="40"/>
+    </row>
+    <row r="286" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" s="40"/>
+    </row>
+    <row r="287" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A287" s="40"/>
+    </row>
+    <row r="288" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" s="40"/>
+    </row>
+    <row r="289" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A289" s="40"/>
+    </row>
+    <row r="290" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A290" s="40"/>
+    </row>
+    <row r="291" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A291" s="40"/>
+    </row>
+    <row r="292" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A292" s="40"/>
+    </row>
+    <row r="293" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="40"/>
+    </row>
+    <row r="294" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" s="40"/>
+    </row>
+    <row r="295" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="40"/>
+    </row>
+    <row r="296" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="40"/>
+    </row>
+    <row r="297" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="40"/>
+    </row>
+    <row r="298" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="40"/>
+    </row>
+    <row r="299" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="40"/>
+    </row>
+    <row r="300" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="40"/>
+    </row>
+    <row r="301" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="40"/>
+    </row>
+    <row r="302" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="40"/>
+    </row>
+    <row r="303" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="40"/>
+    </row>
+    <row r="304" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A304" s="40"/>
+    </row>
+    <row r="305" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="40"/>
+    </row>
+    <row r="306" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="40"/>
+    </row>
+    <row r="307" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="40"/>
+    </row>
+    <row r="308" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="40"/>
+    </row>
+    <row r="309" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A309" s="40"/>
+    </row>
+    <row r="310" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="40"/>
+    </row>
+    <row r="311" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A311" s="40"/>
+    </row>
+    <row r="312" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A312" s="40"/>
+    </row>
+    <row r="313" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A313" s="40"/>
+    </row>
+    <row r="314" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="40"/>
+    </row>
+    <row r="315" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="40"/>
+    </row>
+    <row r="316" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="40"/>
+    </row>
+    <row r="317" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="40"/>
+    </row>
+    <row r="318" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A318" s="40"/>
+    </row>
+    <row r="319" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="40"/>
+    </row>
+    <row r="320" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A320" s="40"/>
+    </row>
+    <row r="321" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="40"/>
+    </row>
+    <row r="322" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="40"/>
+    </row>
+    <row r="323" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="40"/>
+    </row>
+    <row r="324" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A324" s="40"/>
+    </row>
+    <row r="325" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="40"/>
+    </row>
+    <row r="326" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326" s="40"/>
+    </row>
+    <row r="327" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A327" s="40"/>
+    </row>
+    <row r="328" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A328" s="40"/>
+    </row>
+    <row r="329" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A329" s="40"/>
+    </row>
+    <row r="330" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A330" s="40"/>
+    </row>
+    <row r="331" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A331" s="40"/>
+    </row>
+    <row r="332" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A332" s="40"/>
+    </row>
+    <row r="333" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A333" s="40"/>
+    </row>
+    <row r="334" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A334" s="40"/>
+    </row>
+    <row r="335" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A335" s="40"/>
+    </row>
+    <row r="336" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A336" s="40"/>
+    </row>
+    <row r="337" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A337" s="40"/>
+    </row>
+    <row r="338" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A338" s="40"/>
+    </row>
+    <row r="339" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A339" s="40"/>
+    </row>
+    <row r="340" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A340" s="40"/>
+    </row>
+    <row r="341" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A341" s="40"/>
+    </row>
+    <row r="342" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A342" s="40"/>
+    </row>
+    <row r="343" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A343" s="40"/>
+    </row>
+    <row r="344" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A344" s="40"/>
+    </row>
+    <row r="345" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A345" s="40"/>
+    </row>
+    <row r="346" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A346" s="40"/>
+    </row>
+    <row r="347" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A347" s="40"/>
+    </row>
+    <row r="348" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A348" s="40"/>
+    </row>
+    <row r="349" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A349" s="40"/>
+    </row>
+    <row r="350" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A350" s="40"/>
+    </row>
+    <row r="351" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A351" s="40"/>
+    </row>
+    <row r="352" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A352" s="40"/>
+    </row>
+    <row r="353" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A353" s="40"/>
+    </row>
+    <row r="354" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A354" s="40"/>
+    </row>
+    <row r="355" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A355" s="40"/>
+    </row>
+    <row r="356" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A356" s="40"/>
+    </row>
+    <row r="357" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A357" s="40"/>
+    </row>
+    <row r="358" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A358" s="40"/>
+    </row>
+    <row r="359" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A359" s="40"/>
+    </row>
+    <row r="360" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A360" s="40"/>
+    </row>
+    <row r="361" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A361" s="40"/>
+    </row>
+    <row r="362" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A362" s="40"/>
+    </row>
+    <row r="363" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A363" s="40"/>
+    </row>
+    <row r="364" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A364" s="40"/>
+    </row>
+    <row r="365" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A365" s="40"/>
+    </row>
+    <row r="366" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A366" s="40"/>
+    </row>
+    <row r="367" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A367" s="40"/>
+    </row>
+    <row r="368" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A368" s="40"/>
+    </row>
+    <row r="369" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A369" s="40"/>
+    </row>
+    <row r="370" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A370" s="40"/>
+    </row>
+    <row r="371" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A371" s="40"/>
+    </row>
+    <row r="372" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A372" s="40"/>
+    </row>
+    <row r="373" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A373" s="40"/>
+    </row>
+    <row r="374" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A374" s="40"/>
+    </row>
+    <row r="375" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A375" s="40"/>
+    </row>
+    <row r="376" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A376" s="40"/>
+    </row>
+    <row r="377" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A377" s="40"/>
+    </row>
+    <row r="378" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A378" s="40"/>
+    </row>
+    <row r="379" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A379" s="40"/>
+    </row>
+    <row r="380" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A380" s="40"/>
+    </row>
+    <row r="381" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A381" s="40"/>
+    </row>
+    <row r="382" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A382" s="40"/>
+    </row>
+    <row r="383" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A383" s="40"/>
+    </row>
+    <row r="384" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A384" s="40"/>
+    </row>
+    <row r="385" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A385" s="40"/>
+    </row>
+    <row r="386" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A386" s="40"/>
+    </row>
+    <row r="387" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A387" s="40"/>
+    </row>
+    <row r="388" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A388" s="40"/>
+    </row>
+    <row r="389" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A389" s="40"/>
+    </row>
+    <row r="390" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A390" s="40"/>
+    </row>
+    <row r="391" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A391" s="40"/>
+    </row>
+    <row r="392" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A392" s="40"/>
+    </row>
+    <row r="393" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A393" s="40"/>
+    </row>
+    <row r="394" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A394" s="40"/>
+    </row>
+    <row r="395" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A395" s="40"/>
+    </row>
+    <row r="396" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A396" s="40"/>
+    </row>
+    <row r="397" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A397" s="40"/>
+    </row>
+    <row r="398" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A398" s="40"/>
+    </row>
+    <row r="399" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A399" s="40"/>
+    </row>
+    <row r="400" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A400" s="40"/>
+    </row>
+    <row r="401" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A401" s="40"/>
+    </row>
+    <row r="402" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A402" s="40"/>
+    </row>
+    <row r="403" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A403" s="40"/>
+    </row>
+    <row r="404" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A404" s="40"/>
+    </row>
+    <row r="405" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A405" s="40"/>
+    </row>
+    <row r="406" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A406" s="40"/>
+    </row>
+    <row r="407" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A407" s="40"/>
+    </row>
+    <row r="408" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A408" s="40"/>
+    </row>
+    <row r="409" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A409" s="40"/>
+    </row>
+    <row r="410" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A410" s="40"/>
+    </row>
+    <row r="411" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A411" s="40"/>
+    </row>
+    <row r="412" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A412" s="40"/>
+    </row>
+    <row r="413" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A413" s="40"/>
+    </row>
+    <row r="414" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A414" s="40"/>
+    </row>
+    <row r="415" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A415" s="40"/>
+    </row>
+    <row r="416" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A416" s="40"/>
+    </row>
+    <row r="417" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A417" s="40"/>
+    </row>
+    <row r="418" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A418" s="40"/>
+    </row>
+    <row r="419" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A419" s="40"/>
+    </row>
+    <row r="420" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A420" s="40"/>
+    </row>
+    <row r="421" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A421" s="40"/>
+    </row>
+    <row r="422" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A422" s="40"/>
+    </row>
+    <row r="423" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A423" s="40"/>
+    </row>
+    <row r="424" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A424" s="40"/>
+    </row>
+    <row r="425" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A425" s="40"/>
+    </row>
+    <row r="426" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A426" s="40"/>
+    </row>
+    <row r="427" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A427" s="40"/>
+    </row>
+    <row r="428" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A428" s="40"/>
+    </row>
+    <row r="429" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A429" s="40"/>
+    </row>
+    <row r="430" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A430" s="40"/>
+    </row>
+    <row r="431" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A431" s="40"/>
+    </row>
+    <row r="432" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A432" s="40"/>
+    </row>
+    <row r="433" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A433" s="40"/>
+    </row>
+    <row r="434" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A434" s="40"/>
+    </row>
+    <row r="435" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A435" s="40"/>
+    </row>
+    <row r="436" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A436" s="40"/>
+    </row>
+    <row r="437" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A437" s="40"/>
+    </row>
+    <row r="438" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A438" s="40"/>
+    </row>
+    <row r="439" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A439" s="40"/>
+    </row>
+    <row r="440" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A440" s="40"/>
+    </row>
+    <row r="441" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A441" s="40"/>
+    </row>
+    <row r="442" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A442" s="40"/>
+    </row>
+    <row r="443" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A443" s="40"/>
+    </row>
+    <row r="444" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A444" s="40"/>
+    </row>
+    <row r="445" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A445" s="40"/>
+    </row>
+    <row r="446" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A446" s="40"/>
+    </row>
+    <row r="447" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A447" s="40"/>
+    </row>
+    <row r="448" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A448" s="40"/>
+    </row>
+    <row r="449" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A449" s="40"/>
+    </row>
+    <row r="450" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A450" s="40"/>
+    </row>
+    <row r="451" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A451" s="40"/>
+    </row>
+    <row r="452" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A452" s="40"/>
+    </row>
+    <row r="453" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A453" s="40"/>
+    </row>
+    <row r="454" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A454" s="40"/>
+    </row>
+    <row r="455" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A455" s="40"/>
+    </row>
+    <row r="456" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A456" s="40"/>
+    </row>
+    <row r="457" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A457" s="40"/>
+    </row>
+    <row r="458" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A458" s="40"/>
+    </row>
+    <row r="459" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A459" s="40"/>
+    </row>
+    <row r="460" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A460" s="40"/>
+    </row>
+    <row r="461" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A461" s="40"/>
+    </row>
+    <row r="462" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A462" s="40"/>
+    </row>
+    <row r="463" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A463" s="40"/>
+    </row>
+    <row r="464" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A464" s="40"/>
+    </row>
+    <row r="465" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A465" s="40"/>
+    </row>
+    <row r="466" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A466" s="40"/>
+    </row>
+    <row r="467" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A467" s="40"/>
+    </row>
+    <row r="468" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A468" s="40"/>
+    </row>
+    <row r="469" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A469" s="40"/>
+    </row>
+    <row r="470" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A470" s="40"/>
+    </row>
+    <row r="471" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A471" s="40"/>
+    </row>
+    <row r="472" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A472" s="40"/>
+    </row>
+    <row r="473" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A473" s="40"/>
+    </row>
+    <row r="474" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A474" s="40"/>
+    </row>
+    <row r="475" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A475" s="40"/>
+    </row>
+    <row r="476" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A476" s="40"/>
+    </row>
+    <row r="477" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A477" s="40"/>
+    </row>
+    <row r="478" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A478" s="40"/>
+    </row>
+    <row r="479" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A479" s="40"/>
+    </row>
+    <row r="480" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A480" s="40"/>
+    </row>
+    <row r="481" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A481" s="40"/>
+    </row>
+    <row r="482" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A482" s="40"/>
+    </row>
+    <row r="483" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A483" s="40"/>
+    </row>
+    <row r="484" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A484" s="40"/>
+    </row>
+    <row r="485" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A485" s="40"/>
+    </row>
+    <row r="486" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A486" s="40"/>
+    </row>
+    <row r="487" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A487" s="40"/>
+    </row>
+    <row r="488" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A488" s="40"/>
+    </row>
+    <row r="489" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A489" s="40"/>
+    </row>
+    <row r="490" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A490" s="40"/>
+    </row>
+    <row r="491" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A491" s="40"/>
+    </row>
+    <row r="492" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A492" s="40"/>
+    </row>
+    <row r="493" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A493" s="40"/>
+    </row>
+    <row r="494" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A494" s="40"/>
+    </row>
+    <row r="495" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A495" s="40"/>
+    </row>
+    <row r="496" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A496" s="40"/>
+    </row>
+    <row r="497" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A497" s="40"/>
+    </row>
+    <row r="498" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A498" s="40"/>
+    </row>
+    <row r="499" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A499" s="40"/>
+    </row>
+    <row r="500" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A500" s="40"/>
+    </row>
+    <row r="501" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A501" s="40"/>
+    </row>
+    <row r="502" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A502" s="40"/>
+    </row>
+    <row r="503" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A503" s="40"/>
+    </row>
+    <row r="504" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A504" s="40"/>
+    </row>
+    <row r="505" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A505" s="40"/>
+    </row>
+    <row r="506" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A506" s="40"/>
+    </row>
+    <row r="507" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A507" s="40"/>
+    </row>
+    <row r="508" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A508" s="40"/>
+    </row>
+    <row r="509" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A509" s="40"/>
+    </row>
+    <row r="510" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A510" s="40"/>
+    </row>
+    <row r="511" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A511" s="40"/>
+    </row>
+    <row r="512" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A512" s="40"/>
+    </row>
+    <row r="513" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A513" s="40"/>
+    </row>
+    <row r="514" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A514" s="40"/>
+    </row>
+    <row r="515" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A515" s="40"/>
+    </row>
+    <row r="516" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A516" s="40"/>
+    </row>
+    <row r="517" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A517" s="40"/>
+    </row>
+    <row r="518" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A518" s="40"/>
+    </row>
+    <row r="519" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A519" s="40"/>
+    </row>
+    <row r="520" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A520" s="40"/>
+    </row>
+    <row r="521" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A521" s="40"/>
+    </row>
+    <row r="522" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A522" s="40"/>
+    </row>
+    <row r="523" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A523" s="40"/>
+    </row>
+    <row r="524" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A524" s="40"/>
+    </row>
+    <row r="525" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A525" s="40"/>
+    </row>
+    <row r="526" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A526" s="40"/>
+    </row>
+    <row r="527" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A527" s="40"/>
+    </row>
+    <row r="528" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A528" s="40"/>
+    </row>
+    <row r="529" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A529" s="40"/>
+    </row>
+    <row r="530" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A530" s="40"/>
+    </row>
+    <row r="531" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A531" s="40"/>
+    </row>
+    <row r="532" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A532" s="40"/>
+    </row>
+    <row r="533" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A533" s="40"/>
+    </row>
+    <row r="534" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A534" s="40"/>
+    </row>
+    <row r="535" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A535" s="40"/>
+    </row>
+    <row r="536" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A536" s="40"/>
+    </row>
+    <row r="537" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A537" s="40"/>
+    </row>
+    <row r="538" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A538" s="40"/>
+    </row>
+    <row r="539" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A539" s="40"/>
+    </row>
+    <row r="540" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A540" s="40"/>
+    </row>
+    <row r="541" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A541" s="40"/>
+    </row>
+    <row r="542" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A542" s="40"/>
+    </row>
+    <row r="543" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A543" s="40"/>
+    </row>
+    <row r="544" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A544" s="40"/>
+    </row>
+    <row r="545" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A545" s="40"/>
+    </row>
+    <row r="546" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A546" s="40"/>
+    </row>
+    <row r="547" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A547" s="40"/>
+    </row>
+    <row r="548" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A548" s="40"/>
+    </row>
+    <row r="549" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A549" s="40"/>
+    </row>
+    <row r="550" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A550" s="40"/>
+    </row>
+    <row r="551" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A551" s="40"/>
+    </row>
+    <row r="552" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A552" s="40"/>
+    </row>
+    <row r="553" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A553" s="40"/>
+    </row>
+    <row r="554" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A554" s="40"/>
+    </row>
+    <row r="555" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A555" s="40"/>
+    </row>
+    <row r="556" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A556" s="40"/>
+    </row>
+    <row r="557" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A557" s="40"/>
+    </row>
+    <row r="558" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A558" s="40"/>
+    </row>
+    <row r="559" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A559" s="40"/>
+    </row>
+    <row r="560" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A560" s="40"/>
+    </row>
+    <row r="561" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A561" s="40"/>
+    </row>
+    <row r="562" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A562" s="40"/>
+    </row>
+    <row r="563" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A563" s="40"/>
+    </row>
+    <row r="564" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A564" s="40"/>
+    </row>
+    <row r="565" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A565" s="40"/>
+    </row>
+    <row r="566" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A566" s="40"/>
+    </row>
+    <row r="567" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A567" s="40"/>
+    </row>
+    <row r="568" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A568" s="40"/>
+    </row>
+    <row r="569" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A569" s="40"/>
+    </row>
+    <row r="570" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A570" s="40"/>
+    </row>
+    <row r="571" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A571" s="40"/>
+    </row>
+    <row r="572" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A572" s="40"/>
+    </row>
+    <row r="573" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A573" s="40"/>
+    </row>
+    <row r="574" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A574" s="40"/>
+    </row>
+    <row r="575" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A575" s="40"/>
+    </row>
+    <row r="576" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A576" s="40"/>
+    </row>
+    <row r="577" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A577" s="40"/>
+    </row>
+    <row r="578" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A578" s="40"/>
+    </row>
+    <row r="579" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A579" s="40"/>
+    </row>
+    <row r="580" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A580" s="40"/>
+    </row>
+    <row r="581" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A581" s="40"/>
+    </row>
+    <row r="582" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A582" s="40"/>
+    </row>
+    <row r="583" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A583" s="40"/>
+    </row>
+    <row r="584" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A584" s="40"/>
+    </row>
+    <row r="585" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A585" s="40"/>
+    </row>
+    <row r="586" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A586" s="40"/>
+    </row>
+    <row r="587" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A587" s="40"/>
+    </row>
+    <row r="588" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A588" s="40"/>
+    </row>
+    <row r="589" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A589" s="40"/>
+    </row>
+    <row r="590" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A590" s="40"/>
+    </row>
+    <row r="591" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A591" s="40"/>
+    </row>
+    <row r="592" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A592" s="40"/>
+    </row>
+    <row r="593" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A593" s="40"/>
+    </row>
+    <row r="594" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A594" s="40"/>
+    </row>
+    <row r="595" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A595" s="40"/>
+    </row>
+    <row r="596" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A596" s="40"/>
+    </row>
+    <row r="597" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A597" s="40"/>
+    </row>
+    <row r="598" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A598" s="40"/>
+    </row>
+    <row r="599" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A599" s="40"/>
+    </row>
+    <row r="600" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A600" s="40"/>
+    </row>
+    <row r="601" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A601" s="40"/>
+    </row>
+    <row r="602" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A602" s="40"/>
+    </row>
+    <row r="603" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A603" s="40"/>
+    </row>
+    <row r="604" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A604" s="40"/>
+    </row>
+    <row r="605" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A605" s="40"/>
+    </row>
+    <row r="606" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A606" s="40"/>
+    </row>
+    <row r="607" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A607" s="40"/>
+    </row>
+    <row r="608" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A608" s="40"/>
+    </row>
+    <row r="609" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A609" s="40"/>
+    </row>
+    <row r="610" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A610" s="40"/>
+    </row>
+    <row r="611" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A611" s="40"/>
+    </row>
+    <row r="612" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A612" s="40"/>
+    </row>
+    <row r="613" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A613" s="40"/>
+    </row>
+    <row r="614" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A614" s="40"/>
+    </row>
+    <row r="615" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A615" s="40"/>
+    </row>
+    <row r="616" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A616" s="40"/>
+    </row>
+    <row r="617" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A617" s="40"/>
+    </row>
+    <row r="618" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A618" s="40"/>
+    </row>
+    <row r="619" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A619" s="40"/>
+    </row>
+    <row r="620" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A620" s="40"/>
+    </row>
+    <row r="621" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A621" s="40"/>
+    </row>
+    <row r="622" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A622" s="40"/>
+    </row>
+    <row r="623" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A623" s="40"/>
+    </row>
+    <row r="624" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A624" s="40"/>
+    </row>
+    <row r="625" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A625" s="40"/>
+    </row>
+    <row r="626" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A626" s="40"/>
+    </row>
+    <row r="627" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A627" s="40"/>
+    </row>
+    <row r="628" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A628" s="40"/>
+    </row>
+    <row r="629" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A629" s="40"/>
+    </row>
+    <row r="630" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A630" s="40"/>
+    </row>
+    <row r="631" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A631" s="40"/>
+    </row>
+    <row r="632" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A632" s="40"/>
+    </row>
+    <row r="633" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A633" s="40"/>
+    </row>
+    <row r="634" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A634" s="40"/>
+    </row>
+    <row r="635" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A635" s="40"/>
+    </row>
+    <row r="636" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A636" s="40"/>
+    </row>
+    <row r="637" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A637" s="40"/>
+    </row>
+    <row r="638" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A638" s="40"/>
+    </row>
+    <row r="639" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A639" s="40"/>
+    </row>
+    <row r="640" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A640" s="40"/>
+    </row>
+    <row r="641" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A641" s="40"/>
+    </row>
+    <row r="642" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A642" s="40"/>
+    </row>
+    <row r="643" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A643" s="40"/>
+    </row>
+    <row r="644" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A644" s="40"/>
+    </row>
+    <row r="645" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A645" s="40"/>
+    </row>
+    <row r="646" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A646" s="40"/>
+    </row>
+    <row r="647" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A647" s="40"/>
+    </row>
+    <row r="648" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A648" s="40"/>
+    </row>
+    <row r="649" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A649" s="40"/>
+    </row>
+    <row r="650" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A650" s="40"/>
+    </row>
+    <row r="651" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A651" s="40"/>
+    </row>
+    <row r="652" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A652" s="40"/>
+    </row>
+    <row r="653" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A653" s="40"/>
+    </row>
+    <row r="654" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A654" s="40"/>
+    </row>
+    <row r="655" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A655" s="40"/>
+    </row>
+    <row r="656" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A656" s="40"/>
+    </row>
+    <row r="657" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A657" s="40"/>
+    </row>
+    <row r="658" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A658" s="40"/>
+    </row>
+    <row r="659" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A659" s="40"/>
+    </row>
+    <row r="660" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A660" s="40"/>
+    </row>
+    <row r="661" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A661" s="40"/>
+    </row>
+    <row r="662" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A662" s="40"/>
+    </row>
+    <row r="663" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A663" s="40"/>
+    </row>
+    <row r="664" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A664" s="40"/>
+    </row>
+    <row r="665" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A665" s="40"/>
+    </row>
+    <row r="666" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A666" s="40"/>
+    </row>
+    <row r="667" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A667" s="40"/>
+    </row>
+    <row r="668" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A668" s="40"/>
+    </row>
+    <row r="669" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A669" s="40"/>
+    </row>
+    <row r="670" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A670" s="40"/>
+    </row>
+    <row r="671" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A671" s="40"/>
+    </row>
+    <row r="672" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A672" s="40"/>
+    </row>
+    <row r="673" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A673" s="40"/>
+    </row>
+    <row r="674" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A674" s="40"/>
+    </row>
+    <row r="675" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A675" s="40"/>
+    </row>
+    <row r="676" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A676" s="40"/>
+    </row>
+    <row r="677" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A677" s="40"/>
+    </row>
+    <row r="678" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A678" s="40"/>
+    </row>
+    <row r="679" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A679" s="40"/>
+    </row>
+    <row r="680" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A680" s="40"/>
+    </row>
+    <row r="681" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A681" s="40"/>
+    </row>
+    <row r="682" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A682" s="40"/>
+    </row>
+    <row r="683" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A683" s="40"/>
+    </row>
+    <row r="684" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A684" s="40"/>
+    </row>
+    <row r="685" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A685" s="40"/>
+    </row>
+    <row r="686" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A686" s="40"/>
+    </row>
+    <row r="687" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A687" s="40"/>
+    </row>
+    <row r="688" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A688" s="40"/>
+    </row>
+    <row r="689" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A689" s="40"/>
+    </row>
+    <row r="690" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A690" s="40"/>
+    </row>
+    <row r="691" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A691" s="40"/>
+    </row>
+    <row r="692" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A692" s="40"/>
+    </row>
+    <row r="693" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A693" s="40"/>
+    </row>
+    <row r="694" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A694" s="40"/>
+    </row>
+    <row r="695" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A695" s="40"/>
+    </row>
+    <row r="696" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A696" s="40"/>
+    </row>
+    <row r="697" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A697" s="40"/>
+    </row>
+    <row r="698" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A698" s="40"/>
+    </row>
+    <row r="699" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A699" s="40"/>
+    </row>
+    <row r="700" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A700" s="40"/>
+    </row>
+    <row r="701" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A701" s="40"/>
+    </row>
+    <row r="702" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A702" s="40"/>
+    </row>
+    <row r="703" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A703" s="40"/>
+    </row>
+    <row r="704" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A704" s="40"/>
+    </row>
+    <row r="705" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A705" s="40"/>
+    </row>
+    <row r="706" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A706" s="40"/>
+    </row>
+    <row r="707" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A707" s="40"/>
+    </row>
+    <row r="708" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A708" s="40"/>
+    </row>
+    <row r="709" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A709" s="40"/>
+    </row>
+    <row r="710" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A710" s="40"/>
+    </row>
+    <row r="711" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A711" s="40"/>
+    </row>
+    <row r="712" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A712" s="40"/>
+    </row>
+    <row r="713" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A713" s="40"/>
+    </row>
+    <row r="714" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A714" s="40"/>
+    </row>
+    <row r="715" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A715" s="40"/>
+    </row>
+    <row r="716" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A716" s="40"/>
+    </row>
+    <row r="717" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A717" s="40"/>
+    </row>
+    <row r="718" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A718" s="40"/>
+    </row>
+    <row r="719" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A719" s="40"/>
+    </row>
+    <row r="720" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A720" s="40"/>
+    </row>
+    <row r="721" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A721" s="40"/>
+    </row>
+    <row r="722" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A722" s="40"/>
+    </row>
+    <row r="723" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A723" s="40"/>
+    </row>
+    <row r="724" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A724" s="40"/>
+    </row>
+    <row r="725" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A725" s="40"/>
+    </row>
+    <row r="726" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A726" s="40"/>
+    </row>
+    <row r="727" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A727" s="40"/>
+    </row>
+    <row r="728" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A728" s="40"/>
+    </row>
+    <row r="729" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A729" s="40"/>
+    </row>
+    <row r="730" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A730" s="40"/>
+    </row>
+    <row r="731" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A731" s="40"/>
+    </row>
+    <row r="732" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A732" s="40"/>
+    </row>
+    <row r="733" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A733" s="40"/>
+    </row>
+    <row r="734" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A734" s="40"/>
+    </row>
+    <row r="735" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A735" s="40"/>
+    </row>
+    <row r="736" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A736" s="40"/>
+    </row>
+    <row r="737" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A737" s="40"/>
+    </row>
+    <row r="738" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A738" s="40"/>
+    </row>
+    <row r="739" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A739" s="40"/>
+    </row>
+    <row r="740" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A740" s="40"/>
+    </row>
+    <row r="741" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A741" s="40"/>
+    </row>
+    <row r="742" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A742" s="40"/>
+    </row>
+    <row r="743" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A743" s="40"/>
+    </row>
+    <row r="744" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A744" s="40"/>
+    </row>
+    <row r="745" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A745" s="40"/>
+    </row>
+    <row r="746" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A746" s="40"/>
+    </row>
+    <row r="747" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A747" s="40"/>
+    </row>
+    <row r="748" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A748" s="40"/>
+    </row>
+    <row r="749" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A749" s="40"/>
+    </row>
+    <row r="750" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A750" s="40"/>
+    </row>
+    <row r="751" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A751" s="40"/>
+    </row>
+    <row r="752" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A752" s="40"/>
+    </row>
+    <row r="753" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A753" s="40"/>
+    </row>
+    <row r="754" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A754" s="40"/>
+    </row>
+    <row r="755" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A755" s="40"/>
+    </row>
+    <row r="756" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A756" s="40"/>
+    </row>
+    <row r="757" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A757" s="40"/>
+    </row>
+    <row r="758" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A758" s="40"/>
+    </row>
+    <row r="759" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A759" s="40"/>
+    </row>
+    <row r="760" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A760" s="40"/>
+    </row>
+    <row r="761" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A761" s="40"/>
+    </row>
+    <row r="762" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A762" s="40"/>
+    </row>
+    <row r="763" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A763" s="40"/>
+    </row>
+    <row r="764" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A764" s="40"/>
+    </row>
+    <row r="765" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A765" s="40"/>
+    </row>
+    <row r="766" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A766" s="40"/>
+    </row>
+    <row r="767" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A767" s="40"/>
+    </row>
+    <row r="768" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A768" s="40"/>
+    </row>
+    <row r="769" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A769" s="40"/>
+    </row>
+    <row r="770" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A770" s="40"/>
+    </row>
+    <row r="771" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A771" s="40"/>
+    </row>
+    <row r="772" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A772" s="40"/>
+    </row>
+    <row r="773" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A773" s="40"/>
+    </row>
+    <row r="774" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A774" s="40"/>
+    </row>
+    <row r="775" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A775" s="40"/>
+    </row>
+    <row r="776" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A776" s="40"/>
+    </row>
+    <row r="777" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A777" s="40"/>
+    </row>
+    <row r="778" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A778" s="40"/>
+    </row>
+    <row r="779" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A779" s="40"/>
+    </row>
+    <row r="780" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A780" s="40"/>
+    </row>
+    <row r="781" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A781" s="40"/>
+    </row>
+    <row r="782" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A782" s="40"/>
+    </row>
+    <row r="783" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A783" s="40"/>
+    </row>
+    <row r="784" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A784" s="40"/>
+    </row>
+    <row r="785" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A785" s="40"/>
+    </row>
+    <row r="786" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A786" s="40"/>
+    </row>
+    <row r="787" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A787" s="40"/>
+    </row>
+    <row r="788" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A788" s="40"/>
+    </row>
+    <row r="789" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A789" s="40"/>
+    </row>
+    <row r="790" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A790" s="40"/>
+    </row>
+    <row r="791" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A791" s="40"/>
+    </row>
+    <row r="792" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A792" s="40"/>
+    </row>
+    <row r="793" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A793" s="40"/>
+    </row>
+    <row r="794" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A794" s="40"/>
+    </row>
+    <row r="795" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A795" s="40"/>
+    </row>
+    <row r="796" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A796" s="40"/>
+    </row>
+    <row r="797" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A797" s="40"/>
+    </row>
+    <row r="798" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A798" s="40"/>
+    </row>
+    <row r="799" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A799" s="40"/>
+    </row>
+    <row r="800" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A800" s="40"/>
+    </row>
+    <row r="801" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A801" s="40"/>
+    </row>
+    <row r="802" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A802" s="40"/>
+    </row>
+    <row r="803" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A803" s="40"/>
+    </row>
+    <row r="804" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A804" s="40"/>
+    </row>
+    <row r="805" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A805" s="40"/>
+    </row>
+    <row r="806" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A806" s="40"/>
+    </row>
+    <row r="807" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A807" s="40"/>
+    </row>
+    <row r="808" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A808" s="40"/>
+    </row>
+    <row r="809" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A809" s="40"/>
+    </row>
+    <row r="810" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A810" s="40"/>
+    </row>
+    <row r="811" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A811" s="40"/>
+    </row>
+    <row r="812" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A812" s="40"/>
+    </row>
+    <row r="813" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A813" s="40"/>
+    </row>
+    <row r="814" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A814" s="40"/>
+    </row>
+    <row r="815" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A815" s="40"/>
+    </row>
+    <row r="816" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A816" s="40"/>
+    </row>
+    <row r="817" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A817" s="40"/>
+    </row>
+    <row r="818" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A818" s="40"/>
+    </row>
+    <row r="819" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A819" s="40"/>
+    </row>
+    <row r="820" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A820" s="40"/>
+    </row>
+    <row r="821" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A821" s="40"/>
+    </row>
+    <row r="822" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A822" s="40"/>
+    </row>
+    <row r="823" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A823" s="40"/>
+    </row>
+    <row r="824" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A824" s="40"/>
+    </row>
+    <row r="825" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A825" s="40"/>
+    </row>
+    <row r="826" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A826" s="40"/>
+    </row>
+    <row r="827" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A827" s="40"/>
+    </row>
+    <row r="828" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A828" s="40"/>
+    </row>
+    <row r="829" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A829" s="40"/>
+    </row>
+    <row r="830" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A830" s="40"/>
+    </row>
+    <row r="831" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A831" s="40"/>
+    </row>
+    <row r="832" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A832" s="40"/>
+    </row>
+    <row r="833" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A833" s="40"/>
+    </row>
+    <row r="834" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A834" s="40"/>
+    </row>
+    <row r="835" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A835" s="40"/>
+    </row>
+    <row r="836" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A836" s="40"/>
+    </row>
+    <row r="837" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A837" s="40"/>
+    </row>
+    <row r="838" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A838" s="40"/>
+    </row>
+    <row r="839" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A839" s="40"/>
+    </row>
+    <row r="840" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A840" s="40"/>
+    </row>
+    <row r="841" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A841" s="40"/>
+    </row>
+    <row r="842" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A842" s="40"/>
+    </row>
+    <row r="843" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A843" s="40"/>
+    </row>
+    <row r="844" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A844" s="40"/>
+    </row>
+    <row r="845" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A845" s="40"/>
+    </row>
+    <row r="846" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A846" s="40"/>
+    </row>
+    <row r="847" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A847" s="40"/>
+    </row>
+    <row r="848" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A848" s="40"/>
+    </row>
+    <row r="849" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A849" s="40"/>
+    </row>
+    <row r="850" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A850" s="40"/>
+    </row>
+    <row r="851" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A851" s="40"/>
+    </row>
+    <row r="852" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A852" s="40"/>
+    </row>
+    <row r="853" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A853" s="40"/>
+    </row>
+    <row r="854" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A854" s="40"/>
+    </row>
+    <row r="855" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A855" s="40"/>
+    </row>
+    <row r="856" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A856" s="40"/>
+    </row>
+    <row r="857" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A857" s="40"/>
+    </row>
+    <row r="858" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A858" s="40"/>
+    </row>
+    <row r="859" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A859" s="40"/>
+    </row>
+    <row r="860" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A860" s="40"/>
+    </row>
+    <row r="861" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A861" s="40"/>
+    </row>
+    <row r="862" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A862" s="40"/>
+    </row>
+    <row r="863" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A863" s="40"/>
+    </row>
+    <row r="864" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A864" s="40"/>
+    </row>
+    <row r="865" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A865" s="40"/>
+    </row>
+    <row r="866" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A866" s="40"/>
+    </row>
+    <row r="867" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A867" s="40"/>
+    </row>
+    <row r="868" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A868" s="40"/>
+    </row>
+    <row r="869" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A869" s="40"/>
+    </row>
+    <row r="870" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A870" s="40"/>
+    </row>
+    <row r="871" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A871" s="40"/>
+    </row>
+    <row r="872" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A872" s="40"/>
+    </row>
+    <row r="873" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A873" s="40"/>
+    </row>
+    <row r="874" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A874" s="40"/>
+    </row>
+    <row r="875" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A875" s="40"/>
+    </row>
+    <row r="876" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A876" s="40"/>
+    </row>
+    <row r="877" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A877" s="40"/>
+    </row>
+    <row r="878" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A878" s="40"/>
+    </row>
+    <row r="879" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A879" s="40"/>
+    </row>
+    <row r="880" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A880" s="40"/>
+    </row>
+    <row r="881" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A881" s="40"/>
+    </row>
+    <row r="882" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A882" s="40"/>
+    </row>
+    <row r="883" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A883" s="40"/>
+    </row>
+    <row r="884" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A884" s="40"/>
+    </row>
+    <row r="885" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A885" s="40"/>
+    </row>
+    <row r="886" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A886" s="40"/>
+    </row>
+    <row r="887" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A887" s="40"/>
+    </row>
+    <row r="888" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A888" s="40"/>
+    </row>
+    <row r="889" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A889" s="40"/>
+    </row>
+    <row r="890" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A890" s="40"/>
+    </row>
+    <row r="891" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A891" s="40"/>
+    </row>
+    <row r="892" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A892" s="40"/>
+    </row>
+    <row r="893" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A893" s="40"/>
+    </row>
+    <row r="894" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A894" s="40"/>
+    </row>
+    <row r="895" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A895" s="40"/>
+    </row>
+    <row r="896" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A896" s="40"/>
+    </row>
+    <row r="897" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A897" s="40"/>
+    </row>
+    <row r="898" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A898" s="40"/>
+    </row>
+    <row r="899" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A899" s="40"/>
+    </row>
+    <row r="900" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A900" s="40"/>
+    </row>
+    <row r="901" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A901" s="40"/>
+    </row>
+    <row r="902" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A902" s="40"/>
+    </row>
+    <row r="903" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A903" s="40"/>
+    </row>
+    <row r="904" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A904" s="40"/>
+    </row>
+    <row r="905" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A905" s="40"/>
+    </row>
+    <row r="906" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A906" s="40"/>
+    </row>
+    <row r="907" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A907" s="40"/>
+    </row>
+    <row r="908" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A908" s="40"/>
+    </row>
+    <row r="909" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A909" s="40"/>
+    </row>
+    <row r="910" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A910" s="40"/>
+    </row>
+    <row r="911" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A911" s="40"/>
+    </row>
+    <row r="912" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A912" s="40"/>
+    </row>
+    <row r="913" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A913" s="40"/>
+    </row>
+    <row r="914" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A914" s="40"/>
+    </row>
+    <row r="915" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A915" s="40"/>
+    </row>
+    <row r="916" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A916" s="40"/>
+    </row>
+    <row r="917" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A917" s="40"/>
+    </row>
+    <row r="918" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A918" s="40"/>
+    </row>
+    <row r="919" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A919" s="40"/>
+    </row>
+    <row r="920" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A920" s="40"/>
+    </row>
+    <row r="921" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A921" s="40"/>
+    </row>
+    <row r="922" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A922" s="40"/>
+    </row>
+    <row r="923" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A923" s="40"/>
+    </row>
+    <row r="924" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A924" s="40"/>
+    </row>
+    <row r="925" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A925" s="40"/>
+    </row>
+    <row r="926" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A926" s="40"/>
+    </row>
+    <row r="927" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A927" s="40"/>
+    </row>
+    <row r="928" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A928" s="40"/>
+    </row>
+    <row r="929" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A929" s="40"/>
+    </row>
+    <row r="930" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A930" s="40"/>
+    </row>
+    <row r="931" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A931" s="40"/>
+    </row>
+    <row r="932" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A932" s="40"/>
+    </row>
+    <row r="933" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A933" s="40"/>
+    </row>
+    <row r="934" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A934" s="40"/>
+    </row>
+    <row r="935" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A935" s="40"/>
+    </row>
+    <row r="936" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A936" s="40"/>
+    </row>
+    <row r="937" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A937" s="40"/>
+    </row>
+    <row r="938" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A938" s="40"/>
+    </row>
+    <row r="939" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A939" s="40"/>
+    </row>
+    <row r="940" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A940" s="40"/>
+    </row>
+    <row r="941" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A941" s="40"/>
+    </row>
+    <row r="942" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A942" s="40"/>
+    </row>
+    <row r="943" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A943" s="40"/>
+    </row>
+    <row r="944" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A944" s="40"/>
+    </row>
+    <row r="945" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A945" s="40"/>
+    </row>
+    <row r="946" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A946" s="40"/>
+    </row>
+    <row r="947" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A947" s="40"/>
+    </row>
+    <row r="948" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A948" s="40"/>
+    </row>
+    <row r="949" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A949" s="40"/>
+    </row>
+    <row r="950" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A950" s="40"/>
+    </row>
+    <row r="951" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A951" s="40"/>
+    </row>
+    <row r="952" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A952" s="40"/>
+    </row>
+    <row r="953" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A953" s="40"/>
+    </row>
+    <row r="954" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A954" s="40"/>
+    </row>
+    <row r="955" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A955" s="40"/>
+    </row>
+    <row r="956" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A956" s="40"/>
+    </row>
+    <row r="957" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A957" s="40"/>
+    </row>
+    <row r="958" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A958" s="40"/>
+    </row>
+    <row r="959" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A959" s="40"/>
+    </row>
+    <row r="960" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A960" s="40"/>
+    </row>
+    <row r="961" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A961" s="40"/>
+    </row>
+    <row r="962" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A962" s="40"/>
+    </row>
+    <row r="963" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A963" s="40"/>
+    </row>
+    <row r="964" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A964" s="40"/>
+    </row>
+    <row r="965" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A965" s="40"/>
+    </row>
+    <row r="966" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A966" s="40"/>
+    </row>
+    <row r="967" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A967" s="40"/>
+    </row>
+    <row r="968" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A968" s="40"/>
+    </row>
+    <row r="969" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A969" s="40"/>
+    </row>
+    <row r="970" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A970" s="40"/>
+    </row>
+    <row r="971" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A971" s="40"/>
+    </row>
+    <row r="972" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A972" s="40"/>
+    </row>
+    <row r="973" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A973" s="40"/>
+    </row>
+    <row r="974" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A974" s="40"/>
+    </row>
+    <row r="975" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A975" s="40"/>
+    </row>
+    <row r="976" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A976" s="40"/>
+    </row>
+    <row r="977" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A977" s="40"/>
+    </row>
+    <row r="978" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A978" s="40"/>
+    </row>
+    <row r="979" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A979" s="40"/>
+    </row>
+    <row r="980" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A980" s="40"/>
+    </row>
+    <row r="981" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A981" s="40"/>
+    </row>
+    <row r="982" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A982" s="40"/>
+    </row>
+    <row r="983" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A983" s="40"/>
+    </row>
+    <row r="984" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A984" s="40"/>
+    </row>
+    <row r="985" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A985" s="40"/>
+    </row>
+    <row r="986" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A986" s="40"/>
+    </row>
+    <row r="987" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A987" s="40"/>
+    </row>
+    <row r="988" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A988" s="40"/>
+    </row>
+    <row r="989" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A989" s="40"/>
+    </row>
+    <row r="990" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A990" s="40"/>
+    </row>
+    <row r="991" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A991" s="40"/>
+    </row>
+    <row r="992" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A992" s="40"/>
+    </row>
+    <row r="993" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A993" s="40"/>
+    </row>
+    <row r="994" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A994" s="40"/>
+    </row>
+    <row r="995" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A995" s="40"/>
+    </row>
+    <row r="996" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A996" s="40"/>
+    </row>
+    <row r="997" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A997" s="40"/>
+    </row>
+    <row r="998" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A998" s="40"/>
+    </row>
+    <row r="999" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A999" s="40"/>
+    </row>
+    <row r="1000" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1000" s="40"/>
+    </row>
+    <row r="1001" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1001" s="40"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -34256,7 +37419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1ED1493-CE59-7A41-A79B-3D8DDA311E40}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -37445,7 +40608,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -37455,25 +40618,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="97"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="98"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
     </row>
@@ -37484,17 +40647,17 @@
       <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="96"/>
-      <c r="I2" s="96"/>
-      <c r="J2" s="96"/>
-      <c r="K2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="98"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -37578,11 +40741,11 @@
       <c r="B6" s="15">
         <v>16.5</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
@@ -37598,9 +40761,9 @@
       <c r="B7" s="15">
         <v>5.5</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
@@ -37617,9 +40780,9 @@
         <f>SUM(B6:B7)</f>
         <v>22</v>
       </c>
-      <c r="C8" s="92"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="92"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
@@ -37635,9 +40798,9 @@
       <c r="B9" s="15">
         <v>20</v>
       </c>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
@@ -37661,12 +40824,12 @@
       <c r="L10" s="13"/>
     </row>
     <row r="11" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="99" t="s">
+      <c r="A11" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="97"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="98"/>
       <c r="E11" s="17"/>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
@@ -37730,7 +40893,7 @@
       <c r="C15" s="22">
         <v>0.5</v>
       </c>
-      <c r="D15" s="100">
+      <c r="D15" s="101">
         <v>40</v>
       </c>
     </row>
@@ -37744,7 +40907,7 @@
       <c r="C16" s="22">
         <v>1</v>
       </c>
-      <c r="D16" s="101"/>
+      <c r="D16" s="102"/>
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20" t="s">
@@ -37767,12 +40930,12 @@
       <c r="D18" s="17"/>
     </row>
     <row r="19" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="88" t="s">
+      <c r="A19" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="90"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="91"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
@@ -37810,21 +40973,21 @@
         <v>34</v>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIF(Samples!B2:M9,"&lt;&gt;"&amp;"")</f>
+        <f>COUNTIF('Sample IDs'!B2:M9,"&lt;&gt;"&amp;"")</f>
         <v>36</v>
       </c>
-      <c r="C24" s="91" t="s">
+      <c r="C24" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="92"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
     </row>
     <row r="25" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="28" t="s">
@@ -37861,10 +41024,10 @@
       <c r="L26" s="13"/>
     </row>
     <row r="27" spans="1:26" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="94"/>
+      <c r="B27" s="95"/>
       <c r="C27" s="30"/>
       <c r="D27" s="30"/>
       <c r="E27" s="17"/>
@@ -38966,7 +42129,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -39027,7 +42190,7 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="88" t="s">
         <v>215</v>
       </c>
       <c r="B2" s="80" t="s">
@@ -39036,16 +42199,16 @@
       <c r="C2" s="80" t="s">
         <v>217</v>
       </c>
-      <c r="D2" s="102" t="s">
+      <c r="D2" s="88" t="s">
         <v>217</v>
       </c>
-      <c r="E2" s="102" t="s">
+      <c r="E2" s="88" t="s">
         <v>217</v>
       </c>
-      <c r="F2" s="102" t="s">
+      <c r="F2" s="88" t="s">
         <v>217</v>
       </c>
-      <c r="G2" s="102" t="s">
+      <c r="G2" s="88" t="s">
         <v>217</v>
       </c>
       <c r="H2" s="45" t="s">
@@ -39068,7 +42231,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="102" t="s">
+      <c r="A3" s="88" t="s">
         <v>216</v>
       </c>
       <c r="B3" s="45" t="s">
@@ -39112,7 +42275,7 @@
       <c r="A4" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="88" t="s">
         <v>214</v>
       </c>
       <c r="C4" s="49" t="s">
@@ -39247,7 +42410,7 @@
         <v>65</v>
       </c>
       <c r="G8" s="45"/>
-      <c r="H8" s="102" t="s">
+      <c r="H8" s="88" t="s">
         <v>218</v>
       </c>
       <c r="I8" s="45"/>
@@ -39273,7 +42436,7 @@
         <v>119</v>
       </c>
       <c r="G9" s="45"/>
-      <c r="H9" s="102" t="s">
+      <c r="H9" s="88" t="s">
         <v>219</v>
       </c>
       <c r="I9" s="45"/>
@@ -39299,7 +42462,7 @@
         <v>72</v>
       </c>
       <c r="G10" s="45"/>
-      <c r="H10" s="102"/>
+      <c r="H10" s="88"/>
       <c r="I10" s="45"/>
       <c r="J10" s="45"/>
       <c r="K10" s="45"/>
